--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -96,28 +96,6 @@
     <t>inCREDIT_Func_Get_OPT_Amount</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">inDISP_Enter8x16_GetAmount:
-輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
-pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
-pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Check_Is_Ticket_Purchase</t>
   </si>
   <si>
@@ -170,45 +148,6 @@
     <t>如果客製化為_CUSTOMER_INDICATOR_126_MASTERCARD_FLIGHT_TICKET_，
 inNCCC_Func_Get_PDS0530_Other 請使用者輸入按鍵選擇 航班號碼</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_StoreID</t>
-  </si>
-  <si>
-    <r>
-      <t>未輸入櫃號情況下:
-inDISP_Enter8x16_Character_Mask:
-   輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
-   更新</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-如果已有櫃號:
- return;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
   </si>
   <si>
     <r>
@@ -246,10 +185,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Get_OPT_PayItem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>繳費項目功能已開啟情況:
   如果未輸入繳費項目代碼:
@@ -281,185 +216,6 @@
      並在螢幕顯示繳費項目代碼 + 繳費項目說明。
   已存在繳費項目代碼:
       return;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_GetCardFields_CTLS</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
-     inCTLS_SendReadyForSale_Internal:
-       EMVCL_InitTransactionEx(szACTData.bTagNum, szACTData.pbaTransactionData, szACTData.usTransactionDataLen):
-         初始化一筆交易，設定金額、日期、交易類型
-     顯示一般交易金額，偵測事件，包含刷卡、插卡、人工輸入卡號、感應方式
-     以感應卡為例:
-          內圈的WhileLoop:
-               inCTLS_ReceiveReadyForSales_Flow:
-                    ulCTLS_ReceiveReadyForSales_Internal:
-                          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>srCtlsObj.lnSaleRespCode = EMVCL_PerformTransactionEx(&amp;szRCDataEx):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                               透過EMVCL_PerformTransactionEx獲得 發起的交易結果(szRCDataEx)
-          外圈的WhileLoop:
-               偵測感應事件，執行
-                    ulCTLS_CheckResponseCode_SALE:
-                          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszContactlessBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                          inCTLS_UnPackReadyForSale_Flow:
-                              inCTLS_UnPackReadyForSale_Internal:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                             srCtlsObj.uszSchemeID[0] = SCHEME_ID_91_QUICKPASS;
-                                  pobTran-&gt;inTransactionCode = _CUP_SALE_;
-                                  pobTran-&gt;srBRec.inCode = pobTran-&gt;inTransactionCode;
-                                  pobTran-&gt;srBRec.inOrgCode = pobTran-&gt;inTransactionCode;
-                                  pobTran-&gt;srBRec.uszCUPTransBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inKMS_CheckKey:
-                                      這邊看起來是檢查KEY是否存在
-                                       inNCCC_Func_CUP_PowerOn_LogOn:
-                                            暫時沒看
-                                  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszWAVESchemeID = srCtlsObj.uszSchemeID[0];</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inFunc_BCD_to_ASCII(&amp;szASCII[0], &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len * 2);
-                                  szRCDataEx.bTrack2Len = szRCDataEx.bTrack2Len * 2;
-                                  memset(szRCDataEx.baTrack2Data, 0x00, sizeof(szRCDataEx.baTrack2Data));
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                             memcpy(&amp;szRCDataEx.baTrack2Data[0], &amp;szASCII[0], szRCDataEx.bTrack2Len);
-                             memcpy(pobTran-&gt;szTrack1, szRCDataEx.baTrack1Data, szRCDataEx.bTrack1Len);
-                             memcpy(pobTran-&gt;szTrack2, &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inCARD_unPackCard:
-                                       </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>取得PAN、ExpDate、szServiceCode 、CardHolder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inCTLS_ProcessChipData:
-                                       組電文的EMV Data ，這部分的tagID不清楚要參考哪個文件，需要詢問。
-                                  inCTLS_ExceptionCheck:
-                                        暫時沒看</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -762,10 +518,6 @@
     <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
   </si>
   <si>
-    <t>一樣依據pobTran-&gt;srBRec.uszDCCTransBit == VS_TRUE ，往下判斷交易功能是否開啟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>依據上面那支程式的pobTran-&gt;srBRec.uszDCCTransBit == VS_TRUE ，
 設定</t>
@@ -782,10 +534,6 @@
       </rPr>
       <t>pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(暫時沒看Code)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1518,6 +1266,305 @@
   </si>
   <si>
     <t>inNCCC_DCC_Final_DCC_Option</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>先檢查當筆交易如果是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+inDISP_Enter8x16_GetAmount:
+輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
+pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
+pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_StoreID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>檢查櫃號功能開啟，如果當筆交易為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+未輸入櫃號情況下:
+inDISP_Enter8x16_Character_Mask:
+   輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
+   更新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+如果已有櫃號:
+ return;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Get_OPT_PayItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_GetCardFields_CTLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
+     inCTLS_SendReadyForSale_Internal:
+       EMVCL_InitTransactionEx(szACTData.bTagNum, szACTData.pbaTransactionData, szACTData.usTransactionDataLen):
+         初始化一筆交易，設定金額、日期、交易類型
+     顯示一般交易金額，偵測事件，包含刷卡、插卡、人工輸入卡號、感應方式
+     以感應卡為例:
+          內圈的WhileLoop:
+               inCTLS_ReceiveReadyForSales_Flow:
+                    ulCTLS_ReceiveReadyForSales_Internal:
+                          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>srCtlsObj.lnSaleRespCode = EMVCL_PerformTransactionEx(&amp;szRCDataEx):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                               透過EMVCL_PerformTransactionEx獲得 發起的交易結果(szRCDataEx)
+          外圈的WhileLoop:
+               偵測感應事件，執行
+                    ulCTLS_CheckResponseCode_SALE:
+                          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszContactlessBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                          inCTLS_UnPackReadyForSale_Flow:
+                              inCTLS_UnPackReadyForSale_Internal:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                             srCtlsObj.uszSchemeID[0] = SCHEME_ID_91_QUICKPASS;
+                                  pobTran-&gt;inTransactionCode = _CUP_SALE_;
+                                  pobTran-&gt;srBRec.inCode = pobTran-&gt;inTransactionCode;
+                                  pobTran-&gt;srBRec.inOrgCode = pobTran-&gt;inTransactionCode;
+                                  pobTran-&gt;srBRec.uszCUPTransBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inKMS_CheckKey:
+                                      這邊看起來是檢查KEY是否存在
+                                       inNCCC_Func_CUP_PowerOn_LogOn:
+                                            暫時沒看
+                                  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszWAVESchemeID = srCtlsObj.uszSchemeID[0];</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inFunc_BCD_to_ASCII(&amp;szASCII[0], &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len * 2);
+                                  szRCDataEx.bTrack2Len = szRCDataEx.bTrack2Len * 2;
+                                  memset(szRCDataEx.baTrack2Data, 0x00, sizeof(szRCDataEx.baTrack2Data));
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                             memcpy(&amp;szRCDataEx.baTrack2Data[0], &amp;szASCII[0], szRCDataEx.bTrack2Len);
+                             memcpy(pobTran-&gt;szTrack1, szRCDataEx.baTrack1Data, szRCDataEx.bTrack1Len);
+                             memcpy(pobTran-&gt;szTrack2, &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inCARD_unPackCard:
+                                       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>取得PAN、ExpDate、szServiceCode 、CardHolder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inCTLS_ProcessChipData:
+                                       組電文的EMV Data ，這部分的tagID不清楚要參考哪個文件，需要詢問。
+                                  inCTLS_ExceptionCheck:
+                                        暫時沒看</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依據條件判斷功能是否關閉，如果有功能關閉，則return VS_ERROR;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(暫時沒看Code)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1941,514 +1988,514 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="90" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="195" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C50" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C54" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C58" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C72" s="4" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C74" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="2:3" ht="90" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C84" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C88" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C90" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C92" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C94" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C96" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="2:3" ht="210" x14ac:dyDescent="0.3">
       <c r="C98" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="100" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C100" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C104" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C106" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C108" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C110" s="3" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -220,19 +220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_CL_Power_Off</t>
-  </si>
-  <si>
-    <t>關閉感應天線</t>
-  </si>
-  <si>
-    <t>inFunc_CheckPAN_EXP</t>
-  </si>
-  <si>
-    <t>螢幕顯示卡號與有效期供使用者確認</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>/*
     &lt;END&gt;
 */</t>
@@ -256,12 +243,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Must_SETTLE</t>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Func_Must_SETTLE</t>
-  </si>
-  <si>
     <t>透過inGetMustSettleBit(szMustSettleBit)取得 是否結帳的flag判斷是否要先結帳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -282,9 +263,6 @@
   <si>
     <t>撥接開啟+setConfig，實際作撥接動作inModem_Dial，建立連線?</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_GetAmount</t>
   </si>
   <si>
     <r>
@@ -323,16 +301,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Check_Amount_by_Card</t>
-  </si>
-  <si>
-    <t>目前此function 客製化for 建設公司需求 ，暫時不看內部邏輯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_Check_Batch_limit</t>
-  </si>
-  <si>
     <t>inFunc_Check_Single_Trade:
      判斷當筆金額上限
 inFunc_Check_Total_Trade:
@@ -340,12 +308,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inCREDIT_Func_GetStoreID</t>
-  </si>
-  <si>
-    <t>inCREDIT_Func_GetProductCode</t>
-  </si>
-  <si>
     <r>
       <t>如果有開啟列印產品代碼功能，且已存在產品代碼，return，
 反之則要求輸入兩碼數字比對PCD檔是否有對應的HotKey，
@@ -368,120 +330,6 @@
   <si>
     <t>如果有開啟櫃號功能，且已存在櫃號，return，反之則要求輸入櫃號</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_MakeRefNo</t>
-  </si>
-  <si>
-    <t>inNCCC_ESC_Check</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">看起來根據特定條件設定
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.inESCUploadMode = _ESC_STATUS_NOT_SUPPORTED_;
-pobTran-&gt;srBRec.inESCTransactionCode = pobTran-&gt;inTransactionCode;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_CheckSpecialCard_Flow</t>
-  </si>
-  <si>
-    <t>inNCCC_Func_Check_Special_Card_In_OPT_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">有輸入金額情況:
-    inNCCC_Func_CheckSpecialCard_Flow:
-        如果有啟動特殊卡別參數檔功能:
-            inNCCC_Func_CheckSpecialCard:
-                符合活動代碼情況:
-                     檢查出符合卡號範圍內的SCDTRec，檢查金額、活動日期是否有效
-        更新值:
-            </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
-          pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;
-          pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">        </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable);
-        inSqlite_Get_Table_ByRecordID_All(gszReprintDBPath, _TABLE_NAME_DUTY_FREE_FUNCTION_, 0, &amp;srAll);
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可參考上述的inNCCC_Func_Check_Special_Card_In_OPT_Flow，
-因為在這邊已經檢查過，所以pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE，直接return;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_CHECK</t>
   </si>
   <si>
     <r>
@@ -645,26 +493,6 @@
   </si>
   <si>
     <t>inNCCC_Func_BDAU_DeleteAccumBatch</t>
-  </si>
-  <si>
-    <r>
-      <t>組szRRN:szRRN[0] = "9"，szRRN[1:5]取端末機代號[3~7] +szRRN[6:7] 取szlnBatchNum取兩數 + szRRN[8:10]取lnOrgInvNum取三數，並向右填滿空格，讓szRRN 長度固定12(序號 Ref. No.)
-組szAwardSN(優惠序號):端末機代號[0:7]+取得系統日期轉為西元年月日時分秒 取年月
-如果不是信託交易，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>strncpy(pobTran-&gt;srBRec.szRefNo, szRRN, sizeof(pobTran-&gt;srBRec.szRefNo))</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>看起來是針對客製化_CUSTOMER_INDICATOR_042_BDAU1_或是_CUSTOMER_INDICATOR_043_BDAU9_ 要刪除Batch資料</t>
@@ -1372,6 +1200,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>依據條件判斷功能是否關閉，如果有功能關閉，則return VS_ERROR;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(暫時沒看Code)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>inCREDIT_Func_Get_OPT_ProductCode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1560,11 +1396,201 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>依據條件判斷功能是否關閉，如果有功能關閉，則return VS_ERROR;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(暫時沒看Code)</t>
+    <t>inNCCC_Func_Check_Special_Card_In_OPT_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_CL_Power_Off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼叫CTOS_CLPowerOff()，關閉無線感應讀卡機的開關</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckPAN_EXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>螢幕顯示卡號與有效期供使用者確認</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetAmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Check_Amount_by_Card</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前此function只針對建設公司需求做客製化  ，暫時不看內部邏輯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Check_Batch_limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetStoreID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetProductCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_MakeRefNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>組szRRN:szRRN[0] = "9"，szRRN[1:5]取端末機代號[3~7] +szRRN[6:7] 取szlnBatchNum取兩數 + szRRN[8:10]取lnOrgInvNum取三數，並向右填滿空格，讓szRRN 長度固定12(序號 Ref. No.)
+組szAwardSN(優惠序號):端末機代號[0:7]+取得系統日期轉為西元年月日時分秒 取年月
+如果不是信託交易，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strncpy(pobTran-&gt;srBRec.szRefNo, szRRN, sizeof(pobTran-&gt;srBRec.szRefNo))組簽單上的序號。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_ESC_Check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可參考上述的inNCCC_Func_Check_Special_Card_In_OPT_Flow，
+因為在這邊已經檢查過，所以pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE，直接return;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_CheckSpecialCard_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_CHECK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">有輸入金額情況:
+    inNCCC_Func_CheckSpecialCard_Flow:
+        如果有啟動特殊卡別參數檔功能:
+            inNCCC_Func_CheckSpecialCard:
+                符合活動代碼情況:
+                     檢查出符合活動代碼的SCDTRec，進一步檢查卡號是否符合範圍、交易金額是否符合活動限額，活動日期是否在範圍內。
+        更新值:
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
+          pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;
+          pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable);
+        inSqlite_Get_Table_ByRecordID_All(gszReprintDBPath, _TABLE_NAME_DUTY_FREE_FUNCTION_, 0, &amp;srAll);
+                因為srAll有link到inTableID、szEverRichSCDTEnable，後續會針對客製化+szEverRichSCDTEnable等條件判斷額外判斷_CAMPAIGNNUMBER_05_EVER_RICH_COMBO_檢查這個活動代碼。
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">看起來根據特定條件設定
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">pobTran-&gt;srBRec.inESCUploadMode = _ESC_STATUS_NOT_SUPPORTED_;
+pobTran-&gt;srBRec.inESCTransactionCode = pobTran-&gt;inTransactionCode;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>這邊有水位做一些判斷，不清楚是幹嘛的</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1990,7 +2016,7 @@
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
@@ -2055,17 +2081,17 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
@@ -2075,7 +2101,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="120" x14ac:dyDescent="0.3">
@@ -2085,417 +2111,417 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" ht="195" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C50" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C54" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C58" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" ht="60" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" ht="45" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C72" s="4" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C74" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="2:3" ht="90" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C84" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C88" s="1" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C90" s="4" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="92" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C92" s="1" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C94" s="1" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C96" s="1" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="2:3" ht="210" x14ac:dyDescent="0.3">
       <c r="C98" s="1" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
     <row r="100" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C100" s="1" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="104" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C104" s="1" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C106" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C108" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C110" s="3" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -360,12 +360,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_DCC_CurrencyOption</t>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
-  </si>
-  <si>
     <r>
       <t>依據上面那支程式的pobTran-&gt;srBRec.uszDCCTransBit == VS_TRUE ，
 設定</t>
@@ -814,74 +808,6 @@
     <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">inFunc_NCCC_PrintReceipt_ByBuffer_ESC:
-   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pobTran-&gt;srBRec.inPrintOption = _PRT_CUST_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    inCREDIT_PRINT_Receipt_ByBuffer:
-        inPrintIndex = _REPORT_INDEX_NORMAL_;
-                呼叫inPRINT_Buffer_PutGraphic() 、inPRINT_Buffer_PutIn()等function，
-                把Logo、TID/MID、簽單內容、金額資料等存到Buffer，
-                最後呼叫inPRINT_Buffer_OutPut，將Buffer中的資料印出</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">如果是ECR交易:
-    pobTran-&gt;uszDelaySendBit == VS_TRUE:
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;uszDelaySendBit = VS_FALSE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-        inECR_Send_Transaction_Result:
-            !pobTran-&gt;uszDelaySendBit:
-                inECR_Send_Transaction:
-                        組電文、發送電文</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Receive_EI_Flow</t>
   </si>
   <si>
@@ -1034,10 +960,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_DCC_OnlineRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">如果是DCC交易:
     inFunc_Find_Specific_HDTindex:
@@ -1213,10 +1135,6 @@
   </si>
   <si>
     <t>inNCCC_Func_Get_OPT_PayItem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_GetCardFields_CTLS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1591,6 +1509,90 @@
       </rPr>
       <t>這邊有水位做一些判斷，不清楚是幹嘛的</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_CurrencyOption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_OnlineRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">如果是ECR交易:
+    pobTran-&gt;uszDelaySendBit == VS_TRUE:
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;uszDelaySendBit = VS_FALSE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        inECR_Send_Transaction_Result:
+            !pobTran-&gt;uszDelaySendBit:
+                inECR_Send_Transaction:
+                        組電文、發送電文</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inFunc_NCCC_PrintReceipt_ByBuffer_ESC:
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pobTran-&gt;srBRec.inPrintOption = _PRT_CUST_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    inCREDIT_PRINT_Receipt_ByBuffer:
+        inPrintIndex = _REPORT_INDEX_NORMAL_;
+                呼叫inPRINT_Buffer_PutGraphic() 、inPRINT_Buffer_PutIn()等function，
+                把Logo、TID/MID、簽單內容、金額資料等存到Buffer，
+                最後呼叫inPRINT_Buffer_OutPut，將Buffer中的資料印出</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_GetCardFields_CTLS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2016,7 +2018,7 @@
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
@@ -2081,17 +2083,17 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
@@ -2101,7 +2103,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="120" x14ac:dyDescent="0.3">
@@ -2111,42 +2113,42 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -2171,7 +2173,7 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
@@ -2181,7 +2183,7 @@
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="30" x14ac:dyDescent="0.3">
@@ -2191,7 +2193,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -2211,7 +2213,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
@@ -2221,17 +2223,17 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="60" x14ac:dyDescent="0.3">
@@ -2241,7 +2243,7 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
@@ -2251,7 +2253,7 @@
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -2261,37 +2263,37 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
@@ -2301,222 +2303,222 @@
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C72" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C74" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78" spans="2:3" ht="90" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C84" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C88" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C90" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C92" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C94" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C96" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="2:3" ht="210" x14ac:dyDescent="0.3">
       <c r="C98" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C100" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C104" s="1" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C106" s="1" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C108" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C110" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="45" x14ac:dyDescent="0.3">

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
   <si>
     <t>inEVENT_Responder</t>
   </si>
@@ -99,11 +99,6 @@
     <t>inNCCC_Func_Check_Is_Ticket_Purchase</t>
   </si>
   <si>
-    <t>如果客製化為_CUSTOMER_INDICATOR_126_MASTERCARD_FLIGHT_TICKET_，
-請使用這輸入數字(是按[1]，否按[2])是否為機票交易</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Get_PDS0523</t>
   </si>
   <si>
@@ -234,24 +229,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Check_Transaction_Function_Flow</t>
-  </si>
-  <si>
-    <t>inNCCC_Func_Check_Transaction_Function
-inNCCC_Func_Check_Transaction_Function_Award
-確認交易功能是否開啟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>透過inGetMustSettleBit(szMustSettleBit)取得 是否結帳的flag判斷是否要先結帳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先Load HDT檔案 DCC主機功能是否開啟，進一步透過inGetMustSettleBit(szMustSettleBit)，
-取得是否結帳的flag判斷是否要先結帳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不可連續刷卡檢核有開啟情況:
     檢查卡號和gszDuplicatePAN如果重複，顯示提示訊息。
 Note:gszDuplicatePAN值來自於 inFunc_DuplicateSave()</t>
@@ -301,13 +278,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inFunc_Check_Single_Trade:
-     判斷當筆金額上限
-inFunc_Check_Total_Trade:
-     算出批次總金額，並判斷是否超過範圍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>如果有開啟列印產品代碼功能，且已存在產品代碼，return，
 反之則要求輸入兩碼數字比對PCD檔是否有對應的HotKey，
@@ -329,53 +299,6 @@
   </si>
   <si>
     <t>如果有開啟櫃號功能，且已存在櫃號，return，反之則要求輸入櫃號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>主要在設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszDCCTransBit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>開關上</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>依據上面那支程式的pobTran-&gt;srBRec.uszDCCTransBit == VS_TRUE ，
-設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -421,72 +344,14 @@
     <t>inNCCC_Func_SetTxnOnlineOffline_Flow</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">inNCCC_ATS_Func_SetTxnOnlineOffline:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">    pobTran-&gt;srBRec.uszOfflineBit = VS_FALSE; /* 當筆交易要 Online */
-    pobTran-&gt;srBRec.uszUpload1Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;srBRec.uszUpload2Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;srBRec.uszUpload3Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;uszReversalBit = VS_TRUE;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_BuildAndSendPacket_Flow</t>
   </si>
   <si>
-    <t>inNCCC_Func_Beep_After_Auth</t>
-  </si>
-  <si>
     <t>客製化為_CUSTOMER_INDICATOR_123_IKEA_或是_CUSTOMER_INDICATOR_124_EVER_RICH_ 加入提示音</t>
   </si>
   <si>
     <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>利用TID運算出卡號的Transaction Number(交易編號)，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> strcpy(pobTran-&gt;srBRec.szTxnNo, szTxNo);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-因為原本註解就寫得很完整了，詳細可直接閱讀這支程式</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_BDAU_DeleteAccumBatch</t>
   </si>
   <si>
     <t>看起來是針對客製化_CUSTOMER_INDICATOR_042_BDAU1_或是_CUSTOMER_INDICATOR_043_BDAU9_ 要刪除Batch資料</t>
@@ -561,9 +426,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inFunc_DuplicateSave</t>
-  </si>
-  <si>
     <t>inFunc_DuplicateCheck</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -595,15 +457,6 @@
       <t xml:space="preserve">
 Note:在inFunc_DuplicateCheck()會使用到變數gszDuplicatePAN</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_UpdateInvNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新每個主機的資料庫欄位上，
-判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -653,38 +506,6 @@
       <t>，
     並更新回資料庫(inBATCH_Update_NoSignature_By_Sqlite)
 針對CUP交易，螢幕顯示交易完成、授權碼，使用者輸入Enter/逾時離開程式</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inSIGN_TouchSignature_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>看起來是設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">pobTran-&gt;srBRec.inSignStatus </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>更新回資料庫，又或是開啟signPad觸控簽名功能</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -735,6 +556,1081 @@
   </si>
   <si>
     <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>針對ECR發起的交易，且客製化會處理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_ATS_Func_BuildAndSendPacket:
+   inNCCC_ATS_GetSTAN:
+      取得STAN Number
+   處理online交易:
+      inNCCC_ATS_ProcessReversal:
+         inNCCC_ATS_ProcessReversal:
+            inNCCC_ATS_ReversalSave_Flow:
+               因為判斷撥接備援功能為OFF，所以不做事
+   inNCCC_ATS_ProcessOnline:
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inISOTxnCode = pobTran-&gt;inTransactionCode;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inNCCC_ATS_SendPackRecvUnPack:
+      組 ISO 電文、傳送及接收 ISO 電文、解 ISO 電文
+   inNCCC_ATS_CheckRespCode:
+      依據回應碼返回交易結果</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTransactionResult = _TRAN_RESULT_AUTHORIZED_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+   inNCCC_ATS_CheckAuthCode:
+      如果不是CUP交易且授權碼是空白或是"000000"情況:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">         pobTran-&gt;inErrorMsg = _ERROR_CODE_V3_AUTH_CODE_NOT_VALID_;
+         pobTran-&gt;inTransactionResult = _TRAN_RESULT_CANCELLED_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      反之:
+           return VS_SUCCESS;
+   inNCCC_ATS_SetSTAN:
+      STAN Number 加一
+   inNCCC_ATS_AnalysePacket:
+      inNCCC_ATS_OnlineAnalyseEMV:
+         pobTran-&gt;inTransactionResult == _TRAN_RESULT_AUTHORIZED_情況:
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EMVGlobConfig.uszAction = d_ONLINE_ACTION_APPROVAL;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+               inFunc_SetEDCDateTime(pobTran-&gt;srBRec.szDate, pobTran-&gt;srBRec.szTime):
+                     要更新端末機的日期及時間</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_StoreID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(暫時沒看Code)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
+     inCTLS_SendReadyForSale_Internal:
+       EMVCL_InitTransactionEx(szACTData.bTagNum, szACTData.pbaTransactionData, szACTData.usTransactionDataLen):
+         初始化一筆交易，設定金額、日期、交易類型
+     顯示一般交易金額，偵測事件，包含刷卡、插卡、人工輸入卡號、感應方式
+     以感應卡為例:
+          內圈的WhileLoop:
+               inCTLS_ReceiveReadyForSales_Flow:
+                    ulCTLS_ReceiveReadyForSales_Internal:
+                          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>srCtlsObj.lnSaleRespCode = EMVCL_PerformTransactionEx(&amp;szRCDataEx):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                               透過EMVCL_PerformTransactionEx獲得 發起的交易結果(szRCDataEx)
+          外圈的WhileLoop:
+               偵測感應事件，執行
+                    ulCTLS_CheckResponseCode_SALE:
+                          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszContactlessBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                          inCTLS_UnPackReadyForSale_Flow:
+                              inCTLS_UnPackReadyForSale_Internal:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                             srCtlsObj.uszSchemeID[0] = SCHEME_ID_91_QUICKPASS;
+                                  pobTran-&gt;inTransactionCode = _CUP_SALE_;
+                                  pobTran-&gt;srBRec.inCode = pobTran-&gt;inTransactionCode;
+                                  pobTran-&gt;srBRec.inOrgCode = pobTran-&gt;inTransactionCode;
+                                  pobTran-&gt;srBRec.uszCUPTransBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inKMS_CheckKey:
+                                      這邊看起來是檢查KEY是否存在
+                                       inNCCC_Func_CUP_PowerOn_LogOn:
+                                            暫時沒看
+                                  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszWAVESchemeID = srCtlsObj.uszSchemeID[0];</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inFunc_BCD_to_ASCII(&amp;szASCII[0], &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len * 2);
+                                  szRCDataEx.bTrack2Len = szRCDataEx.bTrack2Len * 2;
+                                  memset(szRCDataEx.baTrack2Data, 0x00, sizeof(szRCDataEx.baTrack2Data));
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                             memcpy(&amp;szRCDataEx.baTrack2Data[0], &amp;szASCII[0], szRCDataEx.bTrack2Len);
+                             memcpy(pobTran-&gt;szTrack1, szRCDataEx.baTrack1Data, szRCDataEx.bTrack1Len);
+                             memcpy(pobTran-&gt;szTrack2, &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inCARD_unPackCard:
+                                       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>取得PAN、ExpDate、szServiceCode 、CardHolder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inCTLS_ProcessChipData:
+                                       組電文的EMV Data ，這部分的tagID不清楚要參考哪個文件，需要詢問。
+                                  inCTLS_ExceptionCheck:
+                                        暫時沒看</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Check_Special_Card_In_OPT_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼叫CTOS_CLPowerOff()，關閉無線感應讀卡機的開關</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>螢幕顯示卡號與有效期供使用者確認</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前此function只針對建設公司需求做客製化  ，暫時不看內部邏輯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetProductCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">有輸入金額情況:
+    inNCCC_Func_CheckSpecialCard_Flow:
+        如果有啟動特殊卡別參數檔功能:
+            inNCCC_Func_CheckSpecialCard:
+                符合活動代碼情況:
+                     檢查出符合活動代碼的SCDTRec，進一步檢查卡號是否符合範圍、交易金額是否符合活動限額，活動日期是否在範圍內。
+        更新值:
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
+          pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;
+          pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable);
+        inSqlite_Get_Table_ByRecordID_All(gszReprintDBPath, _TABLE_NAME_DUTY_FREE_FUNCTION_, 0, &amp;srAll);
+                因為srAll有link到inTableID、szEverRichSCDTEnable，後續會針對客製化+szEverRichSCDTEnable等條件判斷額外判斷_CAMPAIGNNUMBER_05_EVER_RICH_COMBO_檢查這個活動代碼。
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">如果是ECR交易:
+    pobTran-&gt;uszDelaySendBit == VS_TRUE:
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;uszDelaySendBit = VS_FALSE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        inECR_Send_Transaction_Result:
+            !pobTran-&gt;uszDelaySendBit:
+                inECR_Send_Transaction:
+                        組電文、發送電文</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inFunc_NCCC_PrintReceipt_ByBuffer_ESC:
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pobTran-&gt;srBRec.inPrintOption = _PRT_CUST_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    inCREDIT_PRINT_Receipt_ByBuffer:
+        inPrintIndex = _REPORT_INDEX_NORMAL_;
+                呼叫inPRINT_Buffer_PutGraphic() 、inPRINT_Buffer_PutIn()等function，
+                把Logo、TID/MID、簽單內容、金額資料等存到Buffer，
+                最後呼叫inPRINT_Buffer_OutPut，將Buffer中的資料印出</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>先檢查當筆交易如果是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+inDISP_Enter8x16_GetAmount:
+輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
+pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
+pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果客製化為_CUSTOMER_INDICATOR_126_MASTERCARD_FLIGHT_TICKET_，
+請使用者輸入數字(是按[1]，否按[2])是否為機票交易</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>檢查櫃號功能開啟，如果當筆交易為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+未輸入櫃號情況下:
+inDISP_Enter8x16_Character_Mask:
+   輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
+   更新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>並且剩餘長度用空白補齊。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+如果已有櫃號:
+ return;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Get_OPT_PayItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_GetCardFields_CTLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_CL_Power_Off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckPAN_EXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">      </t>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">這支程式用於檢查 交易類型的交易功能參數是否都開啟
+如果pobTran-&gt;srBRec.uszDCCTransBit == VS_FALSE，
+    return VS_SUCCESS;
+如果不同交易類型的交易功能參數未開啟，
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">pobTran-&gt;inErrorMsg = _ERROR_CODE_V3_FUNC_CLOSE_; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    return VS_ERROR;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Check_Transaction_Function_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Check_Transaction_Function:
+     只檢查NCCC的交易功能參數，且已知NCCC主機的索引為第一筆，所以inLoadHDTRec(0)，
+     最後判斷特定交易類型的交易功能參數是否有On起來。
+inNCCC_Func_Check_Transaction_Function_Award:
+     一樣是判斷特定交易類型的功能是否有On起來。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Find_Specific_HDTindex取得NCCC的主機index，inLoadHDPTRec(index)使用sql方式更新HDPT_REC，
+inGetMustSettleBit取得HDPT_REC的szMustSettleBit是否結帳的flag，當szMustSettleBit為Y表示要結帳，
+組好DISPLAY_OBJECT，秀在LCD上。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_GetDCC_Enable:
+   主要找符合DCC主機的HDT_REC，並檢查主機功能是否開啟。
+inLoadHDPTRec:
+   inLoadHDPTRec(inDCC_HostIndex)，inGetMustSettleBit取得HDPT_REC的szMustSettleBit是否結帳的flag，當szMustSettleBit為Y表示要結帳，
+組好DISPLAY_OBJECT，秀在LCD上。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetAmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Check_Amount_by_Card</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Check_Batch_limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客製化是_CUSTOMER_INDICATOR_076_8_DIGITS_才做以下流程:
+     inFunc_Check_Single_Trade:
+          判斷當筆金額上限
+     inFunc_Check_Total_Trade:
+          算出批次總金額，並判斷是否超過範圍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetStoreID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_MakeRefNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">組簽單上的序號(Ref. No.):
+    如果NCCC FES MODE不是_NCCC_01_SPDH_MODE_情況下:
+        組szRRN序號:
+            szRRN[0] = "9"，szRRN[1:5]取端末機代號[3~7] +szRRN[6:7] 取szlnBatchNum取兩數+
+            szRRN[8:10]取lnOrgInvNum取三數，並向右填滿空格，讓szRRN 長度固定12。
+        組szAwardSN(優惠序號):
+            端末機代號[0:7]+取得系統日期轉為西元年月日時分秒 取年月
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strcpy(pobTran-&gt;srBRec.szAwardSN, szTerminalID);
+          memcpy(&amp;pobTran-&gt;srBRec.szAwardSN[8], &amp;szTemplate[0], 14);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(szTemplate系統時間)
+    如果是信託交易:
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strncpy(pobTran-&gt;srTrustRec.szTrustRRN, szRRN, sizeof(pobTran-&gt;srTrustRec.szTrustRRN));</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    不是信託交易:
+       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> strncpy(pobTran-&gt;srBRec.szRefNo, szRRN, sizeof(pobTran-&gt;srBRec.szRefNo))</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_ESC_Check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">看起來根據特定條件設定
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">pobTran-&gt;srBRec.inESCUploadMode = _ESC_STATUS_SUPPORTED_;
+pobTran-&gt;srBRec.inESCTransactionCode = pobTran-&gt;inTransactionCode;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>這邊有判斷水位，不確定用意為何?</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_CheckSpecialCard_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可參考上述的 inNCCC_Func_Check_Special_Card_In_OPT_Flow，
+因為在這邊已經檢查過，所以pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE，直接return;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_CHECK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>主要在設定pobTran-&gt;srBRec.uszDCCTransBit開關上
+      以下列出一部分判斷，會設定</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszDCCTransBit = VS_FALSE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，包含:
+            從HDT檔案取得DCC主機但主機功能未開啟、
+            如果交易類型不是結帳情況下:
+                  inNCCC_DCC_Already_Have_Parameter:
+                        存在所有舊參數檔案(DCCBin.dat、ERS.dat、VISADis.dat、 MASTERDis.dat)
+                  不支援DCC+CUP、不支援DCC + SaleOffline、
+                  不支援DCC + PreAuth、非VISA、MASTERCARD 不支援
+                  . . .
+                  inNCCC_DCC_LocalBin_Check(pobTran-&gt;srBRec.szPAN):
+                        如果pobTran-&gt;srBRec.szPAN 已存在在DCCBin.dat檔案之中
+                  inNCCC_DCC_Func_Must_SETTLE:
+                        從HDT檔案取得包含DCC主機的那筆Record，且主機功能有開情況下，
+                        再透過那筆Record去loadHDPT，判斷是否要先結帳。
+      其餘情況設定</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszDCCTransBit = VS_TRUE</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_CurrencyOption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>上述Function會設定pobTran-&gt;srBRec.uszDCCTransBit，
+如果pobTran-&gt;srBRec.uszDCCTransBit == VS_TRUE:
+    設定</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+如果pobTran-&gt;srBRec.uszDCCTransBit == VS_FALSE:
+    do nothing</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">如果是DCC交易:
+    inFunc_Find_Specific_HDTindex:
+        如果DCC主機存在，取得index
+    pobTran-&gt;srBRec.inHDTIndex = inHDTIndex;
+    inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
+    inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);  
+    inFunc_Get_HDPT_General_Data:
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnBatchNum = atol(szBatchNum);
+       pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);   
+       pobTran-&gt;srBRec.lnOrgInvNum = atol(szInvoiceNum);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    pobTran-&gt;srBRec.inCode = _DCC_RATE_;
+    pobTran-&gt;inTransactionCode = _DCC_RATE_;
+    pobTran-&gt;inISOTxnCode = _DCC_RATE_;
+    inNCCC_DCC_SendPackRecvUnPack:
+        組_送_收_解ISO 電文
+    UnPack後會設定pobTran-&gt;srBRec.szDCC_AC值，進一步Action Code設定</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszDCCTransBit</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_OnlineRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Final_DCC_Option</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_ATS_Func_SetTxnOnlineOffline:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    pobTran-&gt;srBRec.uszOfflineBit = VS_FALSE; /* 當筆交易要 Online */
+    pobTran-&gt;srBRec.uszUpload1Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;srBRec.uszUpload2Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;srBRec.uszUpload3Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;uszReversalBit = VS_TRUE;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Beep_After_Auth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>利用TID運算出卡號的Transaction Number(交易編號)，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> strcpy(pobTran-&gt;srBRec.szTxnNo, szTxNo);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+因為原本註解就寫得很詳細，可直接閱讀這支程式</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_BDAU_DeleteAccumBatch</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -805,794 +1701,60 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>inFunc_DuplicateSave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_UpdateInvNum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新每個主機的資料庫欄位上，
+判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Receive_EI_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
-  </si>
-  <si>
-    <t>inNCCC_Func_Receive_EI_Flow</t>
-  </si>
-  <si>
-    <t>針對ECR發起的交易，且客製化會處理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>inNCCC_ESC_Func_Upload</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inNCCC_ATS_Func_BuildAndSendPacket:
-   inNCCC_ATS_GetSTAN:
-      取得STAN Number
-   處理online交易:
-      inNCCC_ATS_ProcessReversal:
-         inNCCC_ATS_ProcessReversal:
-            inNCCC_ATS_ReversalSave_Flow:
-               因為判斷撥接備援功能為OFF，所以不做事
-   inNCCC_ATS_ProcessOnline:
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inISOTxnCode = pobTran-&gt;inTransactionCode;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>inNCCC_ATS_SendPackRecvUnPack:
-      組 ISO 電文、傳送及接收 ISO 電文、解 ISO 電文
-   inNCCC_ATS_CheckRespCode:
-      依據回應碼返回交易結果</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inTransactionResult = _TRAN_RESULT_AUTHORIZED_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-   inNCCC_ATS_CheckAuthCode:
-      如果不是CUP交易且授權碼是空白或是"000000"情況:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">         pobTran-&gt;inErrorMsg = _ERROR_CODE_V3_AUTH_CODE_NOT_VALID_;
-         pobTran-&gt;inTransactionResult = _TRAN_RESULT_CANCELLED_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-      反之:
-           return VS_SUCCESS;
-   inNCCC_ATS_SetSTAN:
-      STAN Number 加一
-   inNCCC_ATS_AnalysePacket:
-      inNCCC_ATS_OnlineAnalyseEMV:
-         pobTran-&gt;inTransactionResult == _TRAN_RESULT_AUTHORIZED_情況:
-               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EMVGlobConfig.uszAction = d_ONLINE_ACTION_APPROVAL;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-               inFunc_SetEDCDateTime(pobTran-&gt;srBRec.szDate, pobTran-&gt;srBRec.szTime):
-                     要更新端末機的日期及時間</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">如果是DCC交易:
-    inFunc_Find_Specific_HDTindex:
-        如果DCC主機存在，取得index
-    pobTran-&gt;srBRec.inHDTIndex = inHDTIndex;
-    inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
-    inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);  
-    inFunc_Get_HDPT_General_Data:
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnBatchNum = atol(szBatchNum);
-       pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);   
-       pobTran-&gt;srBRec.lnOrgInvNum = atol(szInvoiceNum);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    pobTran-&gt;srBRec.inCode = _DCC_RATE_;
-    pobTran-&gt;inTransactionCode = _DCC_RATE_;
-    pobTran-&gt;inISOTxnCode = _DCC_RATE_;
-    inNCCC_DCC_SendPackRecvUnPack:
-        組_送_收_解ISO 電文
-    UnPack後會設定pobTran-&gt;srBRec.szDCC_AC值，進一步Action Code設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszDCCTransBit</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Final_DCC_Option</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>先檢查當筆交易如果是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-inDISP_Enter8x16_GetAmount:
-輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
-pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
-pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_StoreID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>檢查櫃號功能開啟，如果當筆交易為</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-未輸入櫃號情況下:
-inDISP_Enter8x16_Character_Mask:
-   輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
-   更新</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-如果已有櫃號:
- return;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>依據條件判斷功能是否關閉，如果有功能關閉，則return VS_ERROR;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(暫時沒看Code)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Get_OPT_PayItem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
-     inCTLS_SendReadyForSale_Internal:
-       EMVCL_InitTransactionEx(szACTData.bTagNum, szACTData.pbaTransactionData, szACTData.usTransactionDataLen):
-         初始化一筆交易，設定金額、日期、交易類型
-     顯示一般交易金額，偵測事件，包含刷卡、插卡、人工輸入卡號、感應方式
-     以感應卡為例:
-          內圈的WhileLoop:
-               inCTLS_ReceiveReadyForSales_Flow:
-                    ulCTLS_ReceiveReadyForSales_Internal:
-                          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>srCtlsObj.lnSaleRespCode = EMVCL_PerformTransactionEx(&amp;szRCDataEx):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                               透過EMVCL_PerformTransactionEx獲得 發起的交易結果(szRCDataEx)
-          外圈的WhileLoop:
-               偵測感應事件，執行
-                    ulCTLS_CheckResponseCode_SALE:
-                          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszContactlessBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                          inCTLS_UnPackReadyForSale_Flow:
-                              inCTLS_UnPackReadyForSale_Internal:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                             srCtlsObj.uszSchemeID[0] = SCHEME_ID_91_QUICKPASS;
-                                  pobTran-&gt;inTransactionCode = _CUP_SALE_;
-                                  pobTran-&gt;srBRec.inCode = pobTran-&gt;inTransactionCode;
-                                  pobTran-&gt;srBRec.inOrgCode = pobTran-&gt;inTransactionCode;
-                                  pobTran-&gt;srBRec.uszCUPTransBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inKMS_CheckKey:
-                                      這邊看起來是檢查KEY是否存在
-                                       inNCCC_Func_CUP_PowerOn_LogOn:
-                                            暫時沒看
-                                  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszWAVESchemeID = srCtlsObj.uszSchemeID[0];</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inFunc_BCD_to_ASCII(&amp;szASCII[0], &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len * 2);
-                                  szRCDataEx.bTrack2Len = szRCDataEx.bTrack2Len * 2;
-                                  memset(szRCDataEx.baTrack2Data, 0x00, sizeof(szRCDataEx.baTrack2Data));
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                             memcpy(&amp;szRCDataEx.baTrack2Data[0], &amp;szASCII[0], szRCDataEx.bTrack2Len);
-                             memcpy(pobTran-&gt;szTrack1, szRCDataEx.baTrack1Data, szRCDataEx.bTrack1Len);
-                             memcpy(pobTran-&gt;szTrack2, &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inCARD_unPackCard:
-                                       </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>取得PAN、ExpDate、szServiceCode 、CardHolder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inCTLS_ProcessChipData:
-                                       組電文的EMV Data ，這部分的tagID不清楚要參考哪個文件，需要詢問。
-                                  inCTLS_ExceptionCheck:
-                                        暫時沒看</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Check_Special_Card_In_OPT_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_CL_Power_Off</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呼叫CTOS_CLPowerOff()，關閉無線感應讀卡機的開關</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_CheckPAN_EXP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>螢幕顯示卡號與有效期供使用者確認</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Must_SETTLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Func_Must_SETTLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_GetAmount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Check_Amount_by_Card</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前此function只針對建設公司需求做客製化  ，暫時不看內部邏輯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_Check_Batch_limit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_GetStoreID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_GetProductCode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_MakeRefNo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>組szRRN:szRRN[0] = "9"，szRRN[1:5]取端末機代號[3~7] +szRRN[6:7] 取szlnBatchNum取兩數 + szRRN[8:10]取lnOrgInvNum取三數，並向右填滿空格，讓szRRN 長度固定12(序號 Ref. No.)
-組szAwardSN(優惠序號):端末機代號[0:7]+取得系統日期轉為西元年月日時分秒 取年月
-如果不是信託交易，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>strncpy(pobTran-&gt;srBRec.szRefNo, szRRN, sizeof(pobTran-&gt;srBRec.szRefNo))組簽單上的序號。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_ESC_Check</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可參考上述的inNCCC_Func_Check_Special_Card_In_OPT_Flow，
-因為在這邊已經檢查過，所以pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE，直接return;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_CheckSpecialCard_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_CHECK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">有輸入金額情況:
-    inNCCC_Func_CheckSpecialCard_Flow:
-        如果有啟動特殊卡別參數檔功能:
-            inNCCC_Func_CheckSpecialCard:
-                符合活動代碼情況:
-                     檢查出符合活動代碼的SCDTRec，進一步檢查卡號是否符合範圍、交易金額是否符合活動限額，活動日期是否在範圍內。
-        更新值:
-            </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
-          pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;
-          pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">        </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable);
-        inSqlite_Get_Table_ByRecordID_All(gszReprintDBPath, _TABLE_NAME_DUTY_FREE_FUNCTION_, 0, &amp;srAll);
-                因為srAll有link到inTableID、szEverRichSCDTEnable，後續會針對客製化+szEverRichSCDTEnable等條件判斷額外判斷_CAMPAIGNNUMBER_05_EVER_RICH_COMBO_檢查這個活動代碼。
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">看起來根據特定條件設定
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">pobTran-&gt;srBRec.inESCUploadMode = _ESC_STATUS_NOT_SUPPORTED_;
-pobTran-&gt;srBRec.inESCTransactionCode = pobTran-&gt;inTransactionCode;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>這邊有水位做一些判斷，不清楚是幹嘛的</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_CurrencyOption</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_OnlineRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">如果是ECR交易:
-    pobTran-&gt;uszDelaySendBit == VS_TRUE:
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;uszDelaySendBit = VS_FALSE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-        inECR_Send_Transaction_Result:
-            !pobTran-&gt;uszDelaySendBit:
-                inECR_Send_Transaction:
-                        組電文、發送電文</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inFunc_NCCC_PrintReceipt_ByBuffer_ESC:
-   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pobTran-&gt;srBRec.inPrintOption = _PRT_CUST_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    inCREDIT_PRINT_Receipt_ByBuffer:
-        inPrintIndex = _REPORT_INDEX_NORMAL_;
-                呼叫inPRINT_Buffer_PutGraphic() 、inPRINT_Buffer_PutIn()等function，
-                把Logo、TID/MID、簽單內容、金額資料等存到Buffer，
-                最後呼叫inPRINT_Buffer_OutPut，將Buffer中的資料印出</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_GetCardFields_CTLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inSIGN_TouchSignature_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>看起來是設定</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">pobTran-&gt;srBRec.inSignStatus </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新回資料庫，又或是開啟signPad觸控簽名功能</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1600,7 +1762,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1641,6 +1803,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="新細明體"/>
       <family val="1"/>
@@ -1965,7 +2135,7 @@
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="112.5" customWidth="1"/>
-    <col min="3" max="3" width="109.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="130.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2018,12 +2188,12 @@
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2033,497 +2203,500 @@
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="120" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="45" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C42" t="s">
-        <v>27</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="45" x14ac:dyDescent="0.3">
+      <c r="C42" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" ht="30" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="90" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C50" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" ht="60" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C54" s="1" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C58" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" ht="75" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" ht="195" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C66" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="225" x14ac:dyDescent="0.3">
+      <c r="C66" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" ht="30" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="75" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C70" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" ht="90" x14ac:dyDescent="0.3">
+      <c r="C70" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" ht="240" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="240" x14ac:dyDescent="0.3">
       <c r="C72" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C74" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="76" spans="2:3" ht="60" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" ht="90" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" ht="90" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C84" s="1" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C88" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C90" s="4" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C92" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" ht="45" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C94" s="1" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C96" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98" spans="2:3" ht="210" x14ac:dyDescent="0.3">
       <c r="C98" s="1" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C100" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C104" s="1" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C106" s="1" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C108" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C110" s="3" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -302,10 +302,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(暫時沒看Code)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Get_PayItem</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -339,15 +335,6 @@
       <t>);</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_SetTxnOnlineOffline_Flow</t>
-  </si>
-  <si>
-    <t>inNCCC_Func_BuildAndSendPacket_Flow</t>
-  </si>
-  <si>
-    <t>客製化為_CUSTOMER_INDICATOR_123_IKEA_或是_CUSTOMER_INDICATOR_124_EVER_RICH_ 加入提示音</t>
   </si>
   <si>
     <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
@@ -551,157 +538,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inFunc_PrintReceipt_ByBuffer_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>針對ECR發起的交易，且客製化會處理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inNCCC_ATS_Func_BuildAndSendPacket:
-   inNCCC_ATS_GetSTAN:
-      取得STAN Number
-   處理online交易:
-      inNCCC_ATS_ProcessReversal:
-         inNCCC_ATS_ProcessReversal:
-            inNCCC_ATS_ReversalSave_Flow:
-               因為判斷撥接備援功能為OFF，所以不做事
-   inNCCC_ATS_ProcessOnline:
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inISOTxnCode = pobTran-&gt;inTransactionCode;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>inNCCC_ATS_SendPackRecvUnPack:
-      組 ISO 電文、傳送及接收 ISO 電文、解 ISO 電文
-   inNCCC_ATS_CheckRespCode:
-      依據回應碼返回交易結果</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inTransactionResult = _TRAN_RESULT_AUTHORIZED_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-   inNCCC_ATS_CheckAuthCode:
-      如果不是CUP交易且授權碼是空白或是"000000"情況:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">         pobTran-&gt;inErrorMsg = _ERROR_CODE_V3_AUTH_CODE_NOT_VALID_;
-         pobTran-&gt;inTransactionResult = _TRAN_RESULT_CANCELLED_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-      反之:
-           return VS_SUCCESS;
-   inNCCC_ATS_SetSTAN:
-      STAN Number 加一
-   inNCCC_ATS_AnalysePacket:
-      inNCCC_ATS_OnlineAnalyseEMV:
-         pobTran-&gt;inTransactionResult == _TRAN_RESULT_AUTHORIZED_情況:
-               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EMVGlobConfig.uszAction = d_ONLINE_ACTION_APPROVAL;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-               inFunc_SetEDCDateTime(pobTran-&gt;srBRec.szDate, pobTran-&gt;srBRec.szTime):
-                     要更新端末機的日期及時間</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1204,10 +1045,6 @@
     <t xml:space="preserve">      </t>
   </si>
   <si>
-    <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">這支程式用於檢查 交易類型的交易功能參數是否都開啟
 如果pobTran-&gt;srBRec.uszDCCTransBit == VS_FALSE，
@@ -1409,11 +1246,6 @@
   </si>
   <si>
     <t>inNCCC_Func_CheckSpecialCard_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可參考上述的 inNCCC_Func_Check_Special_Card_In_OPT_Flow，
-因為在這邊已經檢查過，所以pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE，直接return;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1475,10 +1307,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_DCC_CurrencyOption</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>上述Function會設定pobTran-&gt;srBRec.uszDCCTransBit，
 如果pobTran-&gt;srBRec.uszDCCTransBit == VS_TRUE:
@@ -1508,96 +1336,6 @@
 如果pobTran-&gt;srBRec.uszDCCTransBit == VS_FALSE:
     do nothing</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">如果是DCC交易:
-    inFunc_Find_Specific_HDTindex:
-        如果DCC主機存在，取得index
-    pobTran-&gt;srBRec.inHDTIndex = inHDTIndex;
-    inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
-    inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);  
-    inFunc_Get_HDPT_General_Data:
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnBatchNum = atol(szBatchNum);
-       pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);   
-       pobTran-&gt;srBRec.lnOrgInvNum = atol(szInvoiceNum);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    pobTran-&gt;srBRec.inCode = _DCC_RATE_;
-    pobTran-&gt;inTransactionCode = _DCC_RATE_;
-    pobTran-&gt;inISOTxnCode = _DCC_RATE_;
-    inNCCC_DCC_SendPackRecvUnPack:
-        組_送_收_解ISO 電文
-    UnPack後會設定pobTran-&gt;srBRec.szDCC_AC值，進一步Action Code設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszDCCTransBit</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_OnlineRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Final_DCC_Option</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inNCCC_ATS_Func_SetTxnOnlineOffline:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">    pobTran-&gt;srBRec.uszOfflineBit = VS_FALSE; /* 當筆交易要 Online */
-    pobTran-&gt;srBRec.uszUpload1Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;srBRec.uszUpload2Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;srBRec.uszUpload3Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;uszReversalBit = VS_TRUE;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Beep_After_Auth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1709,52 +1447,589 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新每個主機的資料庫欄位上，
+    <t>inNCCC_Func_Receive_EI_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_ESC_Func_Upload</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inSIGN_TouchSignature_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>看起來是設定</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">pobTran-&gt;srBRec.inSignStatus </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新回資料庫，又或是開啟signPad觸控簽名功能</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_CurrencyOption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Final_DCC_Option</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_OnlineRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DCC詢價:
+如果是DCC交易(pobTran-&gt;srBRec.uszDCCTransBit == VS_TRUE):
+    inFunc_Find_Specific_HDTindex:
+        如果DCC主機存在，取得index
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inHDTIndex = inHDTIndex;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
+    inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);  
+    inFunc_Get_HDPT_General_Data:
+        inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">pobTran-&gt;srBRec.lnBatchNum = atol(szBatchNum);
+       pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);   
+       pobTran-&gt;srBRec.lnOrgInvNum = atol(szInvoiceNum);
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">inNCCC_DCC_GetSTAN(上述已經有取得過STANNUM，這邊再取一次不懂用意，因為沒看到有重新load HDPT的record):
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">inRetVal = inFLOW_RunFunction(pobTran, _COMM_START_):
+       通訊方式選擇ethernet。
+       從HDT_REC 取得通訊參數索引，然後load CPT record。
+       ethernet 設定ip、port等，然後做socket連線。
+       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">pobTran-&gt;uszConnectionBit = VS_TRUE;
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>這邊的交易類型只是暫時的，後面會設定回來，所以不歸類在return值
+       pobTran-&gt;srBRec.inCode = _DCC_RATE_;
+       pobTran-&gt;inTransactionCode = _DCC_RATE_;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      pobTran-&gt;inISOTxnCode = _DCC_RATE_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    inNCCC_DCC_SendPackRecvUnPack:
+        inNCCC_DCC_PackISO:
+          這邊看的是組tSam版本的電文程式，srNCCC_DCC_ISOFunc[index]存放所有要組送收解電文相關的function
+          inNCCC_DCC_GetBitMapMessagegTypeField03:
+             組MessageType、BitMap。
+             Bit Map做法:
+                是先取得電文需要的欄位list，
+                例如:int inNCCC_DCC_RATE[] = {3, 4, 11, 24, 35, 41, 42, 59, 60, 0}; /* 最後一組一定要放 0!! */
+                存一份list到inTxnBitMap，
+                srISOFunc-&gt;inModifyBitMap(pobTran, inTxnType, inTxnBitMap):
+                   依據一些條件，像是pobTran-&gt;inISOTxnCode條件，新增/刪除欄位到list中。
+                   最後把list的欄位組成真正的Bit Map的byte值。
+          把Bit Map中的欄位做pack。
+        ---電文的送和收都是使用socket方式---
+        inNCCC_DCC_CommSendRecvToHost:
+            vdNCCC_DCC_ISO_FormatDebug_DISP:
+                 可以從log上看到各個欄位pack的值。
+            inCOMM_Send:
+               inETHERNET_Send_Ready_Flow:
+                  inETHERNET_Send_Ready_Flow:
+                    這邊透過select方式達到非阻塞效果?
+               inETHERNET_Send_Data_Flow:
+                    真正執行socket send
+            inCOMM_Receive:
+                 inETHERNET_Receive_Ready_Flow:
+                      透過select判斷是否可接收資料
+                 inETHERNET_Receive_Data_Flow:
+                      執行socket recv
+                 從收到buffer取出長度比對收到的data是否全收到，如果不完全就重新接收資料。
+            vdNCCC_DCC_ISO_FormatDebug_DISP:
+                 可以從這邊vdNCCC_DCC_ISO_FormatDebug_DISP_59的log查看外幣相關資訊。
+        inNCCC_DCC_UnPackISO:
+                當上述執行完會有uszSendBuf和uszRecvBuf，檢查TPDU、MTI、各自的Bit Map是否相等，再檢查欄位39、41等。
+                會針對uszSendBuf和uszRecvBuf 同時有的欄位檢查值是否正確。
+                重點會在srISOFunc.srUnPackISO[inRecvField].inISOLoad(pobTran, &amp;uszRecvBuf[inRecvCnt])，
+                針對接收到的電文做unpack(可參考srNCCC_DCC_ISOFieldUnPack)，以下是unpack後更新的pobTran值。
+                        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inFunc_BCD_to_ASCII(&amp;pobTran-&gt;srBRec.szTime[0], &amp;uszUnPackBuf[0], 3);
+                    inFunc_BCD_to_ASCII(&amp;pobTran-&gt;srBRec.szDate[4], &amp;uszUnPackBuf[0], 2);
+                    memcpy(&amp;pobTran-&gt;srBRec.szAuthCode[0], (char *) &amp;uszUnPackBuf[0], _AUTH_CODE_SIZE_);
+                    memcpy(&amp;pobTran-&gt;srBRec.szRespCode[0], (char *)&amp;uszUnPackBuf[0], 2);
+                    pobTran-&gt;srBRec.szRespCode[2] = 0x00;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                        inNCCC_EMVUnPackData55(pobTran, &amp;uszUnPackBuf[2], inLen);(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>這部分沒看懂，byte&amp;0x1f00用意和為何可以這樣用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+                        因為unpack59要更新的值比較多，所以單獨寫出來。
+                        inNCCC_DCC_UnPack59:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_FCNFR[0], (char *)&amp;uszUnPackBuf[inCnt], 3);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_AC[0], (char *)&amp;uszUnPackBuf[inCnt], 4);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_FCN[0], (char *)&amp;uszUnPackBuf[inCnt], 3);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_FCA[0], (char *)&amp;uszUnPackBuf[inCnt], 12);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_FCMU[0], (char *)&amp;uszUnPackBuf[inCnt], 1);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_FCAC[0], (char *)&amp;uszUnPackBuf[inCnt], 3);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_ERMU[0], (char *)&amp;uszUnPackBuf[inCnt], 1);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_ERV[0], (char *)&amp;uszUnPackBuf[inCnt], 9);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_IRMU[0], (char *)&amp;uszUnPackBuf[inCnt], 1);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_IRV[0], (char *)&amp;uszUnPackBuf[inCnt], 9);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_IRDU[0], (char *)&amp;uszUnPackBuf[inCnt], 1);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_MPV[0], (char *)&amp;uszUnPackBuf[inCnt], 8);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_MPDP[0], (char *)&amp;uszUnPackBuf[inCnt], 1);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_CVCN[0], (char *)&amp;uszUnPackBuf[inCnt], 3);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_CVCA[0], (char *)&amp;uszUnPackBuf[inCnt], 12);
+                            memcpy(&amp;pobTran-&gt;srBRec.szDCC_CVCMU[0], (char *)&amp;uszUnPackBuf[inCnt], 1);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      判斷Action Code是8800，代表詢價成功，但會在呼叫inNCCC_DCC_OnlineRate_CheckF59_TableR，
+      檢查Field_59回覆Table "R"的資料是否有誤，如果資料有異常，
+      則端末機顯示【拒絕交易XI】不提示改由台幣支付。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strcpy(pobTran-&gt;srBRec.szRespCode, "XI");</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">因為已經在inNCCC_Func_Check_Special_Card_In_OPT_Flow(可直接參考這支)檢查過，
+所以pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE，直接return;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_PrintReceipt_ByBuffer_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">因為在DCC詢價接收電文並解電文會取得外幣相關資料，在這支程式會把資料顯示在端末機畫面上，
+顯示內容包含 1.外幣/2.台幣選項、轉換比率、轉換費率，並等待使用者選取選項外幣或是台幣，
+如果選擇台幣，會切換回NCCC主機，並呼叫inFunc_Get_HDPT_General_Data 取得Batch Number, STAN Number, Invoice Number。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnBatchNum = atol(szBatchNum);
+pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);
+pobTran-&gt;srBRec.lnOrgInvNum = atol(szInvoiceNum);
+pobTran-&gt;srBRec.uszNCCCDCCRateBit = VS_TRUE;
+pobTran-&gt;srBRec.uszDCCTransBit = VS_FALSE;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_Func_SetTxnOnlineOffline_Flow:
+依據TRT FileName 去跑function ID，目前只看inNCCC_DCC_Func_SetTxnOnlineOffline這支程式。
+inNCCC_DCC_Func_SetTxnOnlineOffline:
+    DCC不能離線授權，如果pobTran-&gt;srBRec.szAuthCode回Y1,return VS_ERROR;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    pobTran-&gt;srBRec.uszForceOnlineBit = VS_TRUE;
+    pobTran-&gt;srBRec.uszOfflineBit = VS_FALSE;
+    pobTran-&gt;srBRec.uszUpload1Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;srBRec.uszUpload2Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;srBRec.uszUpload3Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;uszReversalBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    如果交易類型是結帳，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;uszReversalBit = VS_FALSE;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_ATS_Func_BuildAndSendPacket:
+   inNCCC_ATS_GetSTAN:
+      取得STAN Number
+   處理online交易:
+      inNCCC_ATS_ProcessReversal:
+         inNCCC_ATS_ProcessReversal:
+            inNCCC_ATS_ReversalSave_Flow:
+               因為判斷撥接備援功能為OFF，所以不做事
+   inNCCC_ATS_ProcessOnline:
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inISOTxnCode = pobTran-&gt;inTransactionCode;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inNCCC_ATS_SendPackRecvUnPack:
+      組 ISO 電文、傳送及接收 ISO 電文、解 ISO 電文
+   inNCCC_ATS_CheckRespCode:
+      依據回應碼返回交易結果</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTransactionResult = _TRAN_RESULT_AUTHORIZED_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+   inNCCC_ATS_CheckAuthCode:
+      如果不是CUP交易且授權碼是空白或是"000000"情況:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">         pobTran-&gt;inErrorMsg = _ERROR_CODE_V3_AUTH_CODE_NOT_VALID_;
+         pobTran-&gt;inTransactionResult = _TRAN_RESULT_CANCELLED_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      反之:
+           return VS_SUCCESS;
+   inNCCC_ATS_SetSTAN:
+      STAN Number 加一
+   inNCCC_ATS_AnalysePacket:
+      inNCCC_ATS_OnlineAnalyseEMV:
+         pobTran-&gt;inTransactionResult == _TRAN_RESULT_AUTHORIZED_情況:
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EMVGlobConfig.uszAction = d_ONLINE_ACTION_APPROVAL;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+               inFunc_SetEDCDateTime(pobTran-&gt;srBRec.szDate, pobTran-&gt;srBRec.szTime):
+                     要更新端末機的日期及時間</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新到其他主機的調閱編號資料庫欄位上，
 判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Receive_EI_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_ESC_Func_Upload</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inSIGN_TouchSignature_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>看起來是設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">pobTran-&gt;srBRec.inSignStatus </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>更新回資料庫，又或是開啟signPad觸控簽名功能</t>
-    </r>
+    <t>inNCCC_Func_SetTxnOnlineOffline_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_BuildAndSendPacket_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Beep_After_Auth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客製化為_CUSTOMER_INDICATOR_123_IKEA_或是_CUSTOMER_INDICATOR_124_EVER_RICH_ ，主機回覆授權加入提示音</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2188,7 +2463,7 @@
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
@@ -2203,7 +2478,7 @@
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2253,17 +2528,17 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
@@ -2273,7 +2548,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="120" x14ac:dyDescent="0.3">
@@ -2283,42 +2558,42 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -2333,37 +2608,37 @@
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="90" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -2383,7 +2658,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
@@ -2393,27 +2668,27 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C54" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
@@ -2423,7 +2698,7 @@
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -2433,265 +2708,265 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="195" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" ht="30" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="225" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="75" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="2:4" ht="90" x14ac:dyDescent="0.3">
       <c r="C70" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" ht="240" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C72" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C74" s="3" t="s">
-        <v>30</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" ht="120" x14ac:dyDescent="0.3">
+      <c r="C74" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" ht="90" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" ht="165" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C84" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88" spans="2:3" ht="240" x14ac:dyDescent="0.3">
       <c r="C88" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C90" s="4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C92" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C94" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C96" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98" spans="2:3" ht="210" x14ac:dyDescent="0.3">
       <c r="C98" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C100" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C104" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="106" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C106" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C108" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C110" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="45" x14ac:dyDescent="0.3">

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
   <si>
     <t>inEVENT_Responder</t>
   </si>
@@ -75,25 +75,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inFunc_CheckTermStatus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>確認機器狀態，包括是否已下TMS參數和DCC參數(未仔細看過整支程式流程)</t>
-  </si>
-  <si>
     <t>inFunc_Idle_CheckCustomPassword_Flow</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_CheckCustomizePassword:
-先Load PWDRec，如果有開啟銷售密碼功能，取得該銷售密碼，
-後續inDISP_Enter8x16_Character_Mask輸入密碼，
-比對是不是銷售密碼，如果不是就一直輸入，直到輸入完成/超時/取消才結束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_Amount</t>
   </si>
   <si>
     <t>inNCCC_Func_Check_Is_Ticket_Purchase</t>
@@ -142,41 +125,6 @@
   <si>
     <t>如果客製化為_CUSTOMER_INDICATOR_126_MASTERCARD_FLIGHT_TICKET_，
 inNCCC_Func_Get_PDS0530_Other 請使用者輸入按鍵選擇 航班號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">已開啟列印產品代碼功能情況:
-  未輸入產品代號:
-    使用者輸入數字0~9比對PCDRec的szKeyMap(端末機對應之按鍵(Hot Key))，
-    找到對應的產品代碼及產品說明
-    memcpy(szDispMsg, pobTran-&gt;srBRec.szProductCode, 16);
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>inGetProductScript(pobTran-&gt;srBRec.szProductCode)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(取得產品代碼及產品說明)
-  已輸入產品代號:
-    return;</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -229,12 +177,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不可連續刷卡檢核有開啟情況:
-    檢查卡號和gszDuplicatePAN如果重複，顯示提示訊息。
-Note:gszDuplicatePAN值來自於 inFunc_DuplicateSave()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inModem_Predial</t>
   </si>
   <si>
@@ -337,15 +279,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>看起來是針對客製化_CUSTOMER_INDICATOR_042_BDAU1_或是_CUSTOMER_INDICATOR_043_BDAU9_ 要刪除Batch資料</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inACCUM_UpdateFlow</t>
   </si>
   <si>
     <r>
@@ -447,293 +382,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inECR_Send_Transaction_Result</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pobTran-&gt;uszDelaySendBit == VS_FALSE情況:
-    inECR_Send_Transaction:
-        印帳單前要送給ECR
-Note:pobTran-&gt;uszDelaySendBit == VS_FALSE可參考inNCCC_Func_Send_ECR_After_Print_Receipt()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_ESC_FuncProcess</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_CheckResult</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>inNCCC_Func_Check_NoSignature_Final:
-    針對客製化設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszNoSignatureBit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，
-    並更新回資料庫(inBATCH_Update_NoSignature_By_Sqlite)
-針對CUP交易，螢幕顯示交易完成、授權碼，使用者輸入Enter/逾時離開程式</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">開啟ESC功能情況:
-    pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
-    pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
-    inSqlite_Drop_Table_Flow:
-        Drop Table
-    inBATCH_Create_BatchTable_Flow:
-        Create Table
-    inBATCH_Insert_All_Flow:
-        Insert Into Table
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">    pobTran-&gt;uszFileNameNoNeedHostBit = VS_FALSE;
-    pobTran-&gt;uszFileNameNoNeedNumBit = VS_FALSE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Note:每次對Table做操作，都會先開啟
-pobTran-&gt;uszFileNameNoNeedHostBit、pobTran-&gt;uszFileNameNoNeedNumBit的BitOn，
-主要用在取檔名，結束操作會關閉這兩個Bit</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>針對ECR發起的交易，且客製化會處理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_StoreID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(暫時沒看Code)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
-     inCTLS_SendReadyForSale_Internal:
-       EMVCL_InitTransactionEx(szACTData.bTagNum, szACTData.pbaTransactionData, szACTData.usTransactionDataLen):
-         初始化一筆交易，設定金額、日期、交易類型
-     顯示一般交易金額，偵測事件，包含刷卡、插卡、人工輸入卡號、感應方式
-     以感應卡為例:
-          內圈的WhileLoop:
-               inCTLS_ReceiveReadyForSales_Flow:
-                    ulCTLS_ReceiveReadyForSales_Internal:
-                          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>srCtlsObj.lnSaleRespCode = EMVCL_PerformTransactionEx(&amp;szRCDataEx):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                               透過EMVCL_PerformTransactionEx獲得 發起的交易結果(szRCDataEx)
-          外圈的WhileLoop:
-               偵測感應事件，執行
-                    ulCTLS_CheckResponseCode_SALE:
-                          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszContactlessBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                          inCTLS_UnPackReadyForSale_Flow:
-                              inCTLS_UnPackReadyForSale_Internal:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                             srCtlsObj.uszSchemeID[0] = SCHEME_ID_91_QUICKPASS;
-                                  pobTran-&gt;inTransactionCode = _CUP_SALE_;
-                                  pobTran-&gt;srBRec.inCode = pobTran-&gt;inTransactionCode;
-                                  pobTran-&gt;srBRec.inOrgCode = pobTran-&gt;inTransactionCode;
-                                  pobTran-&gt;srBRec.uszCUPTransBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inKMS_CheckKey:
-                                      這邊看起來是檢查KEY是否存在
-                                       inNCCC_Func_CUP_PowerOn_LogOn:
-                                            暫時沒看
-                                  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszWAVESchemeID = srCtlsObj.uszSchemeID[0];</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inFunc_BCD_to_ASCII(&amp;szASCII[0], &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len * 2);
-                                  szRCDataEx.bTrack2Len = szRCDataEx.bTrack2Len * 2;
-                                  memset(szRCDataEx.baTrack2Data, 0x00, sizeof(szRCDataEx.baTrack2Data));
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                             memcpy(&amp;szRCDataEx.baTrack2Data[0], &amp;szASCII[0], szRCDataEx.bTrack2Len);
-                             memcpy(pobTran-&gt;szTrack1, szRCDataEx.baTrack1Data, szRCDataEx.bTrack1Len);
-                             memcpy(pobTran-&gt;szTrack2, &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inCARD_unPackCard:
-                                       </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>取得PAN、ExpDate、szServiceCode 、CardHolder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inCTLS_ProcessChipData:
-                                       組電文的EMV Data ，這部分的tagID不清楚要參考哪個文件，需要詢問。
-                                  inCTLS_ExceptionCheck:
-                                        暫時沒看</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Check_Special_Card_In_OPT_Flow</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -751,80 +399,6 @@
   </si>
   <si>
     <t>inCREDIT_Func_GetProductCode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">有輸入金額情況:
-    inNCCC_Func_CheckSpecialCard_Flow:
-        如果有啟動特殊卡別參數檔功能:
-            inNCCC_Func_CheckSpecialCard:
-                符合活動代碼情況:
-                     檢查出符合活動代碼的SCDTRec，進一步檢查卡號是否符合範圍、交易金額是否符合活動限額，活動日期是否在範圍內。
-        更新值:
-            </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
-          pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;
-          pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">        </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable);
-        inSqlite_Get_Table_ByRecordID_All(gszReprintDBPath, _TABLE_NAME_DUTY_FREE_FUNCTION_, 0, &amp;srAll);
-                因為srAll有link到inTableID、szEverRichSCDTEnable，後續會針對客製化+szEverRichSCDTEnable等條件判斷額外判斷_CAMPAIGNNUMBER_05_EVER_RICH_COMBO_檢查這個活動代碼。
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE;</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -862,183 +436,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">inFunc_NCCC_PrintReceipt_ByBuffer_ESC:
-   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pobTran-&gt;srBRec.inPrintOption = _PRT_CUST_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    inCREDIT_PRINT_Receipt_ByBuffer:
-        inPrintIndex = _REPORT_INDEX_NORMAL_;
-                呼叫inPRINT_Buffer_PutGraphic() 、inPRINT_Buffer_PutIn()等function，
-                把Logo、TID/MID、簽單內容、金額資料等存到Buffer，
-                最後呼叫inPRINT_Buffer_OutPut，將Buffer中的資料印出</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>先檢查當筆交易如果是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-inDISP_Enter8x16_GetAmount:
-輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
-pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
-pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>如果客製化為_CUSTOMER_INDICATOR_126_MASTERCARD_FLIGHT_TICKET_，
 請使用者輸入數字(是按[1]，否按[2])是否為機票交易</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>檢查櫃號功能開啟，如果當筆交易為</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-未輸入櫃號情況下:
-inDISP_Enter8x16_Character_Mask:
-   輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
-   更新</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">，
-   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>並且剩餘長度用空白補齊。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-如果已有櫃號:
- return;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Get_OPT_PayItem</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inFunc_GetCardFields_CTLS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_CL_Power_Off</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_CheckPAN_EXP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Must_SETTLE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1082,33 +489,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_DCC_Func_Must_SETTLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Check_Transaction_Function:
      只檢查NCCC的交易功能參數，且已知NCCC主機的索引為第一筆，所以inLoadHDTRec(0)，
      最後判斷特定交易類型的交易功能參數是否有On起來。
 inNCCC_Func_Check_Transaction_Function_Award:
      一樣是判斷特定交易類型的功能是否有On起來。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_Find_Specific_HDTindex取得NCCC的主機index，inLoadHDPTRec(index)使用sql方式更新HDPT_REC，
-inGetMustSettleBit取得HDPT_REC的szMustSettleBit是否結帳的flag，當szMustSettleBit為Y表示要結帳，
-組好DISPLAY_OBJECT，秀在LCD上。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_GetDCC_Enable:
-   主要找符合DCC主機的HDT_REC，並檢查主機功能是否開啟。
-inLoadHDPTRec:
-   inLoadHDPTRec(inDCC_HostIndex)，inGetMustSettleBit取得HDPT_REC的szMustSettleBit是否結帳的flag，當szMustSettleBit為Y表示要結帳，
-組好DISPLAY_OBJECT，秀在LCD上。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_GetAmount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1211,37 +596,6 @@
   </si>
   <si>
     <t>inNCCC_ESC_Check</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">看起來根據特定條件設定
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">pobTran-&gt;srBRec.inESCUploadMode = _ESC_STATUS_SUPPORTED_;
-pobTran-&gt;srBRec.inESCTransactionCode = pobTran-&gt;inTransactionCode;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>這邊有判斷水位，不確定用意為何?</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1308,38 +662,6 @@
   </si>
   <si>
     <r>
-      <t>上述Function會設定pobTran-&gt;srBRec.uszDCCTransBit，
-如果pobTran-&gt;srBRec.uszDCCTransBit == VS_TRUE:
-    設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-如果pobTran-&gt;srBRec.uszDCCTransBit == VS_FALSE:
-    do nothing</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>利用TID運算出卡號的Transaction Number(交易編號)，</t>
     </r>
     <r>
@@ -1368,138 +690,117 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_BDAU_DeleteAccumBatch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>inBATCH_Create_BatchTable_Flow:
-    inTableType 等於_TN_BATCH_TABLE_或是_TN_EMV_TABLE_執行不同SQLite Create Table Function，
-    再依據SQLITE_TAG_TABLE，裡面包含欄位名、型別、屬性1、屬性2，組合Sql語句，建立Table，
-    建立Batch Table和Emv Table。
-inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_):
-    這邊是Insert  srBRec資料到Table
-    inSqlite_Table_Link_BRec:
-        inSqlite_Table_Link:
-            先把srLink的Table mapping到srALL
-    inSqlite_Insert_Record:
-        inSqlite_Calculate_Insert_SQLLength:
-            先計算產生的Sql語句的長度，才能動態配置記憶體空間
-    inSqlite_Gernerate_InsertSQL:
-        組合最終的Sql，Insert into ...values(?,?...)，這邊注意到VALUES裡面是放入問號
-    inSqlite_Binding_Values:
-        上述提到的問號，會透過index方式把參數值綁定回去
-    sqlite3_step(srSQLStat):
-        真正執行Sql動作
-inSqlite_Get_Max_TableID_Flow:
-    取得最大的TableID，更新</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inTableID = atoi(szTableID)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-如果有【EMV】和【Contactless】交易:
-    inBATCH_Insert_All_Flow(pobTran, _TN_EMV_TABLE_):
-        這邊是Insert  srEMVRec資料到Table，可直接參考上述
-inFunc_Save_Last_Txn_Host:
-    inFile_Linux_Delete_In_Fs_Data
-        inFile_Unlink_File:
-            inRetVal = unlink( ./fs_data/LAST_TXN_HOST.txt );
-inFile_Linux_Create_In_Fs_Data:
-    inFile_Linux_Create:
-        open file，取得Fd
-inFunc_Data_Chmod:
-    新增檔案權限為744
-檔案指針指向開頭，寫入pobTran-&gt;srBRec.inHDTIndex資料到檔案
-inFunc_Load_Last_UniqueNo:
-    流程跟上述一樣，差別在刪除和建立的檔名不同，寫入的資料不同，這邊寫入的資料是pobTran-&gt;szUniqueNo
-Note:
-    unlink 會 從檔案系統中刪除檔名。
-    如果檔案之前有任何 開啟的檔案描述字（fd），即使呼叫了 unlink，程式仍然可以透過這些 fd 讀寫檔案。
-    只有當 所有 fd 都關閉 且檔名已被刪除後，檔案的內容才會被系統釋放，檔案才算真正被刪除。 
+    <t>inFunc_DuplicateSave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_UpdateInvNum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">因為已經在inNCCC_Func_Check_Special_Card_In_OPT_Flow(可直接參考這支)檢查過，
+所以pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE，直接return;
 </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_DuplicateSave</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_UpdateInvNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Receive_EI_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_ESC_Func_Upload</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inSIGN_TouchSignature_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>看起來是設定</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">pobTran-&gt;srBRec.inSignStatus </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>更新回資料庫，又或是開啟signPad觸控簽名功能</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_CurrencyOption</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Func_CheckTransactionFunction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">因為在DCC詢價接收電文並解電文會取得外幣相關資料，在這支程式會把資料顯示在端末機畫面上，
+顯示內容包含 1.外幣/2.台幣選項、轉換比率、轉換費率，並等待使用者選取選項外幣或是台幣，
+如果選擇台幣，會切換回NCCC主機，並呼叫inFunc_Get_HDPT_General_Data 取得Batch Number, STAN Number, Invoice Number。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnBatchNum = atol(szBatchNum);
+pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);
+pobTran-&gt;srBRec.lnOrgInvNum = atol(szInvoiceNum);
+pobTran-&gt;srBRec.uszNCCCDCCRateBit = VS_TRUE;
+pobTran-&gt;srBRec.uszDCCTransBit = VS_FALSE;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_Func_SetTxnOnlineOffline_Flow:
+依據TRT FileName 去跑function ID，目前只看inNCCC_DCC_Func_SetTxnOnlineOffline這支程式。
+inNCCC_DCC_Func_SetTxnOnlineOffline:
+    DCC不能離線授權，如果pobTran-&gt;srBRec.szAuthCode回Y1,return VS_ERROR;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    pobTran-&gt;srBRec.uszForceOnlineBit = VS_TRUE;
+    pobTran-&gt;srBRec.uszOfflineBit = VS_FALSE;
+    pobTran-&gt;srBRec.uszUpload1Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;srBRec.uszUpload2Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;srBRec.uszUpload3Bit = VS_FALSE; /* 不會產生任何 Advice */
+    pobTran-&gt;uszReversalBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    如果交易類型是結帳，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;uszReversalBit = VS_FALSE;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新到其他主機的調閱編號資料庫欄位上，
+判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Beep_After_Auth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客製化為_CUSTOMER_INDICATOR_123_IKEA_或是_CUSTOMER_INDICATOR_124_EVER_RICH_ ，主機回覆授權加入提示音</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>inNCCC_DCC_Final_DCC_Option</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_SetTxnOnlineOffline_Flow</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1785,9 +1086,1062 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">因為已經在inNCCC_Func_Check_Special_Card_In_OPT_Flow(可直接參考這支)檢查過，
-所以pobTran-&gt;uszCheck_OPT_Special_CardBit = VS_TRUE，直接return;
+    <t>inNCCC_Func_BDAU_DeleteAccumBatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_BuildAndSendPacket_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_BuildAndSendPacket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inFunc_Find_Specific_HDTindex 取得DCC主機的INDEX
 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inHDTIndex = inHDTIndex;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
+inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);
+inNCCC_DCC_GetSTAN:
+   szSTANNum為srHDPTRec.szSTANNum
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果是ONLINE交易(pobTran-&gt;srBRec.uszOfflineBit == VS_FALSE):
+    inNCCC_DCC_ProcessReversal:
+        如果srHDPTRec.szSendReversalBit為Y 要先把上筆reversal送出並產生當筆reversal。
+        流程為:
+            先判斷srHDPTRec.szSendReversalBit為Y會取得.rev檔案，讀出上筆reversal電文，
+            可參考 inNCCC_DCC_ReversalSave，
+            接著送 收 解電文，檢查回應碼為00，設定srHDPTRec.szSendReversalBit為N，
+            並更新值回資料庫，最後再把.rev檔案刪除。
+        inNCCC_DCC_SetReversalCnt:
+            HDPT檔案的reversal count +1 ，並更新回資料庫。
+        如果是pobTran-&gt;uszReversalBit == VS_TRUE:
+           inNCCC_DCC_ReversalSave_Flow:   
+                inNCCC_DCC_ReversalSave:
+                     pobTran-&gt;inISOTxnCode = _REVERSAL_; /* 沖銷 */
+                     先取得index知道要讀哪個function table(srNCCC_DCC_ISOFunc[inISOFuncIndex])，
+                     取得該table的reversal的所需電文欄位和message type，
+                     uszSendBuf根據電文欄位組bit map。
+                     呼叫reversal電文欄位的pack function去組出電文。
+                     透過inFunc_ComposeFileName 取得檔名(DCC + Batch Num +.rev)，
+                     呼叫inFILE_Delete 刪除舊檔案，inFILE_Create產生新檔案，
+                     inFILE_Seek指向檔案開頭把組好的電文寫進檔案中，
+                     並設定srHDPTRec.szSendReversalBit 為Y，
+                     最後呼叫inSaveHDPTRec_SQLite更新整筆srHDPTRec。
+        如果Dial_Up_Backup_Enable ==Y :
+            inNCCC_DCC_ReversalSave_For_DialBeckUp:
+                跟inNCCC_DCC_ReversalSave一樣的做法，唯一差別在於取得的檔案名稱不同。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">如果是ONLINE交易(pobTran-&gt;srBRec.uszOfflineBit == VS_FALSE):
+    inNCCC_DCC_ProcessOnline:
+      inNCCC_DCC_SendPackRecvUnPack: 
+          開始組SALE封包，送、收、組、解
+      inNCCC_DCC_CheckRespCode:
+          如果response code = 00 or 11，
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTransactionResult = _TRAN_RESULT_AUTHORIZED_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      inNCCC_DCC_CheckAuthCode:
+          如果授權碼是pobTran-&gt;srBRec.szAuthCode是"000000"或是"      " ，拒絕交易。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inErrorMsg = _ERROR_CODE_V3_AUTH_CODE_NOT_VALID_;
+        pobTran-&gt;inTransactionResult = _TRAN_RESULT_CANCELLED_;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_SetSTAN:
+    STAN Number +1並更新回資料庫。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_DCC_AnalysePacket:
+    srNCCC_DCC_ISOFunc[inISOFuncIndex].inNCCC_DCC_ISOOnlineAnalyse:
+        inNCCC_DCC_OnlineAnalyseMagneticManual:
+             如果交易結果是_TRAN_RESULT_AUTHORIZED_:
+                  inNCCC_DCC_SyncHostTerminalDateTime 原先要更新端末機的日期及時間，
+                  但DCC交易不做。
+                  設定srHDPTRec.szSendReversalBit 為N，inSaveHDPTRec更新資料庫 
+                  inNCCC_DCC_AdviceSendRecvPacket:
+                       inBATCH_AdviceHandleReadOnly_By_Sqlite:
+                           inFunc_ComposeFileName 取得 DC + STAN NUM + .adv，確認檔案是否存在
+                        如果檔案存在:
+                            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>暫時未看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                       如果檔案不存在:
+                            inNCCC_DCC_Advice_ESC_SendRecvPacket:
+                                 inBATCH_Advice_ESC_HandleReadOnly_Flow:
+                                      do nothing
+                                 inBATCH_GetAdvice_ESC_DetailRecord_Flow:
+                                      inBATCH_GetAdvice_ESC_DetailRecord_By_Sqlite:
+                                           inSqlite_ESC_Get_BRec_Top_Flow:
+                                                    這邊會取得檔案名稱，然後抓這個檔案的table，
+                                                    inTableID最小的資料出來。
+                                                    inNCCC_DCC_SendPackRecvUnPack:
+                                                         電文的組、送、收、解。
+                                                    如果inNCCC_DCC_SendPackRecvUnPack回傳VS_SUCCESS:
+                                                         inNCCC_DCC_CheckRespCode:
+                                                              檢查授權碼為00，
+                                                              inRetVal = _TRAN_RESULT_AUTHORIZED_;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                                              pobTran-&gt;inErrorMsg = _ERROR_CODE_V3_NONE_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                                              inADVICE_ESC_DeleteRecordFlow:
+                                                                   inADVICE_ESC_DeleteRecord_By_Sqlite:
+                                                                       inSqlite_ESC_Delete_Record_Flow:
+                                                                             刪除檔案TABLE，
+                                                                             inTableID最小的那筆資料。
+                                 inBATCH_GlobalAdvice_ESC_HandleClose_Flow:
+                                      inBATCH_GlobalAdvice_ESC_HandleClose_By_Sqlite:
+                                            do nothing</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
+     inCTLS_SendReadyForSale_Internal:
+       EMVCL_InitTransactionEx(szACTData.bTagNum, szACTData.pbaTransactionData, szACTData.usTransactionDataLen):
+         初始化一筆交易，設定金額、日期、交易類型
+     顯示一般交易金額，偵測事件，包含刷卡、插卡、人工輸入卡號、感應方式
+     以感應卡為例:
+          內圈的WhileLoop:
+               inCTLS_ReceiveReadyForSales_Flow:
+                    ulCTLS_ReceiveReadyForSales_Internal:
+                          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>srCtlsObj.lnSaleRespCode = EMVCL_PerformTransactionEx(&amp;szRCDataEx):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                               透過EMVCL_PerformTransactionEx獲得 發起的交易結果(szRCDataEx)
+          外圈的WhileLoop:
+               偵測感應事件，執行
+                    ulCTLS_CheckResponseCode_SALE:
+                          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszContactlessBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                          inCTLS_UnPackReadyForSale_Flow:
+                              inCTLS_UnPackReadyForSale_Internal:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                             srCtlsObj.uszSchemeID[0] = SCHEME_ID_91_QUICKPASS;
+                                  pobTran-&gt;inTransactionCode = _CUP_SALE_;
+                                  pobTran-&gt;srBRec.inCode = pobTran-&gt;inTransactionCode;
+                                  pobTran-&gt;srBRec.inOrgCode = pobTran-&gt;inTransactionCode;
+                                  pobTran-&gt;srBRec.uszCUPTransBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inKMS_CheckKey:
+                                      這邊看起來是檢查KEY是否存在
+                                       inNCCC_Func_CUP_PowerOn_LogOn:
+                                            暫時沒看
+                                  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszWAVESchemeID = srCtlsObj.uszSchemeID[0];</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inFunc_BCD_to_ASCII(&amp;szASCII[0], &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len * 2);
+                                  szRCDataEx.bTrack2Len = szRCDataEx.bTrack2Len * 2;
+                                  memset(szRCDataEx.baTrack2Data, 0x00, sizeof(szRCDataEx.baTrack2Data));
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                             memcpy(&amp;szRCDataEx.baTrack2Data[0], &amp;szASCII[0], szRCDataEx.bTrack2Len);
+                             memcpy(pobTran-&gt;szTrack1, szRCDataEx.baTrack1Data, szRCDataEx.bTrack1Len);
+                             memcpy(pobTran-&gt;szTrack2, &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inCARD_unPackCard:
+                                       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>取得PAN、ExpDate、szServiceCode 、CardHolder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                  inCTLS_ProcessChipData:
+                                       組電文的EMV Data ，這部分的tagID不清楚要參考哪個文件，需要詢問。
+                                  inCTLS_ExceptionCheck:
+                                        暫時沒看</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Receive_EI_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>針對ECR發起的交易，且為客製化才會做後續邏輯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_ESC_Func_Upload</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inFunc_NCCC_PrintReceipt_ByBuffer_ESC:
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pobTran-&gt;srBRec.inPrintOption = _PRT_CUST_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    inCREDIT_PRINT_Receipt_ByBuffer:
+        inPrintIndex = _REPORT_INDEX_NORMAL_;
+                呼叫inPRINT_Buffer_PutGraphic() 、inPRINT_Buffer_PutIn()等function，
+                把Logo、TID/MID、簽單內容、金額資料等存到Buffer，
+                最後呼叫inPRINT_Buffer_OutPut，將Buffer中的資料印出</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
+pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
+inSqlite_ESC_Delete_Record_Flow:
+    因為設定uszFileNameNoNeedHostBit和uszFileNameNoNeedNumBit 為true，所以取得的檔名為ALL + _ESCTEMP，
+    inSqlite_ESC_Delete_Record:
+         刪除這個ALL_ESCTEMP這個TABLE中，inTableID最小的資料。
+pobTran-&gt;uszFileNameNoNeedHostBit = VS_FALSE;
+pobTran-&gt;uszFileNameNoNeedNumBit = VS_FALSE;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_ESC_Func_Upload:
+   inNCCC_ESC_ProcessOnline:
+       inNCCC_ESC_Make_E1Data:
+           inNCCC_ESC_Open_File:
+              針對 ESC_E1.txt，先刪除既有檔案，並重新建立新檔案。
+           取得inPrintIndex = 1(DCC 簽單 For Sale)，呼叫srESCReceiptType[inPrintIndex]取得簽單內容存到buffer中，
+           再呼叫inNCCC_ESC_Append_E1 把buffer內容轉成big5，寫入ESC_E1.txt檔案中。
+       inNCCC_ESC_Data_Compress_Encryption:
+           inNCCC_tSAM_Decide_tSAM_Slot:
+               抓tSAM Slot
+           刪除檔案ESC_E1_E.txt.gz、ESC_E2_E.bmp.gz。
+           inFunc_Data_GZip:
+               組字串gzip  ./fs_data/ESC_E1.txt，執行這行command。
+           inNCCC_TMK_Write_ESCKey:
+               組Encryption Key(szKeyFull) = Key1 + Key2 + Key1，設定CTOS_KMS2KEYWRITE_PARA srKeyWritePara結構體，
+               inKMS_Write(&amp;srKeyWritePara)，流程是這樣，但這個結構體和inKMS_Write用意並不清楚。
+           開啟ESC_E1.txt.gz檔案，從檔案開頭讀出32個字元(szRawData32)，inNCCC_tSAM_Encrypt針對szRawData32的17~32個字元做加密，
+           取得加密後16 Bytes並塞回去並重新寫入檔案開頭中，並把ESC_E1.txt.gz改名為ESC_E1_E.txt.gz
+           inFunc_ComposeFileName_InvoiceNumber:
+               取得主機名稱+調閱編號+ .bmp，例如DC000009.bmp
+           inFILE_Check_Exist:
+               檢查檔案是否存在
+           inFunc_Data_Copy:
+               組字串cp ./fs_data/DC000009.bmp ./fs_data/ESC_BMP_BACKUP.bmp，執行command。
+           inFunc_Data_GZip:
+               組字串gzip  ./fs_data/DC000009.bmp，執行command。
+           inFunc_Data_Rename:
+               組字串mv ./fs_data/ESC_BMP_BACKUP.bmp ./fs_data/DC000009.bmp，執行command。
+           inFILE_Rename:
+               DC000009.bmp.gz改名為ESC_E2.bmp.gz
+           開啟ESC_E2.bmp.gz檔案，從檔案開頭讀出32個字元(szRawData32)，inNCCC_tSAM_Encrypt針對szRawData32的17~32個字元做加密，
+           取得加密後16 Bytes並塞回去並重新寫入檔案開頭中，並把ESC_E2.bmp.gz改名為ESC_E2_E.bmp.gz
+           inNCCC_ESC_Data_Packet:
+               讀取ESC_E1_E.txt.gz和ESC_E2_E.bmp.gz資料存到EscData ESC_UPLOAD_DATA[_ESC_LIMIT_]，包含
+               //表示E1/E2
+               ESC_UPLOAD_DATA[ginEscDataIndex].inTableIndex = inTableIndex;
+               //總封包數
+               ESC_UPLOAD_DATA[ginEscDataIndex].inTotalPacketCnt = inTotalCnt;
+               //第幾個封包
+               ESC_UPLOAD_DATA[ginEscDataIndex].inPacketCnt = i;
+               //總封包大小
+               ESC_UPLOAD_DATA[ginEscDataIndex].lnTotalPacketSize = lnFileSize;
+           while迴圈 根據ESC_UPLOAD_DATA[ginEscDataIndex].inTableIndex是E1/E2，開始組 電簽上傳 的電文，欄位F_11會是STAN NUM遞增，
+           欄位F_59則會使用ESC_UPLOAD_DATA[ginEscDataIndex]的內容，接著做送、收、解電文。
+           inFILE_Delete:
+               刪除ESC_E1_E.txt.gz和ESC_E2_E.bmp.gz檔案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>如果inNCCC_ESC_ProcessOnline return VS_SUCCESS:
+    inACCUM_UpdateFlow_ESC:
+        inFunc_ComposeFileName:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+              </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">取得檔名hostName + batch num + .amt，例如:DC000004.amt
+        開啟DC000004.amt檔案，如果不存在就建立檔案，並指向檔案開頭，讀取ACCUM_TOTAL_REC srAccumRec的資料，
+        inACCUM_Update_ESC_TotalAmount:
+                srAccumRec-&gt;lnESC_SuccessNum ++;
+                srAccumRec-&gt;llESC_SuccessAmount += pobTran-&gt;srBRec.lnTxnAmount;
+         inACCUM_StoreRecord:
+                 一樣開啟檔案，指向檔案開頭，把ACCUM_TOTAL_REC srAccumRec 資料寫入檔案。
+         inBATCH_GetTransRecord_By_Sqlite:
+                 inBATCH_Get_Batch_ByInvNum_Flow:
+                        更新pobTran-&gt;srBRec資料
+                 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnOrgSTANNum = pobTran-&gt;srBRec.lnSTANNum;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">       pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_UPLOADED_;
+       pobTran-&gt;srBRec.uszESCOrgUploadBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         inBATCH_Update_ESC_Uploaded_By_Sqlite:
+             inBATCH_FuncUpdateTxnRecord_By_Sqlite:
+                  pobTran-&gt;uszUpdateBatchBit == VS_TRUE:
+                      inSqlite_Check_Table_Exist_Flow:
+                            確認Table是否存在。
+                      inSqlite_Update_ByInvNum_TranState_Flow:
+                         inSqlite_Update_ByInvNum_TranState:
+                               取得table name是主機名稱 +調閱編號
+                               更新table的uszUpdated 的狀態為1
+                  inBATCH_Insert_All_Flow:
+                        insert into 當前的pobtran的srBRec到資料庫。
+                  inSqlite_Get_Max_TableID_Flow:
+                        抓出最大筆的TableID，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                 inFunc_Save_Last_Txn_Host:
+                       刪除既有的LAST_TXN_HOST.txt檔案，新增檔案，設定檔案權限為744
+                       開啟檔案，寫入pobTran-&gt;srBRec.inHDTIndex到檔案裡。
+         inFunc_Save_Last_UniqueNo:
+             不是ECR發動，return VS_SUCCESS;
+     inFunc_ComposeFileName_InvoiceNumber:
+         取得主機名稱 + 調閱編號+.bmp
+     inFILE_Delete:
+          刪除檔案。
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inECR_Send_Transaction_Result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inECR_Send_Transaction_Result:
+   pobTran-&gt;uszECRBit != VS_TRUE:
+       不是ECR連線就跳走，return (VS_SUCCESS);
+   !pobTran-&gt;uszDelaySendBit:
+       不等待簽單列印完成，立即回傳 ECR 結果，
+         inECR_Send_Transaction:
+                inRS232_ECR_Send_Transaction_Result:
+                    組ECR電文、傳送出去。
+                   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> srECROb-&gt;srTransData.uszIsResponse = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">       pobTran-&gt;srBRec.uszMPASReprintBit = VS_FALSE;
+       pobTran-&gt;srTRec.uszMPASReprintBit = VS_FALSE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         /* 把不能重印的結果存回Batch */
+         inBATCH_Update_MPAS_Reprint_By_Sqlite:
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;uszUpdateBatchBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            inBATCH_FuncUpdateTxnRecord_By_Sqlite:
+                   pobTran-&gt;uszUpdateBatchBit == VS_TRUE:
+                            inSqlite_Check_Table_Exist_Flow:
+                                     inFunc_ComposeFileName:
+                                          組table name。
+                                     inSqlite_Check_Table_Exist:
+                                          sql語句判斷table是否存在。
+                            inSqlite_Update_ByInvNum_TranState_Flow:
+                                     inFunc_ComposeFileName:
+                                          一樣組table name。
+                                     inSqlite_Update_ByInvNum_TranState:
+                                          更新table 的uszUpdated 為1。
+                   inBATCH_Insert_All_Flow:
+                         把目前pobTran-&gt;srBRec的資料寫入table裡
+                   inSqlite_Get_Max_TableID_Flow:
+                         inSqlite_Get_Max_TableID:
+                             找出最大一筆的TableID。
+                   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inBATCH_Insert_All_Flow(pobTran, _TN_EMV_TABLE_):
+                         一樣先組table name(主機名稱+Batch num +_EMV)，insert into一筆pobTran-&gt;srEMVRec到table。
+Note:  pobTran-&gt;uszDelaySendBit == VS_FALSE可參考inNCCC_Func_Send_ECR_After_Print_Receipt()</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>inBATCH_Create_BatchTable_Flow:
+    inTableType 等於_TN_BATCH_TABLE_或是_TN_EMV_TABLE_執行不同SQLite Create Table Function，
+    再依據SQLITE_TAG_TABLE，裡面包含欄位名、型別、屬性1、屬性2，組合Sql語句，建立Table，
+    建立Batch Table和Emv Table。
+inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_):
+    這邊是Insert  srBRec資料到Table
+    inSqlite_Table_Link_BRec:
+        inSqlite_Table_Link:
+            先把srLink的Table mapping到srALL
+    inSqlite_Insert_Record:
+        inSqlite_Calculate_Insert_SQLLength:
+            先計算產生的Sql語句的長度，才能動態配置記憶體空間
+    inSqlite_Gernerate_InsertSQL:
+        組合最終的Sql，Insert into ...values(?,?...)，這邊注意到VALUES裡面是放入問號
+    inSqlite_Binding_Values:
+        上述提到的問號，會透過index方式把參數值綁定回去
+    sqlite3_step(srSQLStat):
+        真正執行Sql動作
+inSqlite_Get_Max_TableID_Flow:
+    取得最大的TableID，更新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTableID = atoi(szTableID)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+如果有【EMV】和【Contactless】交易:
+    inBATCH_Insert_All_Flow(pobTran, _TN_EMV_TABLE_):
+        這邊是Insert  srEMVRec資料到Table，可直接參考上述
+inFunc_Save_Last_Txn_Host:
+    inFile_Linux_Delete_In_Fs_Data
+        inFile_Unlink_File:
+            inRetVal = unlink( ./fs_data/LAST_TXN_HOST.txt );
+inFile_Linux_Create_In_Fs_Data:
+    inFile_Linux_Create:
+        open file，取得Fd
+inFunc_Data_Chmod:
+    新增檔案權限為744
+檔案指針指向開頭，寫入pobTran-&gt;srBRec.inHDTIndex資料到檔案
+inFunc_Load_Last_UniqueNo:
+    流程跟上述一樣，差別在刪除和建立的檔名不同，寫入的資料不同，這邊寫入的資料是pobTran-&gt;szUniqueNo
+Note:
+    unlink 會 從檔案系統中刪除檔名。
+    如果檔案之前有任何 開啟的檔案描述字（fd），即使呼叫了 unlink，程式仍然可以透過這些 fd 讀寫檔案。
+    只有當 所有 fd 都關閉 且檔名已被刪除後，檔案的內容才會被系統釋放，檔案才算真正被刪除。 
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_ESC_FuncProcess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_CheckResult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_ESC_FuncProcess:
+    pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
+    pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
+    上述兩個參數BitOn代表檔案不是以主機名為開頭，而是ALL，且不參考批次號
+    inTableType = _TN_BATCH_TABLE_ESC_TEMP_，table name是ALL_ESCTEMP。
+    inSqlite_Drop_Table_Flow:
+        drop table
+    inBATCH_Create_BatchTable_Flow:
+        create table
+    inBATCH_Insert_All_Flow:
+         把當前的pobTran-&gt;srBRec資料寫入table
+    inSqlite_Fsync_TranDB:
+        inSqlite_Fsync_DB:
+            開檔案取得fd，call inSqlite_fsync_retry。
+            inSqlite_fsync_retry:
+                do-while嘗試fsync(fd)，
+                如果遇到errno == EINTR，retry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_CheckResult:
+   inNCCC_Func_Check_NoSignature_Final:
+      根據客製化去設定免簽名(pobTran-&gt;srBRec.uszNoSignatureBit =VS_TRUE/VS_FALSE)
+   inBATCH_Update_NoSignature_By_Sqlite:
+       inFunc_ComposeFileName:
+           取得table name = DC+ Batch Num
+       更新當前調閱編號的TABLE欄位uszNoSignatureBit =  pobTran-&gt;srBRec.uszNoSignatureBit。
+   針對CUP交易:
+       卡機螢幕顯示交易完成、授權碼、金額等，使用者輸入Enter/逾時離開程式。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inSIGN_TouchSignature_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inSIGN_TouchSignature_Flow:
+    如果CFGT的Signpad為_SIGNPAD_MODE_1_INTERNAL_:
+        inSIGN_TouchSignature_Internal:
+            gsrSignpad.inPosition = _SIGNPAD_RIGHT_;
+            inTouchSensorFunc = _Touch_SIGNATURE_;
+            inSIGN_TouchSignature_Internal_START(pobTran, &amp;gsrSignpad):
+                szDispBuffer:組DCC金額+小費
+                srSignpad-&gt;inPosition == _SIGNPAD_RIGHT_:
+                    顯示SIGNPAD_RIGHT.bmp
+                    inSIGN_Text_To_BMPEx:
+                        這邊猜是把szDispBuffer 轉成圖
+                    這裡呼叫inSIGN_Rotate_TextBMP兩次:     
+                    inSIGN_Rotate_TextBMP:
+                        旋轉圖
+                    顯示金額的圖
+                inDISP_Display_Black_Back:
+                    CTOS_LCDGSetBox:
+                        在畫布上塗滿一個矩形
+                inSIGN_TouchSignature_Start:
+                    CTOS_TouchSignatureStart:
+                            通過在觸控面板上準備一個區域並等待用戶在面板區域簽名來啟動簽名捕捉過程。
+                            簽名將被記錄到Signature.bmp中。
+                inSIGN_TimeoutStart:
+                    設定srSignpad-&gt;ulSignTimeStart
+                inFunc_ComposeFileName_InvoiceNumber:
+                    取得主機名稱+Batch num +.bmp
+                inFILE_Delete:
+                    先刪檔避免沒簽名用到上個批次漏刪的簽名圖檔
+                inDisTouch_Flush_TouchFile:
+                        原先有開啟/dev/input/event0，要先close(&amp;ginTouch_Handle)
+            while-loop:
+                inDisTouch_TouchSensor_Click_Slide:
+                    開啟觸控檔，讀取觸控檔案，開始分析讀出的事件，並inchoice取得返回的觸碰事件。
+                如果在簽名板上下筆(inChoice == _SignTouch_Signpad_):
+                    gsrSignpad.inSigned = VS_TRUE;
+                    /* 簽名板，於落筆簽名後，應重新計算timeout時間。 */
+                    inSIGN_TimeoutStart(&amp;gsrSignpad.ulSignTimeStart);
+                進入簽名板後於1分鐘後開始提示音，1分30秒後Timeout。
+                如果點擊取消或是按鍵按下取消(inChoice == _SignTouch_Clear_ || uszKey == _KEY_CANCEL_):
+                    inSIGN_TouchSignature_Internal_END:
+                        CTOS_TouchSignatureTerminate:
+                            立即終止簽名捕捉過程。
+                    inSIGN_TouchSignature_Internal_START:
+                        顯示簽名板。
+                如果是點擊確認或是按鍵按下Ok或是逾時:
+                    inSIGN_IsSigned:
+                        確認是否有被簽名過
+                    如果有被簽名過:
+                        inSIGN_TouchSignature_Internal_END:
+                            關掉觸碰檔
+                        inSIGN_BMPConverter_Right:
+                            bmp檔案向右轉90度
+                        inSIGN_BMPConverter_OneColor:
+                            圖片轉換成單色並存成批次簽名圖檔(主機名+批次號+.bmp)
+                        inFile_Move_File:
+                            檔案從./目錄移動到./fs_data/底下
+                        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inSignStatus = _SIGN_SIGNED_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                        inBATCH_Update_Sign_Status_By_Sqlite:
+                            inSqlite_Update_ByInvNum_SignState:
+                                資料庫更新table欄位inSignStatus = _SIGN_SIGNED_
+                            inNCCC_Func_ESC_FuncProcess:
+                                針對ALL_ESCTEMP table name，
+                                先drop舊table，create table，在把新的pobTran-&gt;srBRec資料insert到table
+                    如果未被簽名過:
+                        inSIGN_TouchSignature_Internal_END:
+                            關掉觸碰檔
+                        inFile_Unlink_File:
+                            unlink ./Signature.bmp
+                        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inSignStatus = _SIGN_BYPASS_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                        inBATCH_Update_Sign_Status_By_Sqlite:
+                            資料庫更新table欄位inSignStatus = _SIGN_BYPASS_
+                        inNCCC_Func_ESC_FuncProcess:
+                            參考上述
+                    如果點擊旋轉或是按下d_KBD_DOT(是#這個按鍵嗎?):
+                        判斷是否已經下筆 有下筆則擋住旋轉，
+                        inSIGN_TouchSignature_Internal_END:
+                            關掉觸碰檔
+                        gsrSignpad.inPosition把左邊改成右邊、右邊改成左邊，
+                        並重新呼叫inSIGN_TouchSignature_Internal_START，產生新的簽名板。
+</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1796,9 +2150,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">因為在DCC詢價接收電文並解電文會取得外幣相關資料，在這支程式會把資料顯示在端末機畫面上，
-顯示內容包含 1.外幣/2.台幣選項、轉換比率、轉換費率，並等待使用者選取選項外幣或是台幣，
-如果選擇台幣，會切換回NCCC主機，並呼叫inFunc_Get_HDPT_General_Data 取得Batch Number, STAN Number, Invoice Number。
+      <t xml:space="preserve">看起來根據特定條件設定
 </t>
     </r>
     <r>
@@ -1811,178 +2163,56 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>pobTran-&gt;srBRec.lnBatchNum = atol(szBatchNum);
-pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);
-pobTran-&gt;srBRec.lnOrgInvNum = atol(szInvoiceNum);
-pobTran-&gt;srBRec.uszNCCCDCCRateBit = VS_TRUE;
-pobTran-&gt;srBRec.uszDCCTransBit = VS_FALSE;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inNCCC_Func_SetTxnOnlineOffline_Flow:
-依據TRT FileName 去跑function ID，目前只看inNCCC_DCC_Func_SetTxnOnlineOffline這支程式。
-inNCCC_DCC_Func_SetTxnOnlineOffline:
-    DCC不能離線授權，如果pobTran-&gt;srBRec.szAuthCode回Y1,return VS_ERROR;
+      <t xml:space="preserve">pobTran-&gt;srBRec.inESCUploadMode = _ESC_STATUS_SUPPORTED_;
+pobTran-&gt;srBRec.inESCTransactionCode = pobTran-&gt;inTransactionCode;
 </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">    pobTran-&gt;srBRec.uszForceOnlineBit = VS_TRUE;
-    pobTran-&gt;srBRec.uszOfflineBit = VS_FALSE;
-    pobTran-&gt;srBRec.uszUpload1Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;srBRec.uszUpload2Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;srBRec.uszUpload3Bit = VS_FALSE; /* 不會產生任何 Advice */
-    pobTran-&gt;uszReversalBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    如果交易類型是結帳，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;uszReversalBit = VS_FALSE;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inNCCC_ATS_Func_BuildAndSendPacket:
-   inNCCC_ATS_GetSTAN:
-      取得STAN Number
-   處理online交易:
-      inNCCC_ATS_ProcessReversal:
-         inNCCC_ATS_ProcessReversal:
-            inNCCC_ATS_ReversalSave_Flow:
-               因為判斷撥接備援功能為OFF，所以不做事
-   inNCCC_ATS_ProcessOnline:
-      </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inISOTxnCode = pobTran-&gt;inTransactionCode;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>inNCCC_ATS_SendPackRecvUnPack:
-      組 ISO 電文、傳送及接收 ISO 電文、解 ISO 電文
-   inNCCC_ATS_CheckRespCode:
-      依據回應碼返回交易結果</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inTransactionResult = _TRAN_RESULT_AUTHORIZED_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-   inNCCC_ATS_CheckAuthCode:
-      如果不是CUP交易且授權碼是空白或是"000000"情況:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">         pobTran-&gt;inErrorMsg = _ERROR_CODE_V3_AUTH_CODE_NOT_VALID_;
-         pobTran-&gt;inTransactionResult = _TRAN_RESULT_CANCELLED_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-      反之:
-           return VS_SUCCESS;
-   inNCCC_ATS_SetSTAN:
-      STAN Number 加一
-   inNCCC_ATS_AnalysePacket:
-      inNCCC_ATS_OnlineAnalyseEMV:
-         pobTran-&gt;inTransactionResult == _TRAN_RESULT_AUTHORIZED_情況:
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>這邊有判斷水位，不曉得是什麼?</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckPAN_EXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_Func_Check_Special_Card_In_OPT_Flow:
+     有輸入金額情況:
+          inNCCC_Func_CheckSpecialCard_Flow:
+               pobTran-&gt;uszCheck_OPT_Special_CardBit == VS_TRUE:
+                    return (VS_SUCCESS);
+                    會在inNCCC_Func_Check_Special_Card_In_OPT_Flow執行完inNCCC_Func_CheckSpecialCard_Flow，
+                    設定uszCheck_OPT_Special_CardBit，也就是在opt會做設定，之後再進入check special card會因為這個bit跳過檢查。
+               inGetSpecialCardRangeEnable(szFuncEnable):
+                    如果CFGT沒開特殊卡別參數檔，跳過不檢核。
+               inNCCC_Func_CheckSpecialCard(pobTran, _CAMPAIGNNUMBER_00_NO_SIGNATURE_):
+                    inGetSpecialCardRangeEnable(szFuncEnable):
+                         如果CFGT沒開特殊卡別參數檔，一樣跳過不檢核。
+                    取得卡號長度，
+                    for-loop:
+                         inLoadSCDTRec(i):
+                              讀SCDT檔案，每次讀一筆record，取得高低卡號範圍、活動代碼，
+                              如果是要判別的活動代碼:
+                              如果卡別是CUP:
+                                   判斷高低卡號是否皆為9999999999，如果符合，設定uszInCardBin = VS_TRUE。
+                              如果不是:
+                                   判斷卡號在高低卡號範圍內，設定uszInCardBin = VS_TRUE。
+                         如果uszInCardBin == VS_TRUE(SCDT檔案有該卡別):
+                              取得SCDT Rec的活動限額，
+                              如果交易金額&lt;=活動限額:
+                                   inFunc_SunDay_Sum_Check_In_Range:
+                                        判斷現在日期是否符合活動日期內。
+          如果活動代碼是_CAMPAIGNNUMBER_00_NO_SIGNATURE_:
+               交易類型不是簽名優先程度比活動代碼高，
                </t>
     </r>
     <r>
@@ -1995,41 +2225,368 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>EMVGlobConfig.uszAction = d_ONLINE_ACTION_APPROVAL;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-               inFunc_SetEDCDateTime(pobTran-&gt;srBRec.szDate, pobTran-&gt;srBRec.szTime):
-                     要更新端末機的日期及時間</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新到其他主機的調閱編號資料庫欄位上，
-判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_SetTxnOnlineOffline_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_BuildAndSendPacket_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Beep_After_Auth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>客製化為_CUSTOMER_INDICATOR_123_IKEA_或是_CUSTOMER_INDICATOR_124_EVER_RICH_ ，主機回覆授權加入提示音</t>
+      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
+            pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+          如果活動代碼是_CAMPAIGNNUMBER_01_PLAIN_PAN_:
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial01Bit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+          inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable):
+               srLink的TABLE欄位會reference inTableID和szEverRichSCDTEnable
+          inSqlite_Get_Table_ByRecordID_All:
+               會select query結果給srAll，更新szEverRichSCDTEnable的值，是為了往下客製化會用到。
+          往下做客製化是_CUSTOMER_INDICATOR_075_DUTY_FREE_或是_CUSTOMER_INDICATOR_103_DUTY_FREE_，
+          先跳過不看。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_CurrencyOption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果是DCC交易:
+     pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;
+如果不是:
+     跳過。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CFGT檔案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">已開啟列印產品代碼功能情況:
+    未輸入產品代號:
+        使用者輸入數字0~9比對PCDRec的szKeyMap(端末機對應之按鍵(Hot Key))，
+        找到對應的產品代碼及產品說明
+        memcpy(szDispMsg, pobTran-&gt;srBRec.szProductCode, 16);
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inGetProductScript(pobTran-&gt;srBRec.szProductCode)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(取得產品代碼及產品說明)
+    已輸入產品代號:
+        跳過function;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckCustomizePassword:
+    先Load PWDRec，如果有開啟銷售密碼功能，取得該銷售密碼，
+    後續inDISP_Enter8x16_Character_Mask輸入密碼，
+    比對是不是銷售密碼，如果不是就一直輸入，直到輸入完成/超時/取消才結束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>先檢查當筆交易如果是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+inDISP_Enter8x16_GetAmount:
+    輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
+    pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
+    pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_DCC_, &amp;inDCC_HostIndex):
+     找HDT檔案中是否有DCC主機名稱的這筆Record，並把這筆Record所在第幾筆更新到inDCC_HostIndex。
+inNCCC_DCC_GetDCC_Enable:
+     判斷DCC主機功能是否開啟。
+如果DCC主機功能已開啟:
+     inLoadHDPTRec(inDCC_HostIndex):
+          取得srHDPTRec資料。
+     inGetMustSettleBit:
+          取得szMustSettleBit 為是否結帳的flag。
+     如果szMustSettleBit為true:
+          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_CREDIT_NCCC_, &amp;inNCCC_HostIndex):
+    取得HDT是否有NCCC主機這筆Record，並把這筆Record所在第幾筆更新到inNCCC_HostIndex上。
+    inLoadHDPTRec(inNCCC_HostIndex):
+          執行select * from HDPT where inTableID = (inNCCC_HostIndex +1) ORDER BY inTableID DESC LIMIT 1，
+          query完結果更新到srHDPTRec。
+     inGetMustSettleBit:
+          取得szMustSettleBit 為是否結帳的flag。
+     如果szMustSettleBit為true:
+          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可連續刷卡檢核有開啟情況:
+    檢查卡號和gszDuplicatePAN如果重複，顯示提示訊息。
+Note :  gszDuplicatePAN值來自於 inFunc_DuplicateSave()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_GetCardFields_CTLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inGetTMSOK:
+     從EDC檔案取得szTMSOK判斷TMS下載是否成功
+如果szTMSOK 不是Y:
+     卡機螢幕顯示請執行參數下載等訊息。
+inNCCC_DCC_GetDCC_Enable:
+     從HDT檔案找DCC主機，並判斷主機功能是否開啟。
+如果主機功能已開啟:
+     inGetNCCCFESMode:
+          取得NCCC FES
+     如果FESMode 不是MFES或是ATS:
+          卡機螢幕顯示 此版不支援DCC等訊息。
+     inGetDCCInit:
+          取得szDCCInit，是否還沒下過第一次DCC參數
+     如果szDCCInit 是 1:
+          卡機螢幕顯示 請執行DCC參數下載等訊息。
+inNCCC_Func_Check_TMS_Setting_Compatible:
+     根據條件判斷，不符合情況下，卡機螢幕顯示此機器不支援、請重新參數下載 等訊息。
+inGetEncryptMode:
+     取得CFGT檔案中的szEncryptMode，檢查是否有 註冊TSAM 和是否有放入SLOT1 SAM卡
+inNCCC_Func_Check_Inv_Problem_Before_Txn:
+     for-loop主要執行兩次抓前兩筆:
+          inFunc_Find_Specific_HDTindex:
+               取NCCC或是DCC的index。
+          inLoadHDTRec(inHDTIndex[i]);
+          inLoadHDPTRec(inHDTIndex[i]);
+          檢查主機功能是否開啟，
+          檢查是否需要先結帳，
+          抓主機調閱編號最大值inMaxInv，
+          這邊取inMaxInv方式是，如果inMaxInv 小於等於 ginNCCCDCCInvoice，
+          更新inMaxInv = ginNCCCDCCInvoice;，
+          這邊的ginNCCCDCCInvoice 因為還未呼叫inNCCC_Func_Update_Memory_Invoice，所以目前為0?
+          Note: inNCCC_Func_Update_Memory_Invoice會更新ginNCCCDCCInvoice。
+     for-loop主要執行兩次抓前兩筆:
+          inFunc_Find_Specific_HDTindex:
+               取NCCC或是DCC的index。
+          inLoadHDTRec(inHDTIndex[i]);
+          inLoadHDPTRec(inHDTIndex[i]);
+          檢查主機功能是否開啟，
+          檢查是否需要先結帳，
+          inGetInvoiceNum:
+               取得NCCC/DCC的各自Invoice Number。
+          如果各自的Invoice Number &lt;= inMaxInv:
+               卡機螢幕顯示 10秒後重開機等訊息，逾時執行inFunc_Reboot 重置系統。
+     如果上述檢查都沒問題，要load原本的index(pobTran-&gt;srBRec.inHDTIndex)，
+     如果pobTran-&gt;srBRec.inHDTIndex&gt;=0:
+          inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
+          inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);
+     如果pobTran-&gt;srBRec.inHDTIndex&lt; 0(防呆):
+          inLoadHDTRec(0);
+          inLoadHDPTRec(0);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CFGT檔案中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>櫃號功能有開啟情況下，如果當筆交易為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+未輸入櫃號情況下:
+    inDISP_Enter8x16_Character_Mask:
+        輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
+        更新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，
+       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>並且剩餘長度用空白補齊。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+如果已有櫃號:
+    跳過function;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_StoreID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckTermStatus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_Amount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetAmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inACCUM_UpdateFlow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2037,7 +2594,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2092,6 +2649,15 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2113,7 +2679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2121,8 +2687,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2405,12 +2976,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="112.5" customWidth="1"/>
     <col min="3" max="3" width="130.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="100.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2435,543 +3007,583 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
-      <c r="C6" t="s">
-        <v>5</v>
+      <c r="C6" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="135" x14ac:dyDescent="0.3">
-      <c r="C24" s="1" t="s">
-        <v>60</v>
+      <c r="C24" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
-      <c r="C26" s="1" t="s">
-        <v>20</v>
+      <c r="C26" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" ht="240" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" ht="45" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" ht="90" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="165" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C50" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C54" s="1" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C58" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="195" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="225" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D66" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" ht="75" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="2:4" ht="90" x14ac:dyDescent="0.3">
       <c r="C70" s="1" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="C72" s="4" t="s">
-        <v>100</v>
+      <c r="C72" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="2:4" ht="120" x14ac:dyDescent="0.3">
-      <c r="C74" s="4" t="s">
-        <v>103</v>
+      <c r="C74" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="2:4" ht="165" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B81" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C82" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B83" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" ht="30" x14ac:dyDescent="0.3">
-      <c r="C84" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" ht="105" x14ac:dyDescent="0.3">
+      <c r="C81" s="1"/>
+      <c r="D81" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" ht="390" x14ac:dyDescent="0.3">
+      <c r="C82" s="1"/>
+      <c r="D82" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" ht="165" x14ac:dyDescent="0.3">
+      <c r="C83" s="1"/>
+      <c r="D83" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="C84" s="1"/>
+      <c r="D84" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C85" s="1"/>
+      <c r="D85" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C87" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" ht="30" x14ac:dyDescent="0.3">
+      <c r="C89" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C91" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" ht="240" x14ac:dyDescent="0.3">
+      <c r="C93" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C95" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" ht="45" x14ac:dyDescent="0.3">
+      <c r="C97" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" ht="30" x14ac:dyDescent="0.3">
+      <c r="C99" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C101" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C86" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B87" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3" ht="240" x14ac:dyDescent="0.3">
-      <c r="C88" s="1" t="s">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" ht="255" x14ac:dyDescent="0.3">
+      <c r="C103" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B104" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" ht="135" x14ac:dyDescent="0.3">
+      <c r="C105" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C107" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" ht="105" x14ac:dyDescent="0.3">
+      <c r="C109" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" ht="105" x14ac:dyDescent="0.3">
+      <c r="C111" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B89" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="C90" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" ht="45" x14ac:dyDescent="0.3">
-      <c r="C92" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B93" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" ht="30" x14ac:dyDescent="0.3">
-      <c r="C94" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B95" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3" ht="60" x14ac:dyDescent="0.3">
-      <c r="C96" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B97" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" ht="210" x14ac:dyDescent="0.3">
-      <c r="C98" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B99" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3" ht="60" x14ac:dyDescent="0.3">
-      <c r="C100" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B101" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C102" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B103" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="2:3" ht="105" x14ac:dyDescent="0.3">
-      <c r="C104" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B105" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3" ht="105" x14ac:dyDescent="0.3">
-      <c r="C106" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B107" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C108" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B109" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C110" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3" ht="45" x14ac:dyDescent="0.3">
-      <c r="B111" s="1" t="s">
-        <v>22</v>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B112" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C113" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B114" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C115" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C116" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" ht="120" x14ac:dyDescent="0.3">
+      <c r="C117" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" ht="45" x14ac:dyDescent="0.3">
+      <c r="B118" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -780,11 +780,6 @@
       </rPr>
       <t>pobTran-&gt;uszReversalBit = VS_FALSE;</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新到其他主機的調閱編號資料庫欄位上，
-判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1324,10 +1319,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
      inCTLS_SendReadyForSale_Internal:
@@ -1550,205 +1541,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
-pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
-inSqlite_ESC_Delete_Record_Flow:
-    因為設定uszFileNameNoNeedHostBit和uszFileNameNoNeedNumBit 為true，所以取得的檔名為ALL + _ESCTEMP，
-    inSqlite_ESC_Delete_Record:
-         刪除這個ALL_ESCTEMP這個TABLE中，inTableID最小的資料。
-pobTran-&gt;uszFileNameNoNeedHostBit = VS_FALSE;
-pobTran-&gt;uszFileNameNoNeedNumBit = VS_FALSE;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_ESC_Func_Upload:
-   inNCCC_ESC_ProcessOnline:
-       inNCCC_ESC_Make_E1Data:
-           inNCCC_ESC_Open_File:
-              針對 ESC_E1.txt，先刪除既有檔案，並重新建立新檔案。
-           取得inPrintIndex = 1(DCC 簽單 For Sale)，呼叫srESCReceiptType[inPrintIndex]取得簽單內容存到buffer中，
-           再呼叫inNCCC_ESC_Append_E1 把buffer內容轉成big5，寫入ESC_E1.txt檔案中。
-       inNCCC_ESC_Data_Compress_Encryption:
-           inNCCC_tSAM_Decide_tSAM_Slot:
-               抓tSAM Slot
-           刪除檔案ESC_E1_E.txt.gz、ESC_E2_E.bmp.gz。
-           inFunc_Data_GZip:
-               組字串gzip  ./fs_data/ESC_E1.txt，執行這行command。
-           inNCCC_TMK_Write_ESCKey:
-               組Encryption Key(szKeyFull) = Key1 + Key2 + Key1，設定CTOS_KMS2KEYWRITE_PARA srKeyWritePara結構體，
-               inKMS_Write(&amp;srKeyWritePara)，流程是這樣，但這個結構體和inKMS_Write用意並不清楚。
-           開啟ESC_E1.txt.gz檔案，從檔案開頭讀出32個字元(szRawData32)，inNCCC_tSAM_Encrypt針對szRawData32的17~32個字元做加密，
-           取得加密後16 Bytes並塞回去並重新寫入檔案開頭中，並把ESC_E1.txt.gz改名為ESC_E1_E.txt.gz
-           inFunc_ComposeFileName_InvoiceNumber:
-               取得主機名稱+調閱編號+ .bmp，例如DC000009.bmp
-           inFILE_Check_Exist:
-               檢查檔案是否存在
-           inFunc_Data_Copy:
-               組字串cp ./fs_data/DC000009.bmp ./fs_data/ESC_BMP_BACKUP.bmp，執行command。
-           inFunc_Data_GZip:
-               組字串gzip  ./fs_data/DC000009.bmp，執行command。
-           inFunc_Data_Rename:
-               組字串mv ./fs_data/ESC_BMP_BACKUP.bmp ./fs_data/DC000009.bmp，執行command。
-           inFILE_Rename:
-               DC000009.bmp.gz改名為ESC_E2.bmp.gz
-           開啟ESC_E2.bmp.gz檔案，從檔案開頭讀出32個字元(szRawData32)，inNCCC_tSAM_Encrypt針對szRawData32的17~32個字元做加密，
-           取得加密後16 Bytes並塞回去並重新寫入檔案開頭中，並把ESC_E2.bmp.gz改名為ESC_E2_E.bmp.gz
-           inNCCC_ESC_Data_Packet:
-               讀取ESC_E1_E.txt.gz和ESC_E2_E.bmp.gz資料存到EscData ESC_UPLOAD_DATA[_ESC_LIMIT_]，包含
-               //表示E1/E2
-               ESC_UPLOAD_DATA[ginEscDataIndex].inTableIndex = inTableIndex;
-               //總封包數
-               ESC_UPLOAD_DATA[ginEscDataIndex].inTotalPacketCnt = inTotalCnt;
-               //第幾個封包
-               ESC_UPLOAD_DATA[ginEscDataIndex].inPacketCnt = i;
-               //總封包大小
-               ESC_UPLOAD_DATA[ginEscDataIndex].lnTotalPacketSize = lnFileSize;
-           while迴圈 根據ESC_UPLOAD_DATA[ginEscDataIndex].inTableIndex是E1/E2，開始組 電簽上傳 的電文，欄位F_11會是STAN NUM遞增，
-           欄位F_59則會使用ESC_UPLOAD_DATA[ginEscDataIndex]的內容，接著做送、收、解電文。
-           inFILE_Delete:
-               刪除ESC_E1_E.txt.gz和ESC_E2_E.bmp.gz檔案。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>如果inNCCC_ESC_ProcessOnline return VS_SUCCESS:
-    inACCUM_UpdateFlow_ESC:
-        inFunc_ComposeFileName:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-              </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">取得檔名hostName + batch num + .amt，例如:DC000004.amt
-        開啟DC000004.amt檔案，如果不存在就建立檔案，並指向檔案開頭，讀取ACCUM_TOTAL_REC srAccumRec的資料，
-        inACCUM_Update_ESC_TotalAmount:
-                srAccumRec-&gt;lnESC_SuccessNum ++;
-                srAccumRec-&gt;llESC_SuccessAmount += pobTran-&gt;srBRec.lnTxnAmount;
-         inACCUM_StoreRecord:
-                 一樣開啟檔案，指向檔案開頭，把ACCUM_TOTAL_REC srAccumRec 資料寫入檔案。
-         inBATCH_GetTransRecord_By_Sqlite:
-                 inBATCH_Get_Batch_ByInvNum_Flow:
-                        更新pobTran-&gt;srBRec資料
-                 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnOrgSTANNum = pobTran-&gt;srBRec.lnSTANNum;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">       pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_UPLOADED_;
-       pobTran-&gt;srBRec.uszESCOrgUploadBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         inBATCH_Update_ESC_Uploaded_By_Sqlite:
-             inBATCH_FuncUpdateTxnRecord_By_Sqlite:
-                  pobTran-&gt;uszUpdateBatchBit == VS_TRUE:
-                      inSqlite_Check_Table_Exist_Flow:
-                            確認Table是否存在。
-                      inSqlite_Update_ByInvNum_TranState_Flow:
-                         inSqlite_Update_ByInvNum_TranState:
-                               取得table name是主機名稱 +調閱編號
-                               更新table的uszUpdated 的狀態為1
-                  inBATCH_Insert_All_Flow:
-                        insert into 當前的pobtran的srBRec到資料庫。
-                  inSqlite_Get_Max_TableID_Flow:
-                        抓出最大筆的TableID，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                 inFunc_Save_Last_Txn_Host:
-                       刪除既有的LAST_TXN_HOST.txt檔案，新增檔案，設定檔案權限為744
-                       開啟檔案，寫入pobTran-&gt;srBRec.inHDTIndex到檔案裡。
-         inFunc_Save_Last_UniqueNo:
-             不是ECR發動，return VS_SUCCESS;
-     inFunc_ComposeFileName_InvoiceNumber:
-         取得主機名稱 + 調閱編號+.bmp
-     inFILE_Delete:
-          刪除檔案。
-</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2013,6 +1806,421 @@
   </si>
   <si>
     <t>inSIGN_TouchSignature_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_PrintReceipt_ByBuffer_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckPAN_EXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_Func_Check_Special_Card_In_OPT_Flow:
+     有輸入金額情況:
+          inNCCC_Func_CheckSpecialCard_Flow:
+               pobTran-&gt;uszCheck_OPT_Special_CardBit == VS_TRUE:
+                    return (VS_SUCCESS);
+                    會在inNCCC_Func_Check_Special_Card_In_OPT_Flow執行完inNCCC_Func_CheckSpecialCard_Flow，
+                    設定uszCheck_OPT_Special_CardBit，也就是在opt會做設定，之後再進入check special card會因為這個bit跳過檢查。
+               inGetSpecialCardRangeEnable(szFuncEnable):
+                    如果CFGT沒開特殊卡別參數檔，跳過不檢核。
+               inNCCC_Func_CheckSpecialCard(pobTran, _CAMPAIGNNUMBER_00_NO_SIGNATURE_):
+                    inGetSpecialCardRangeEnable(szFuncEnable):
+                         如果CFGT沒開特殊卡別參數檔，一樣跳過不檢核。
+                    取得卡號長度，
+                    for-loop:
+                         inLoadSCDTRec(i):
+                              讀SCDT檔案，每次讀一筆record，取得高低卡號範圍、活動代碼，
+                              如果是要判別的活動代碼:
+                              如果卡別是CUP:
+                                   判斷高低卡號是否皆為9999999999，如果符合，設定uszInCardBin = VS_TRUE。
+                              如果不是:
+                                   判斷卡號在高低卡號範圍內，設定uszInCardBin = VS_TRUE。
+                         如果uszInCardBin == VS_TRUE(SCDT檔案有該卡別):
+                              取得SCDT Rec的活動限額，
+                              如果交易金額&lt;=活動限額:
+                                   inFunc_SunDay_Sum_Check_In_Range:
+                                        判斷現在日期是否符合活動日期內。
+          如果活動代碼是_CAMPAIGNNUMBER_00_NO_SIGNATURE_:
+               交易類型不是簽名優先程度比活動代碼高，
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
+            pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+          如果活動代碼是_CAMPAIGNNUMBER_01_PLAIN_PAN_:
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial01Bit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+          inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable):
+               srLink的TABLE欄位會reference inTableID和szEverRichSCDTEnable
+          inSqlite_Get_Table_ByRecordID_All:
+               會select query結果給srAll，更新szEverRichSCDTEnable的值，是為了往下客製化會用到。
+          往下做客製化是_CUSTOMER_INDICATOR_075_DUTY_FREE_或是_CUSTOMER_INDICATOR_103_DUTY_FREE_，
+          先跳過不看。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_CurrencyOption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果是DCC交易:
+     pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;
+如果不是:
+     跳過。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CFGT檔案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">已開啟列印產品代碼功能情況:
+    未輸入產品代號:
+        使用者輸入數字0~9比對PCDRec的szKeyMap(端末機對應之按鍵(Hot Key))，
+        找到對應的產品代碼及產品說明
+        memcpy(szDispMsg, pobTran-&gt;srBRec.szProductCode, 16);
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inGetProductScript(pobTran-&gt;srBRec.szProductCode)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(取得產品代碼及產品說明)
+    已輸入產品代號:
+        跳過function;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckCustomizePassword:
+    先Load PWDRec，如果有開啟銷售密碼功能，取得該銷售密碼，
+    後續inDISP_Enter8x16_Character_Mask輸入密碼，
+    比對是不是銷售密碼，如果不是就一直輸入，直到輸入完成/超時/取消才結束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>先檢查當筆交易如果是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+inDISP_Enter8x16_GetAmount:
+    輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
+    pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
+    pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_DCC_, &amp;inDCC_HostIndex):
+     找HDT檔案中是否有DCC主機名稱的這筆Record，並把這筆Record所在第幾筆更新到inDCC_HostIndex。
+inNCCC_DCC_GetDCC_Enable:
+     判斷DCC主機功能是否開啟。
+如果DCC主機功能已開啟:
+     inLoadHDPTRec(inDCC_HostIndex):
+          取得srHDPTRec資料。
+     inGetMustSettleBit:
+          取得szMustSettleBit 為是否結帳的flag。
+     如果szMustSettleBit為true:
+          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_CREDIT_NCCC_, &amp;inNCCC_HostIndex):
+    取得HDT是否有NCCC主機這筆Record，並把這筆Record所在第幾筆更新到inNCCC_HostIndex上。
+    inLoadHDPTRec(inNCCC_HostIndex):
+          執行select * from HDPT where inTableID = (inNCCC_HostIndex +1) ORDER BY inTableID DESC LIMIT 1，
+          query完結果更新到srHDPTRec。
+     inGetMustSettleBit:
+          取得szMustSettleBit 為是否結帳的flag。
+     如果szMustSettleBit為true:
+          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可連續刷卡檢核有開啟情況:
+    檢查卡號和gszDuplicatePAN如果重複，顯示提示訊息。
+Note :  gszDuplicatePAN值來自於 inFunc_DuplicateSave()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_GetCardFields_CTLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inGetTMSOK:
+     從EDC檔案取得szTMSOK判斷TMS下載是否成功
+如果szTMSOK 不是Y:
+     卡機螢幕顯示請執行參數下載等訊息。
+inNCCC_DCC_GetDCC_Enable:
+     從HDT檔案找DCC主機，並判斷主機功能是否開啟。
+如果主機功能已開啟:
+     inGetNCCCFESMode:
+          取得NCCC FES
+     如果FESMode 不是MFES或是ATS:
+          卡機螢幕顯示 此版不支援DCC等訊息。
+     inGetDCCInit:
+          取得szDCCInit，是否還沒下過第一次DCC參數
+     如果szDCCInit 是 1:
+          卡機螢幕顯示 請執行DCC參數下載等訊息。
+inNCCC_Func_Check_TMS_Setting_Compatible:
+     根據條件判斷，不符合情況下，卡機螢幕顯示此機器不支援、請重新參數下載 等訊息。
+inGetEncryptMode:
+     取得CFGT檔案中的szEncryptMode，檢查是否有 註冊TSAM 和是否有放入SLOT1 SAM卡
+inNCCC_Func_Check_Inv_Problem_Before_Txn:
+     for-loop主要執行兩次抓前兩筆:
+          inFunc_Find_Specific_HDTindex:
+               取NCCC或是DCC的index。
+          inLoadHDTRec(inHDTIndex[i]);
+          inLoadHDPTRec(inHDTIndex[i]);
+          檢查主機功能是否開啟，
+          檢查是否需要先結帳，
+          抓主機調閱編號最大值inMaxInv，
+          這邊取inMaxInv方式是，如果inMaxInv 小於等於 ginNCCCDCCInvoice，
+          更新inMaxInv = ginNCCCDCCInvoice;，
+          這邊的ginNCCCDCCInvoice 因為還未呼叫inNCCC_Func_Update_Memory_Invoice，所以目前為0?
+          Note: inNCCC_Func_Update_Memory_Invoice會更新ginNCCCDCCInvoice。
+     for-loop主要執行兩次抓前兩筆:
+          inFunc_Find_Specific_HDTindex:
+               取NCCC或是DCC的index。
+          inLoadHDTRec(inHDTIndex[i]);
+          inLoadHDPTRec(inHDTIndex[i]);
+          檢查主機功能是否開啟，
+          檢查是否需要先結帳，
+          inGetInvoiceNum:
+               取得NCCC/DCC的各自Invoice Number。
+          如果各自的Invoice Number &lt;= inMaxInv:
+               卡機螢幕顯示 10秒後重開機等訊息，逾時執行inFunc_Reboot 重置系統。
+     如果上述檢查都沒問題，要load原本的index(pobTran-&gt;srBRec.inHDTIndex)，
+     如果pobTran-&gt;srBRec.inHDTIndex&gt;=0:
+          inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
+          inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);
+     如果pobTran-&gt;srBRec.inHDTIndex&lt; 0(防呆):
+          inLoadHDTRec(0);
+          inLoadHDPTRec(0);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CFGT檔案中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>櫃號功能有開啟情況下，如果當筆交易為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+未輸入櫃號情況下:
+    inDISP_Enter8x16_Character_Mask:
+        輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
+        更新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，
+       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>並且剩餘長度用空白補齊。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+如果已有櫃號:
+    跳過function;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_StoreID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckTermStatus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_Amount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetAmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新到其他主機的調閱編號資料庫欄位上，
+判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2145,10 +2353,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inFunc_PrintReceipt_ByBuffer_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">看起來根據特定條件設定
 </t>
@@ -2175,133 +2379,106 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
+      <t>Note:這邊的pobTran-&gt;srBRec.inESCUploadMode會在inNCCC_ESC_Func_Upload當作條件判斷，做電子簽單上傳。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>這邊有判斷水位，不曉得是什麼?</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inFunc_CheckPAN_EXP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inNCCC_Func_Check_Special_Card_In_OPT_Flow:
-     有輸入金額情況:
-          inNCCC_Func_CheckSpecialCard_Flow:
-               pobTran-&gt;uszCheck_OPT_Special_CardBit == VS_TRUE:
-                    return (VS_SUCCESS);
-                    會在inNCCC_Func_Check_Special_Card_In_OPT_Flow執行完inNCCC_Func_CheckSpecialCard_Flow，
-                    設定uszCheck_OPT_Special_CardBit，也就是在opt會做設定，之後再進入check special card會因為這個bit跳過檢查。
-               inGetSpecialCardRangeEnable(szFuncEnable):
-                    如果CFGT沒開特殊卡別參數檔，跳過不檢核。
-               inNCCC_Func_CheckSpecialCard(pobTran, _CAMPAIGNNUMBER_00_NO_SIGNATURE_):
-                    inGetSpecialCardRangeEnable(szFuncEnable):
-                         如果CFGT沒開特殊卡別參數檔，一樣跳過不檢核。
-                    取得卡號長度，
-                    for-loop:
-                         inLoadSCDTRec(i):
-                              讀SCDT檔案，每次讀一筆record，取得高低卡號範圍、活動代碼，
-                              如果是要判別的活動代碼:
-                              如果卡別是CUP:
-                                   判斷高低卡號是否皆為9999999999，如果符合，設定uszInCardBin = VS_TRUE。
-                              如果不是:
-                                   判斷卡號在高低卡號範圍內，設定uszInCardBin = VS_TRUE。
-                         如果uszInCardBin == VS_TRUE(SCDT檔案有該卡別):
-                              取得SCDT Rec的活動限額，
-                              如果交易金額&lt;=活動限額:
-                                   inFunc_SunDay_Sum_Check_In_Range:
-                                        判斷現在日期是否符合活動日期內。
-          如果活動代碼是_CAMPAIGNNUMBER_00_NO_SIGNATURE_:
-               交易類型不是簽名優先程度比活動代碼高，
-               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
-            pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-          如果活動代碼是_CAMPAIGNNUMBER_01_PLAIN_PAN_:
-               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial01Bit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-          inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable):
-               srLink的TABLE欄位會reference inTableID和szEverRichSCDTEnable
-          inSqlite_Get_Table_ByRecordID_All:
-               會select query結果給srAll，更新szEverRichSCDTEnable的值，是為了往下客製化會用到。
-          往下做客製化是_CUSTOMER_INDICATOR_075_DUTY_FREE_或是_CUSTOMER_INDICATOR_103_DUTY_FREE_，
-          先跳過不看。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_CurrencyOption</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果是DCC交易:
-     pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;
-如果不是:
-     跳過。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>CFGT檔案</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">已開啟列印產品代碼功能情況:
-    未輸入產品代號:
-        使用者輸入數字0~9比對PCDRec的szKeyMap(端末機對應之按鍵(Hot Key))，
-        找到對應的產品代碼及產品說明
-        memcpy(szDispMsg, pobTran-&gt;srBRec.szProductCode, 16);
+    <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inACCUM_UpdateFlow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inBATCH_GetTransRecord_By_Sqlite(pobTran):
+    inBATCH_Get_Batch_ByInvNum_Flow(pobTran, _TN_BATCH_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
+        讀取最初得invoice num的pobTran-&gt;srBRec。
+        如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
+                pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE):
+                    inBATCH_Get_Batch_ByInvNum_Flow(pobTran, _TN_EMV_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
+                        讀取最初得invoice num的pobTran-&gt;srEMVRec。
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnOrgSTANNum = pobTran-&gt;srBRec.lnSTANNum;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_PAPER_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+inBATCH_Update_ESC_Uploaded_By_Sqlite(pobTran):
+    pobTran-&gt;uszUpdateBatchBit = VS_TRUE;
+    這邊設定uszUpdateBatchBit是為了inBATCH_FuncUpdateTxnRecord_By_Sqlite只做更新資料而非Insert。
+    inBATCH_FuncUpdateTxnRecord_By_Sqlite(pobTran):
+        inSqlite_Update_ByInvNum_TranState_Flow(pobTran, _TN_BATCH_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
+            更新資料庫欄位uszUpdated 值為1
+        inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_):
+            insert into pobTran-&gt;srBRec資料。
+        inSqlite_Get_Max_TableID_Flow(pobTran, _TN_BATCH_TABLE_, szTableID):
+            szTableID取得最大的主鍵。
         </t>
     </r>
     <r>
@@ -2314,55 +2491,54 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>inGetProductScript(pobTran-&gt;srBRec.szProductCode)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(取得產品代碼及產品說明)
-    已輸入產品代號:
-        跳過function;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_CheckCustomizePassword:
-    先Load PWDRec，如果有開啟銷售密碼功能，取得該銷售密碼，
-    後續inDISP_Enter8x16_Character_Mask輸入密碼，
-    比對是不是銷售密碼，如果不是就一直輸入，直到輸入完成/超時/取消才結束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>先檢查當筆交易如果是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-inDISP_Enter8x16_GetAmount:
-    輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
+      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
+            pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE): 
+            inBATCH_Insert_All_Flow(pobTran, _TN_EMV_TABLE_):
+                insert into pobTran-&gt;srEMVRec 資料。
+pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
+pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
+設定上述兩個bit，檔名不取主機名稱+Batch num。
+inSqlite_ESC_Delete_Record_Flow(pobTran, _TN_BATCH_TABLE_ESC_TEMP_):
+    刪除最小一筆inTableID的ALL_ESCTEMP資料。
+pobTran-&gt;uszFileNameNoNeedHostBit = VS_FALSE;
+pobTran-&gt;uszFileNameNoNeedNumBit = VS_FALSE;
+設定上述兩個bit，恢復原先設定。
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">如果pobTran-&gt;srBRec支援ESC支援且pobTran-&gt;srBRec簽名狀態是_SIGN_BYPASS_:
+    inACCUM_UpdateFlow_ESC(pobTran, _ESC_ACCUM_STATUS_BYPASS_):
+        inFunc_ComposeFileName:
+            取得檔名是NCCC+Batch Num + .amt，這個檔名已在inACCUM_UpdateFlow被建立。
+        讀取檔案的到 ACCUM_TOTAL_REC srAccumRec，執行以下兩個function，   
+        inACCUM_Update_ESC_TotalAmount:
+            srAccumRec-&gt;lnESC_BypassNum ++;
+            srAccumRec-&gt;lnESC_TotalFailULNum ++;
+            如果inUpdateType == _ESC_ACCUM_STATUS_BYPASS_:
+                如果是正向且一般交易:
+                    srAccumRec-&gt;llESC_BypassAmount += pobTran-&gt;srBRec.lnTxnAmount;
+                    srAccumRec-&gt;llESC_TotalFailULAmount += pobTran-&gt;srBRec.lnTxnAmount;
+        inACCUM_StoreRecord:
+            將ACCUM_TOTAL_REC srAccumRec 重新寫回檔案裡。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">如果pobTran-&gt;srBRec支援ESC支援且pobTran-&gt;srBRec簽名狀態是_SIGN_BYPASS_: 
     </t>
     </r>
     <r>
@@ -2375,218 +2551,89 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
-    pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
-    pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Must_SETTLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Func_Must_SETTLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_DCC_, &amp;inDCC_HostIndex):
-     找HDT檔案中是否有DCC主機名稱的這筆Record，並把這筆Record所在第幾筆更新到inDCC_HostIndex。
-inNCCC_DCC_GetDCC_Enable:
-     判斷DCC主機功能是否開啟。
-如果DCC主機功能已開啟:
-     inLoadHDPTRec(inDCC_HostIndex):
-          取得srHDPTRec資料。
-     inGetMustSettleBit:
-          取得szMustSettleBit 為是否結帳的flag。
-     如果szMustSettleBit為true:
-          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_CREDIT_NCCC_, &amp;inNCCC_HostIndex):
-    取得HDT是否有NCCC主機這筆Record，並把這筆Record所在第幾筆更新到inNCCC_HostIndex上。
-    inLoadHDPTRec(inNCCC_HostIndex):
-          執行select * from HDPT where inTableID = (inNCCC_HostIndex +1) ORDER BY inTableID DESC LIMIT 1，
-          query完結果更新到srHDPTRec。
-     inGetMustSettleBit:
-          取得szMustSettleBit 為是否結帳的flag。
-     如果szMustSettleBit為true:
-          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不可連續刷卡檢核有開啟情況:
-    檢查卡號和gszDuplicatePAN如果重複，顯示提示訊息。
-Note :  gszDuplicatePAN值來自於 inFunc_DuplicateSave()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_GetCardFields_CTLS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inGetTMSOK:
-     從EDC檔案取得szTMSOK判斷TMS下載是否成功
-如果szTMSOK 不是Y:
-     卡機螢幕顯示請執行參數下載等訊息。
-inNCCC_DCC_GetDCC_Enable:
-     從HDT檔案找DCC主機，並判斷主機功能是否開啟。
-如果主機功能已開啟:
-     inGetNCCCFESMode:
-          取得NCCC FES
-     如果FESMode 不是MFES或是ATS:
-          卡機螢幕顯示 此版不支援DCC等訊息。
-     inGetDCCInit:
-          取得szDCCInit，是否還沒下過第一次DCC參數
-     如果szDCCInit 是 1:
-          卡機螢幕顯示 請執行DCC參數下載等訊息。
-inNCCC_Func_Check_TMS_Setting_Compatible:
-     根據條件判斷，不符合情況下，卡機螢幕顯示此機器不支援、請重新參數下載 等訊息。
-inGetEncryptMode:
-     取得CFGT檔案中的szEncryptMode，檢查是否有 註冊TSAM 和是否有放入SLOT1 SAM卡
-inNCCC_Func_Check_Inv_Problem_Before_Txn:
-     for-loop主要執行兩次抓前兩筆:
-          inFunc_Find_Specific_HDTindex:
-               取NCCC或是DCC的index。
-          inLoadHDTRec(inHDTIndex[i]);
-          inLoadHDPTRec(inHDTIndex[i]);
-          檢查主機功能是否開啟，
-          檢查是否需要先結帳，
-          抓主機調閱編號最大值inMaxInv，
-          這邊取inMaxInv方式是，如果inMaxInv 小於等於 ginNCCCDCCInvoice，
-          更新inMaxInv = ginNCCCDCCInvoice;，
-          這邊的ginNCCCDCCInvoice 因為還未呼叫inNCCC_Func_Update_Memory_Invoice，所以目前為0?
-          Note: inNCCC_Func_Update_Memory_Invoice會更新ginNCCCDCCInvoice。
-     for-loop主要執行兩次抓前兩筆:
-          inFunc_Find_Specific_HDTindex:
-               取NCCC或是DCC的index。
-          inLoadHDTRec(inHDTIndex[i]);
-          inLoadHDPTRec(inHDTIndex[i]);
-          檢查主機功能是否開啟，
-          檢查是否需要先結帳，
-          inGetInvoiceNum:
-               取得NCCC/DCC的各自Invoice Number。
-          如果各自的Invoice Number &lt;= inMaxInv:
-               卡機螢幕顯示 10秒後重開機等訊息，逾時執行inFunc_Reboot 重置系統。
-     如果上述檢查都沒問題，要load原本的index(pobTran-&gt;srBRec.inHDTIndex)，
-     如果pobTran-&gt;srBRec.inHDTIndex&gt;=0:
-          inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
-          inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);
-     如果pobTran-&gt;srBRec.inHDTIndex&lt; 0(防呆):
-          inLoadHDTRec(0);
-          inLoadHDPTRec(0);</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>CFGT檔案中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>櫃號功能有開啟情況下，如果當筆交易為</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-未輸入櫃號情況下:
-    inDISP_Enter8x16_Character_Mask:
-        輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
-        更新</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">，
-       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>並且剩餘長度用空白補齊。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-如果已有櫃號:
-    跳過function;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_StoreID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_CheckTermStatus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_Amount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_GetAmount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inACCUM_UpdateFlow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
+      <t>pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_PAPER_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    inBATCH_ESC_Save_Advice_Flow(pobTran):
+        inNCCC_Func_Get_STAN_Flow:
+            inFunc_Find_Specific_HDTindex 找到NCCC/DCC/TAKA的HDT index，比對pobTran-&gt;srBRec.inHDTIndex是抓哪個主機，
+            目前主機是選NCCC,
+            inNCCC_ATS_GetSTAN:
+                取得STAN NUM，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        inNCCC_Func_Set_STAN_Flow:
+            一樣透過inFunc_Find_Specific_HDTindex 找到NCCC/DCC/TAKA的HDT index，
+            且pobTran-&gt;srBRec.inHDTIndex抓NCCC主機，
+            inNCCC_ATS_SetSTAN:
+                取得HDT主機index對應的HDPT檔案的Stan Num，做Stan Num +1 ,更新回HDPT.szSTANNum，
+                inSaveHDPTRec:
+                    更新HDPT Record回資料庫。
+        inBATCH_ESC_Save_Advice_By_Sqlite:
+            inADVICE_ESC_SaveAppend_By_Sqlite:
+                inBATCH_Create_BatchTable_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_):
+                    建立table ，table name = NCCC + Batch Num + _ESCADV
+                inBATCH_Create_BatchTable_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_EMV_):
+                    建立table ，table name = NCCC + Batch Num + _ESCADVEMV，外鍵是NCCC + Batch Num + _ESCADV。
+                inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_):
+                    insert into pobTran-&gt;srBRec 資料。
+                inSqlite_Get_Max_TableID_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_, szTableID):
+                    取得最大的PK，更新值到szTableID，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
+                    pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE):
+                        inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_EMV_):
+                            insert into pobTran-&gt;srEMVRec 資料。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2679,7 +2726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2688,9 +2735,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3007,14 +3051,14 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -3025,17 +3069,17 @@
     </row>
     <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
@@ -3100,22 +3144,22 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="135" x14ac:dyDescent="0.3">
-      <c r="C24" s="5" t="s">
-        <v>111</v>
+      <c r="C24" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
-      <c r="C26" s="5" t="s">
-        <v>101</v>
+      <c r="C26" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -3130,12 +3174,12 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -3145,7 +3189,7 @@
     </row>
     <row r="32" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -3160,7 +3204,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -3190,22 +3234,22 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="165" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
@@ -3215,7 +3259,7 @@
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
@@ -3230,7 +3274,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
@@ -3293,9 +3337,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -3323,12 +3367,12 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.3">
@@ -3343,17 +3387,17 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C72" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="2:4" ht="120" x14ac:dyDescent="0.3">
@@ -3373,7 +3417,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="2:4" ht="165" x14ac:dyDescent="0.3">
@@ -3383,57 +3427,57 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="2:4" ht="105" x14ac:dyDescent="0.3">
       <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="2:4" ht="390" x14ac:dyDescent="0.3">
       <c r="C82" s="1"/>
       <c r="D82" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="2:4" ht="165" x14ac:dyDescent="0.3">
       <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="2:4" ht="30" x14ac:dyDescent="0.3">
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="2:4" ht="30" x14ac:dyDescent="0.3">
@@ -3443,7 +3487,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.3">
@@ -3453,7 +3497,7 @@
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93" spans="2:4" ht="240" x14ac:dyDescent="0.3">
@@ -3463,12 +3507,12 @@
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C95" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.3">
@@ -3488,62 +3532,62 @@
     </row>
     <row r="99" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C99" s="1" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C101" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103" spans="2:3" ht="255" x14ac:dyDescent="0.3">
       <c r="C103" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="105" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C105" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="107" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C107" s="1" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C109" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="105" x14ac:dyDescent="0.3">
@@ -3553,32 +3597,32 @@
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" ht="225" x14ac:dyDescent="0.3">
       <c r="C115" s="1" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="C116" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" ht="120" x14ac:dyDescent="0.3">
-      <c r="C117" s="3" t="s">
-        <v>81</v>
+      <c r="C116" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C117" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="2:3" ht="45" x14ac:dyDescent="0.3">

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -780,6 +780,11 @@
       </rPr>
       <t>pobTran-&gt;uszReversalBit = VS_FALSE;</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新到其他主機的調閱編號資料庫欄位上，
+判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1319,6 +1324,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
      inCTLS_SendReadyForSale_Internal:
@@ -1541,7 +1550,205 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
+pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
+inSqlite_ESC_Delete_Record_Flow:
+    因為設定uszFileNameNoNeedHostBit和uszFileNameNoNeedNumBit 為true，所以取得的檔名為ALL + _ESCTEMP，
+    inSqlite_ESC_Delete_Record:
+         刪除這個ALL_ESCTEMP這個TABLE中，inTableID最小的資料。
+pobTran-&gt;uszFileNameNoNeedHostBit = VS_FALSE;
+pobTran-&gt;uszFileNameNoNeedNumBit = VS_FALSE;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_ESC_Func_Upload:
+   inNCCC_ESC_ProcessOnline:
+       inNCCC_ESC_Make_E1Data:
+           inNCCC_ESC_Open_File:
+              針對 ESC_E1.txt，先刪除既有檔案，並重新建立新檔案。
+           取得inPrintIndex = 1(DCC 簽單 For Sale)，呼叫srESCReceiptType[inPrintIndex]取得簽單內容存到buffer中，
+           再呼叫inNCCC_ESC_Append_E1 把buffer內容轉成big5，寫入ESC_E1.txt檔案中。
+       inNCCC_ESC_Data_Compress_Encryption:
+           inNCCC_tSAM_Decide_tSAM_Slot:
+               抓tSAM Slot
+           刪除檔案ESC_E1_E.txt.gz、ESC_E2_E.bmp.gz。
+           inFunc_Data_GZip:
+               組字串gzip  ./fs_data/ESC_E1.txt，執行這行command。
+           inNCCC_TMK_Write_ESCKey:
+               組Encryption Key(szKeyFull) = Key1 + Key2 + Key1，設定CTOS_KMS2KEYWRITE_PARA srKeyWritePara結構體，
+               inKMS_Write(&amp;srKeyWritePara)，流程是這樣，但這個結構體和inKMS_Write用意並不清楚。
+           開啟ESC_E1.txt.gz檔案，從檔案開頭讀出32個字元(szRawData32)，inNCCC_tSAM_Encrypt針對szRawData32的17~32個字元做加密，
+           取得加密後16 Bytes並塞回去並重新寫入檔案開頭中，並把ESC_E1.txt.gz改名為ESC_E1_E.txt.gz
+           inFunc_ComposeFileName_InvoiceNumber:
+               取得主機名稱+調閱編號+ .bmp，例如DC000009.bmp
+           inFILE_Check_Exist:
+               檢查檔案是否存在
+           inFunc_Data_Copy:
+               組字串cp ./fs_data/DC000009.bmp ./fs_data/ESC_BMP_BACKUP.bmp，執行command。
+           inFunc_Data_GZip:
+               組字串gzip  ./fs_data/DC000009.bmp，執行command。
+           inFunc_Data_Rename:
+               組字串mv ./fs_data/ESC_BMP_BACKUP.bmp ./fs_data/DC000009.bmp，執行command。
+           inFILE_Rename:
+               DC000009.bmp.gz改名為ESC_E2.bmp.gz
+           開啟ESC_E2.bmp.gz檔案，從檔案開頭讀出32個字元(szRawData32)，inNCCC_tSAM_Encrypt針對szRawData32的17~32個字元做加密，
+           取得加密後16 Bytes並塞回去並重新寫入檔案開頭中，並把ESC_E2.bmp.gz改名為ESC_E2_E.bmp.gz
+           inNCCC_ESC_Data_Packet:
+               讀取ESC_E1_E.txt.gz和ESC_E2_E.bmp.gz資料存到EscData ESC_UPLOAD_DATA[_ESC_LIMIT_]，包含
+               //表示E1/E2
+               ESC_UPLOAD_DATA[ginEscDataIndex].inTableIndex = inTableIndex;
+               //總封包數
+               ESC_UPLOAD_DATA[ginEscDataIndex].inTotalPacketCnt = inTotalCnt;
+               //第幾個封包
+               ESC_UPLOAD_DATA[ginEscDataIndex].inPacketCnt = i;
+               //總封包大小
+               ESC_UPLOAD_DATA[ginEscDataIndex].lnTotalPacketSize = lnFileSize;
+           while迴圈 根據ESC_UPLOAD_DATA[ginEscDataIndex].inTableIndex是E1/E2，開始組 電簽上傳 的電文，欄位F_11會是STAN NUM遞增，
+           欄位F_59則會使用ESC_UPLOAD_DATA[ginEscDataIndex]的內容，接著做送、收、解電文。
+           inFILE_Delete:
+               刪除ESC_E1_E.txt.gz和ESC_E2_E.bmp.gz檔案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>如果inNCCC_ESC_ProcessOnline return VS_SUCCESS:
+    inACCUM_UpdateFlow_ESC:
+        inFunc_ComposeFileName:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+              </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">取得檔名hostName + batch num + .amt，例如:DC000004.amt
+        開啟DC000004.amt檔案，如果不存在就建立檔案，並指向檔案開頭，讀取ACCUM_TOTAL_REC srAccumRec的資料，
+        inACCUM_Update_ESC_TotalAmount:
+                srAccumRec-&gt;lnESC_SuccessNum ++;
+                srAccumRec-&gt;llESC_SuccessAmount += pobTran-&gt;srBRec.lnTxnAmount;
+         inACCUM_StoreRecord:
+                 一樣開啟檔案，指向檔案開頭，把ACCUM_TOTAL_REC srAccumRec 資料寫入檔案。
+         inBATCH_GetTransRecord_By_Sqlite:
+                 inBATCH_Get_Batch_ByInvNum_Flow:
+                        更新pobTran-&gt;srBRec資料
+                 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnOrgSTANNum = pobTran-&gt;srBRec.lnSTANNum;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">       pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_UPLOADED_;
+       pobTran-&gt;srBRec.uszESCOrgUploadBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         inBATCH_Update_ESC_Uploaded_By_Sqlite:
+             inBATCH_FuncUpdateTxnRecord_By_Sqlite:
+                  pobTran-&gt;uszUpdateBatchBit == VS_TRUE:
+                      inSqlite_Check_Table_Exist_Flow:
+                            確認Table是否存在。
+                      inSqlite_Update_ByInvNum_TranState_Flow:
+                         inSqlite_Update_ByInvNum_TranState:
+                               取得table name是主機名稱 +調閱編號
+                               更新table的uszUpdated 的狀態為1
+                  inBATCH_Insert_All_Flow:
+                        insert into 當前的pobtran的srBRec到資料庫。
+                  inSqlite_Get_Max_TableID_Flow:
+                        抓出最大筆的TableID，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                 inFunc_Save_Last_Txn_Host:
+                       刪除既有的LAST_TXN_HOST.txt檔案，新增檔案，設定檔案權限為744
+                       開啟檔案，寫入pobTran-&gt;srBRec.inHDTIndex到檔案裡。
+         inFunc_Save_Last_UniqueNo:
+             不是ECR發動，return VS_SUCCESS;
+     inFunc_ComposeFileName_InvoiceNumber:
+         取得主機名稱 + 調閱編號+.bmp
+     inFILE_Delete:
+          刪除檔案。
+</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1806,421 +2013,6 @@
   </si>
   <si>
     <t>inSIGN_TouchSignature_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_PrintReceipt_ByBuffer_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_CheckPAN_EXP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inNCCC_Func_Check_Special_Card_In_OPT_Flow:
-     有輸入金額情況:
-          inNCCC_Func_CheckSpecialCard_Flow:
-               pobTran-&gt;uszCheck_OPT_Special_CardBit == VS_TRUE:
-                    return (VS_SUCCESS);
-                    會在inNCCC_Func_Check_Special_Card_In_OPT_Flow執行完inNCCC_Func_CheckSpecialCard_Flow，
-                    設定uszCheck_OPT_Special_CardBit，也就是在opt會做設定，之後再進入check special card會因為這個bit跳過檢查。
-               inGetSpecialCardRangeEnable(szFuncEnable):
-                    如果CFGT沒開特殊卡別參數檔，跳過不檢核。
-               inNCCC_Func_CheckSpecialCard(pobTran, _CAMPAIGNNUMBER_00_NO_SIGNATURE_):
-                    inGetSpecialCardRangeEnable(szFuncEnable):
-                         如果CFGT沒開特殊卡別參數檔，一樣跳過不檢核。
-                    取得卡號長度，
-                    for-loop:
-                         inLoadSCDTRec(i):
-                              讀SCDT檔案，每次讀一筆record，取得高低卡號範圍、活動代碼，
-                              如果是要判別的活動代碼:
-                              如果卡別是CUP:
-                                   判斷高低卡號是否皆為9999999999，如果符合，設定uszInCardBin = VS_TRUE。
-                              如果不是:
-                                   判斷卡號在高低卡號範圍內，設定uszInCardBin = VS_TRUE。
-                         如果uszInCardBin == VS_TRUE(SCDT檔案有該卡別):
-                              取得SCDT Rec的活動限額，
-                              如果交易金額&lt;=活動限額:
-                                   inFunc_SunDay_Sum_Check_In_Range:
-                                        判斷現在日期是否符合活動日期內。
-          如果活動代碼是_CAMPAIGNNUMBER_00_NO_SIGNATURE_:
-               交易類型不是簽名優先程度比活動代碼高，
-               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
-            pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-          如果活動代碼是_CAMPAIGNNUMBER_01_PLAIN_PAN_:
-               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial01Bit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-          inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable):
-               srLink的TABLE欄位會reference inTableID和szEverRichSCDTEnable
-          inSqlite_Get_Table_ByRecordID_All:
-               會select query結果給srAll，更新szEverRichSCDTEnable的值，是為了往下客製化會用到。
-          往下做客製化是_CUSTOMER_INDICATOR_075_DUTY_FREE_或是_CUSTOMER_INDICATOR_103_DUTY_FREE_，
-          先跳過不看。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_CurrencyOption</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果是DCC交易:
-     pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;
-如果不是:
-     跳過。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>CFGT檔案</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">已開啟列印產品代碼功能情況:
-    未輸入產品代號:
-        使用者輸入數字0~9比對PCDRec的szKeyMap(端末機對應之按鍵(Hot Key))，
-        找到對應的產品代碼及產品說明
-        memcpy(szDispMsg, pobTran-&gt;srBRec.szProductCode, 16);
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>inGetProductScript(pobTran-&gt;srBRec.szProductCode)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(取得產品代碼及產品說明)
-    已輸入產品代號:
-        跳過function;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_CheckCustomizePassword:
-    先Load PWDRec，如果有開啟銷售密碼功能，取得該銷售密碼，
-    後續inDISP_Enter8x16_Character_Mask輸入密碼，
-    比對是不是銷售密碼，如果不是就一直輸入，直到輸入完成/超時/取消才結束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>先檢查當筆交易如果是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-inDISP_Enter8x16_GetAmount:
-    輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
-    pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
-    pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_Func_Must_SETTLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_DCC_Func_Must_SETTLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_DCC_, &amp;inDCC_HostIndex):
-     找HDT檔案中是否有DCC主機名稱的這筆Record，並把這筆Record所在第幾筆更新到inDCC_HostIndex。
-inNCCC_DCC_GetDCC_Enable:
-     判斷DCC主機功能是否開啟。
-如果DCC主機功能已開啟:
-     inLoadHDPTRec(inDCC_HostIndex):
-          取得srHDPTRec資料。
-     inGetMustSettleBit:
-          取得szMustSettleBit 為是否結帳的flag。
-     如果szMustSettleBit為true:
-          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_CREDIT_NCCC_, &amp;inNCCC_HostIndex):
-    取得HDT是否有NCCC主機這筆Record，並把這筆Record所在第幾筆更新到inNCCC_HostIndex上。
-    inLoadHDPTRec(inNCCC_HostIndex):
-          執行select * from HDPT where inTableID = (inNCCC_HostIndex +1) ORDER BY inTableID DESC LIMIT 1，
-          query完結果更新到srHDPTRec。
-     inGetMustSettleBit:
-          取得szMustSettleBit 為是否結帳的flag。
-     如果szMustSettleBit為true:
-          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不可連續刷卡檢核有開啟情況:
-    檢查卡號和gszDuplicatePAN如果重複，顯示提示訊息。
-Note :  gszDuplicatePAN值來自於 inFunc_DuplicateSave()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_GetCardFields_CTLS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inGetTMSOK:
-     從EDC檔案取得szTMSOK判斷TMS下載是否成功
-如果szTMSOK 不是Y:
-     卡機螢幕顯示請執行參數下載等訊息。
-inNCCC_DCC_GetDCC_Enable:
-     從HDT檔案找DCC主機，並判斷主機功能是否開啟。
-如果主機功能已開啟:
-     inGetNCCCFESMode:
-          取得NCCC FES
-     如果FESMode 不是MFES或是ATS:
-          卡機螢幕顯示 此版不支援DCC等訊息。
-     inGetDCCInit:
-          取得szDCCInit，是否還沒下過第一次DCC參數
-     如果szDCCInit 是 1:
-          卡機螢幕顯示 請執行DCC參數下載等訊息。
-inNCCC_Func_Check_TMS_Setting_Compatible:
-     根據條件判斷，不符合情況下，卡機螢幕顯示此機器不支援、請重新參數下載 等訊息。
-inGetEncryptMode:
-     取得CFGT檔案中的szEncryptMode，檢查是否有 註冊TSAM 和是否有放入SLOT1 SAM卡
-inNCCC_Func_Check_Inv_Problem_Before_Txn:
-     for-loop主要執行兩次抓前兩筆:
-          inFunc_Find_Specific_HDTindex:
-               取NCCC或是DCC的index。
-          inLoadHDTRec(inHDTIndex[i]);
-          inLoadHDPTRec(inHDTIndex[i]);
-          檢查主機功能是否開啟，
-          檢查是否需要先結帳，
-          抓主機調閱編號最大值inMaxInv，
-          這邊取inMaxInv方式是，如果inMaxInv 小於等於 ginNCCCDCCInvoice，
-          更新inMaxInv = ginNCCCDCCInvoice;，
-          這邊的ginNCCCDCCInvoice 因為還未呼叫inNCCC_Func_Update_Memory_Invoice，所以目前為0?
-          Note: inNCCC_Func_Update_Memory_Invoice會更新ginNCCCDCCInvoice。
-     for-loop主要執行兩次抓前兩筆:
-          inFunc_Find_Specific_HDTindex:
-               取NCCC或是DCC的index。
-          inLoadHDTRec(inHDTIndex[i]);
-          inLoadHDPTRec(inHDTIndex[i]);
-          檢查主機功能是否開啟，
-          檢查是否需要先結帳，
-          inGetInvoiceNum:
-               取得NCCC/DCC的各自Invoice Number。
-          如果各自的Invoice Number &lt;= inMaxInv:
-               卡機螢幕顯示 10秒後重開機等訊息，逾時執行inFunc_Reboot 重置系統。
-     如果上述檢查都沒問題，要load原本的index(pobTran-&gt;srBRec.inHDTIndex)，
-     如果pobTran-&gt;srBRec.inHDTIndex&gt;=0:
-          inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
-          inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);
-     如果pobTran-&gt;srBRec.inHDTIndex&lt; 0(防呆):
-          inLoadHDTRec(0);
-          inLoadHDPTRec(0);</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>CFGT檔案中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>櫃號功能有開啟情況下，如果當筆交易為</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-未輸入櫃號情況下:
-    inDISP_Enter8x16_Character_Mask:
-        輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
-        更新</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">，
-       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>並且剩餘長度用空白補齊。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-如果已有櫃號:
-    跳過function;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_StoreID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_CheckTermStatus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_Get_OPT_Amount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inCREDIT_Func_GetAmount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>會先抓每個主機的調閱編號，取最大值編號，同步更新到其他主機的調閱編號資料庫欄位上，
-判斷如果原始的調閱編號超過上限且要結帳，設定szMustSettleBit(是否結帳的flag)為"Y"，並同步更新資料庫的欄位值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2353,6 +2145,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>inFunc_PrintReceipt_ByBuffer_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">看起來根據特定條件設定
 </t>
@@ -2379,35 +2175,410 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Note:這邊的pobTran-&gt;srBRec.inESCUploadMode會在inNCCC_ESC_Func_Upload當作條件判斷，做電子簽單上傳。</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>這邊有判斷水位，不曉得是什麼?</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
+    <t>inFunc_CheckPAN_EXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_Func_Check_Special_Card_In_OPT_Flow:
+     有輸入金額情況:
+          inNCCC_Func_CheckSpecialCard_Flow:
+               pobTran-&gt;uszCheck_OPT_Special_CardBit == VS_TRUE:
+                    return (VS_SUCCESS);
+                    會在inNCCC_Func_Check_Special_Card_In_OPT_Flow執行完inNCCC_Func_CheckSpecialCard_Flow，
+                    設定uszCheck_OPT_Special_CardBit，也就是在opt會做設定，之後再進入check special card會因為這個bit跳過檢查。
+               inGetSpecialCardRangeEnable(szFuncEnable):
+                    如果CFGT沒開特殊卡別參數檔，跳過不檢核。
+               inNCCC_Func_CheckSpecialCard(pobTran, _CAMPAIGNNUMBER_00_NO_SIGNATURE_):
+                    inGetSpecialCardRangeEnable(szFuncEnable):
+                         如果CFGT沒開特殊卡別參數檔，一樣跳過不檢核。
+                    取得卡號長度，
+                    for-loop:
+                         inLoadSCDTRec(i):
+                              讀SCDT檔案，每次讀一筆record，取得高低卡號範圍、活動代碼，
+                              如果是要判別的活動代碼:
+                              如果卡別是CUP:
+                                   判斷高低卡號是否皆為9999999999，如果符合，設定uszInCardBin = VS_TRUE。
+                              如果不是:
+                                   判斷卡號在高低卡號範圍內，設定uszInCardBin = VS_TRUE。
+                         如果uszInCardBin == VS_TRUE(SCDT檔案有該卡別):
+                              取得SCDT Rec的活動限額，
+                              如果交易金額&lt;=活動限額:
+                                   inFunc_SunDay_Sum_Check_In_Range:
+                                        判斷現在日期是否符合活動日期內。
+          如果活動代碼是_CAMPAIGNNUMBER_00_NO_SIGNATURE_:
+               交易類型不是簽名優先程度比活動代碼高，
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
+            pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+          如果活動代碼是_CAMPAIGNNUMBER_01_PLAIN_PAN_:
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial01Bit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+          inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable):
+               srLink的TABLE欄位會reference inTableID和szEverRichSCDTEnable
+          inSqlite_Get_Table_ByRecordID_All:
+               會select query結果給srAll，更新szEverRichSCDTEnable的值，是為了往下客製化會用到。
+          往下做客製化是_CUSTOMER_INDICATOR_075_DUTY_FREE_或是_CUSTOMER_INDICATOR_103_DUTY_FREE_，
+          先跳過不看。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_CurrencyOption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果是DCC交易:
+     pobTran-&gt;srBRec.uszNoSignatureBit = VS_FALSE;
+如果不是:
+     跳過。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_ProductCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CFGT檔案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">已開啟列印產品代碼功能情況:
+    未輸入產品代號:
+        使用者輸入數字0~9比對PCDRec的szKeyMap(端末機對應之按鍵(Hot Key))，
+        找到對應的產品代碼及產品說明
+        memcpy(szDispMsg, pobTran-&gt;srBRec.szProductCode, 16);
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inGetProductScript(pobTran-&gt;srBRec.szProductCode)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(取得產品代碼及產品說明)
+    已輸入產品代號:
+        跳過function;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckCustomizePassword:
+    先Load PWDRec，如果有開啟銷售密碼功能，取得該銷售密碼，
+    後續inDISP_Enter8x16_Character_Mask輸入密碼，
+    比對是不是銷售密碼，如果不是就一直輸入，直到輸入完成/超時/取消才結束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>先檢查當筆交易如果是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果已輸入過金額或是二段式收銀機連線的擋第一段不輸入，跳出程式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+inDISP_Enter8x16_GetAmount:
+    輸入金額，顯示的格式為幣別+金額+靠右，金額會加上comma，輸入正確金額後，最後更新值:
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnTxnAmount = atol(srDispObj.szOutput);
+    pobTran-&gt;srBRec.lnOrgTxnAmount = atol(srDispObj.szOutput);
+    pobTran-&gt;srBRec.lnTotalTxnAmount = atol(srDispObj.szOutput);</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_DCC_Func_Must_SETTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_DCC_, &amp;inDCC_HostIndex):
+     找HDT檔案中是否有DCC主機名稱的這筆Record，並把這筆Record所在第幾筆更新到inDCC_HostIndex。
+inNCCC_DCC_GetDCC_Enable:
+     判斷DCC主機功能是否開啟。
+如果DCC主機功能已開啟:
+     inLoadHDPTRec(inDCC_HostIndex):
+          取得srHDPTRec資料。
+     inGetMustSettleBit:
+          取得szMustSettleBit 為是否結帳的flag。
+     如果szMustSettleBit為true:
+          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_Find_Specific_HDTindex(pobTran-&gt;srBRec.inHDTIndex, _HOST_NAME_CREDIT_NCCC_, &amp;inNCCC_HostIndex):
+    取得HDT是否有NCCC主機這筆Record，並把這筆Record所在第幾筆更新到inNCCC_HostIndex上。
+    inLoadHDPTRec(inNCCC_HostIndex):
+          執行select * from HDPT where inTableID = (inNCCC_HostIndex +1) ORDER BY inTableID DESC LIMIT 1，
+          query完結果更新到srHDPTRec。
+     inGetMustSettleBit:
+          取得szMustSettleBit 為是否結帳的flag。
+     如果szMustSettleBit為true:
+          表示要先結帳，卡機畫面顯示請先進行結帳等訊息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可連續刷卡檢核有開啟情況:
+    檢查卡號和gszDuplicatePAN如果重複，顯示提示訊息。
+Note :  gszDuplicatePAN值來自於 inFunc_DuplicateSave()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_GetCardFields_CTLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inGetTMSOK:
+     從EDC檔案取得szTMSOK判斷TMS下載是否成功
+如果szTMSOK 不是Y:
+     卡機螢幕顯示請執行參數下載等訊息。
+inNCCC_DCC_GetDCC_Enable:
+     從HDT檔案找DCC主機，並判斷主機功能是否開啟。
+如果主機功能已開啟:
+     inGetNCCCFESMode:
+          取得NCCC FES
+     如果FESMode 不是MFES或是ATS:
+          卡機螢幕顯示 此版不支援DCC等訊息。
+     inGetDCCInit:
+          取得szDCCInit，是否還沒下過第一次DCC參數
+     如果szDCCInit 是 1:
+          卡機螢幕顯示 請執行DCC參數下載等訊息。
+inNCCC_Func_Check_TMS_Setting_Compatible:
+     根據條件判斷，不符合情況下，卡機螢幕顯示此機器不支援、請重新參數下載 等訊息。
+inGetEncryptMode:
+     取得CFGT檔案中的szEncryptMode，檢查是否有 註冊TSAM 和是否有放入SLOT1 SAM卡
+inNCCC_Func_Check_Inv_Problem_Before_Txn:
+     for-loop主要執行兩次抓前兩筆:
+          inFunc_Find_Specific_HDTindex:
+               取NCCC或是DCC的index。
+          inLoadHDTRec(inHDTIndex[i]);
+          inLoadHDPTRec(inHDTIndex[i]);
+          檢查主機功能是否開啟，
+          檢查是否需要先結帳，
+          抓主機調閱編號最大值inMaxInv，
+          這邊取inMaxInv方式是，如果inMaxInv 小於等於 ginNCCCDCCInvoice，
+          更新inMaxInv = ginNCCCDCCInvoice;，
+          這邊的ginNCCCDCCInvoice 因為還未呼叫inNCCC_Func_Update_Memory_Invoice，所以目前為0?
+          Note: inNCCC_Func_Update_Memory_Invoice會更新ginNCCCDCCInvoice。
+     for-loop主要執行兩次抓前兩筆:
+          inFunc_Find_Specific_HDTindex:
+               取NCCC或是DCC的index。
+          inLoadHDTRec(inHDTIndex[i]);
+          inLoadHDPTRec(inHDTIndex[i]);
+          檢查主機功能是否開啟，
+          檢查是否需要先結帳，
+          inGetInvoiceNum:
+               取得NCCC/DCC的各自Invoice Number。
+          如果各自的Invoice Number &lt;= inMaxInv:
+               卡機螢幕顯示 10秒後重開機等訊息，逾時執行inFunc_Reboot 重置系統。
+     如果上述檢查都沒問題，要load原本的index(pobTran-&gt;srBRec.inHDTIndex)，
+     如果pobTran-&gt;srBRec.inHDTIndex&gt;=0:
+          inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex);
+          inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex);
+     如果pobTran-&gt;srBRec.inHDTIndex&lt; 0(防呆):
+          inLoadHDTRec(0);
+          inLoadHDPTRec(0);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CFGT檔案中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>櫃號功能有開啟情況下，如果當筆交易為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECR發動，如果是已輸入櫃號、二段式收銀機連線的第一段詢卡或是客製化商店，會擋輸入櫃號，否則接著往下判斷。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+未輸入櫃號情況下:
+    inDISP_Enter8x16_Character_Mask:
+        輸入櫃號後，判斷櫃號輸入長度是否在範圍內，
+        更新</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>memcpy(&amp;pobTran-&gt;srBRec.szStoreID[0], &amp;srDispObj.szOutput[0], srDispObj.inOutputLen);</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，
+       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>並且剩餘長度用空白補齊。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+如果已有櫃號:
+    跳過function;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_StoreID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_CheckTermStatus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_Amount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_GetAmount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2415,225 +2586,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">inBATCH_GetTransRecord_By_Sqlite(pobTran):
-    inBATCH_Get_Batch_ByInvNum_Flow(pobTran, _TN_BATCH_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
-        讀取最初得invoice num的pobTran-&gt;srBRec。
-        如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
-                pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE):
-                    inBATCH_Get_Batch_ByInvNum_Flow(pobTran, _TN_EMV_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
-                        讀取最初得invoice num的pobTran-&gt;srEMVRec。
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnOrgSTANNum = pobTran-&gt;srBRec.lnSTANNum;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_PAPER_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-inBATCH_Update_ESC_Uploaded_By_Sqlite(pobTran):
-    pobTran-&gt;uszUpdateBatchBit = VS_TRUE;
-    這邊設定uszUpdateBatchBit是為了inBATCH_FuncUpdateTxnRecord_By_Sqlite只做更新資料而非Insert。
-    inBATCH_FuncUpdateTxnRecord_By_Sqlite(pobTran):
-        inSqlite_Update_ByInvNum_TranState_Flow(pobTran, _TN_BATCH_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
-            更新資料庫欄位uszUpdated 值為1
-        inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_):
-            insert into pobTran-&gt;srBRec資料。
-        inSqlite_Get_Max_TableID_Flow(pobTran, _TN_BATCH_TABLE_, szTableID):
-            szTableID取得最大的主鍵。
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
-            pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE): 
-            inBATCH_Insert_All_Flow(pobTran, _TN_EMV_TABLE_):
-                insert into pobTran-&gt;srEMVRec 資料。
-pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
-pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
-設定上述兩個bit，檔名不取主機名稱+Batch num。
-inSqlite_ESC_Delete_Record_Flow(pobTran, _TN_BATCH_TABLE_ESC_TEMP_):
-    刪除最小一筆inTableID的ALL_ESCTEMP資料。
-pobTran-&gt;uszFileNameNoNeedHostBit = VS_FALSE;
-pobTran-&gt;uszFileNameNoNeedNumBit = VS_FALSE;
-設定上述兩個bit，恢復原先設定。
-</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">如果pobTran-&gt;srBRec支援ESC支援且pobTran-&gt;srBRec簽名狀態是_SIGN_BYPASS_:
-    inACCUM_UpdateFlow_ESC(pobTran, _ESC_ACCUM_STATUS_BYPASS_):
-        inFunc_ComposeFileName:
-            取得檔名是NCCC+Batch Num + .amt，這個檔名已在inACCUM_UpdateFlow被建立。
-        讀取檔案的到 ACCUM_TOTAL_REC srAccumRec，執行以下兩個function，   
-        inACCUM_Update_ESC_TotalAmount:
-            srAccumRec-&gt;lnESC_BypassNum ++;
-            srAccumRec-&gt;lnESC_TotalFailULNum ++;
-            如果inUpdateType == _ESC_ACCUM_STATUS_BYPASS_:
-                如果是正向且一般交易:
-                    srAccumRec-&gt;llESC_BypassAmount += pobTran-&gt;srBRec.lnTxnAmount;
-                    srAccumRec-&gt;llESC_TotalFailULAmount += pobTran-&gt;srBRec.lnTxnAmount;
-        inACCUM_StoreRecord:
-            將ACCUM_TOTAL_REC srAccumRec 重新寫回檔案裡。
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">如果pobTran-&gt;srBRec支援ESC支援且pobTran-&gt;srBRec簽名狀態是_SIGN_BYPASS_: 
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_PAPER_;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    inBATCH_ESC_Save_Advice_Flow(pobTran):
-        inNCCC_Func_Get_STAN_Flow:
-            inFunc_Find_Specific_HDTindex 找到NCCC/DCC/TAKA的HDT index，比對pobTran-&gt;srBRec.inHDTIndex是抓哪個主機，
-            目前主機是選NCCC,
-            inNCCC_ATS_GetSTAN:
-                取得STAN NUM，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-        inNCCC_Func_Set_STAN_Flow:
-            一樣透過inFunc_Find_Specific_HDTindex 找到NCCC/DCC/TAKA的HDT index，
-            且pobTran-&gt;srBRec.inHDTIndex抓NCCC主機，
-            inNCCC_ATS_SetSTAN:
-                取得HDT主機index對應的HDPT檔案的Stan Num，做Stan Num +1 ,更新回HDPT.szSTANNum，
-                inSaveHDPTRec:
-                    更新HDPT Record回資料庫。
-        inBATCH_ESC_Save_Advice_By_Sqlite:
-            inADVICE_ESC_SaveAppend_By_Sqlite:
-                inBATCH_Create_BatchTable_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_):
-                    建立table ，table name = NCCC + Batch Num + _ESCADV
-                inBATCH_Create_BatchTable_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_EMV_):
-                    建立table ，table name = NCCC + Batch Num + _ESCADVEMV，外鍵是NCCC + Batch Num + _ESCADV。
-                inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_):
-                    insert into pobTran-&gt;srBRec 資料。
-                inSqlite_Get_Max_TableID_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_, szTableID):
-                    取得最大的PK，更新值到szTableID，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-            如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
-                    pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE):
-                        inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_EMV_):
-                            insert into pobTran-&gt;srEMVRec 資料。</t>
-    </r>
+    <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2726,7 +2679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2735,6 +2688,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3051,14 +3007,14 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -3069,17 +3025,17 @@
     </row>
     <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
@@ -3144,22 +3100,22 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="135" x14ac:dyDescent="0.3">
-      <c r="C24" s="4" t="s">
-        <v>104</v>
+      <c r="C24" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
-      <c r="C26" s="4" t="s">
-        <v>94</v>
+      <c r="C26" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -3174,12 +3130,12 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -3189,7 +3145,7 @@
     </row>
     <row r="32" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -3204,7 +3160,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -3234,22 +3190,22 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="165" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
@@ -3259,7 +3215,7 @@
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
@@ -3274,7 +3230,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
@@ -3337,9 +3293,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="2:3" ht="75" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -3367,12 +3323,12 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.3">
@@ -3387,17 +3343,17 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C72" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="2:4" ht="120" x14ac:dyDescent="0.3">
@@ -3417,7 +3373,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="2:4" ht="165" x14ac:dyDescent="0.3">
@@ -3427,57 +3383,57 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="2:4" ht="105" x14ac:dyDescent="0.3">
       <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="2:4" ht="390" x14ac:dyDescent="0.3">
       <c r="C82" s="1"/>
       <c r="D82" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="2:4" ht="165" x14ac:dyDescent="0.3">
       <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="2:4" ht="30" x14ac:dyDescent="0.3">
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" spans="2:4" ht="30" x14ac:dyDescent="0.3">
@@ -3487,7 +3443,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.3">
@@ -3497,7 +3453,7 @@
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="2:4" ht="240" x14ac:dyDescent="0.3">
@@ -3507,12 +3463,12 @@
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C95" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.3">
@@ -3532,62 +3488,62 @@
     </row>
     <row r="99" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C99" s="1" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C101" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="103" spans="2:3" ht="255" x14ac:dyDescent="0.3">
       <c r="C103" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C105" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C107" s="1" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="109" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C109" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="105" x14ac:dyDescent="0.3">
@@ -3597,32 +3553,32 @@
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3" ht="225" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C115" s="1" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="C116" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="C117" s="1" t="s">
-        <v>115</v>
+      <c r="C116" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" ht="120" x14ac:dyDescent="0.3">
+      <c r="C117" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="118" spans="2:3" ht="45" x14ac:dyDescent="0.3">

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -1550,205 +1550,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
-pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
-inSqlite_ESC_Delete_Record_Flow:
-    因為設定uszFileNameNoNeedHostBit和uszFileNameNoNeedNumBit 為true，所以取得的檔名為ALL + _ESCTEMP，
-    inSqlite_ESC_Delete_Record:
-         刪除這個ALL_ESCTEMP這個TABLE中，inTableID最小的資料。
-pobTran-&gt;uszFileNameNoNeedHostBit = VS_FALSE;
-pobTran-&gt;uszFileNameNoNeedNumBit = VS_FALSE;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inNCCC_ESC_Func_Upload:
-   inNCCC_ESC_ProcessOnline:
-       inNCCC_ESC_Make_E1Data:
-           inNCCC_ESC_Open_File:
-              針對 ESC_E1.txt，先刪除既有檔案，並重新建立新檔案。
-           取得inPrintIndex = 1(DCC 簽單 For Sale)，呼叫srESCReceiptType[inPrintIndex]取得簽單內容存到buffer中，
-           再呼叫inNCCC_ESC_Append_E1 把buffer內容轉成big5，寫入ESC_E1.txt檔案中。
-       inNCCC_ESC_Data_Compress_Encryption:
-           inNCCC_tSAM_Decide_tSAM_Slot:
-               抓tSAM Slot
-           刪除檔案ESC_E1_E.txt.gz、ESC_E2_E.bmp.gz。
-           inFunc_Data_GZip:
-               組字串gzip  ./fs_data/ESC_E1.txt，執行這行command。
-           inNCCC_TMK_Write_ESCKey:
-               組Encryption Key(szKeyFull) = Key1 + Key2 + Key1，設定CTOS_KMS2KEYWRITE_PARA srKeyWritePara結構體，
-               inKMS_Write(&amp;srKeyWritePara)，流程是這樣，但這個結構體和inKMS_Write用意並不清楚。
-           開啟ESC_E1.txt.gz檔案，從檔案開頭讀出32個字元(szRawData32)，inNCCC_tSAM_Encrypt針對szRawData32的17~32個字元做加密，
-           取得加密後16 Bytes並塞回去並重新寫入檔案開頭中，並把ESC_E1.txt.gz改名為ESC_E1_E.txt.gz
-           inFunc_ComposeFileName_InvoiceNumber:
-               取得主機名稱+調閱編號+ .bmp，例如DC000009.bmp
-           inFILE_Check_Exist:
-               檢查檔案是否存在
-           inFunc_Data_Copy:
-               組字串cp ./fs_data/DC000009.bmp ./fs_data/ESC_BMP_BACKUP.bmp，執行command。
-           inFunc_Data_GZip:
-               組字串gzip  ./fs_data/DC000009.bmp，執行command。
-           inFunc_Data_Rename:
-               組字串mv ./fs_data/ESC_BMP_BACKUP.bmp ./fs_data/DC000009.bmp，執行command。
-           inFILE_Rename:
-               DC000009.bmp.gz改名為ESC_E2.bmp.gz
-           開啟ESC_E2.bmp.gz檔案，從檔案開頭讀出32個字元(szRawData32)，inNCCC_tSAM_Encrypt針對szRawData32的17~32個字元做加密，
-           取得加密後16 Bytes並塞回去並重新寫入檔案開頭中，並把ESC_E2.bmp.gz改名為ESC_E2_E.bmp.gz
-           inNCCC_ESC_Data_Packet:
-               讀取ESC_E1_E.txt.gz和ESC_E2_E.bmp.gz資料存到EscData ESC_UPLOAD_DATA[_ESC_LIMIT_]，包含
-               //表示E1/E2
-               ESC_UPLOAD_DATA[ginEscDataIndex].inTableIndex = inTableIndex;
-               //總封包數
-               ESC_UPLOAD_DATA[ginEscDataIndex].inTotalPacketCnt = inTotalCnt;
-               //第幾個封包
-               ESC_UPLOAD_DATA[ginEscDataIndex].inPacketCnt = i;
-               //總封包大小
-               ESC_UPLOAD_DATA[ginEscDataIndex].lnTotalPacketSize = lnFileSize;
-           while迴圈 根據ESC_UPLOAD_DATA[ginEscDataIndex].inTableIndex是E1/E2，開始組 電簽上傳 的電文，欄位F_11會是STAN NUM遞增，
-           欄位F_59則會使用ESC_UPLOAD_DATA[ginEscDataIndex]的內容，接著做送、收、解電文。
-           inFILE_Delete:
-               刪除ESC_E1_E.txt.gz和ESC_E2_E.bmp.gz檔案。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_Func_Send_ECR_After_Print_Receipt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>如果inNCCC_ESC_ProcessOnline return VS_SUCCESS:
-    inACCUM_UpdateFlow_ESC:
-        inFunc_ComposeFileName:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-              </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">取得檔名hostName + batch num + .amt，例如:DC000004.amt
-        開啟DC000004.amt檔案，如果不存在就建立檔案，並指向檔案開頭，讀取ACCUM_TOTAL_REC srAccumRec的資料，
-        inACCUM_Update_ESC_TotalAmount:
-                srAccumRec-&gt;lnESC_SuccessNum ++;
-                srAccumRec-&gt;llESC_SuccessAmount += pobTran-&gt;srBRec.lnTxnAmount;
-         inACCUM_StoreRecord:
-                 一樣開啟檔案，指向檔案開頭，把ACCUM_TOTAL_REC srAccumRec 資料寫入檔案。
-         inBATCH_GetTransRecord_By_Sqlite:
-                 inBATCH_Get_Batch_ByInvNum_Flow:
-                        更新pobTran-&gt;srBRec資料
-                 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.lnOrgSTANNum = pobTran-&gt;srBRec.lnSTANNum;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">       pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_UPLOADED_;
-       pobTran-&gt;srBRec.uszESCOrgUploadBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         inBATCH_Update_ESC_Uploaded_By_Sqlite:
-             inBATCH_FuncUpdateTxnRecord_By_Sqlite:
-                  pobTran-&gt;uszUpdateBatchBit == VS_TRUE:
-                      inSqlite_Check_Table_Exist_Flow:
-                            確認Table是否存在。
-                      inSqlite_Update_ByInvNum_TranState_Flow:
-                         inSqlite_Update_ByInvNum_TranState:
-                               取得table name是主機名稱 +調閱編號
-                               更新table的uszUpdated 的狀態為1
-                  inBATCH_Insert_All_Flow:
-                        insert into 當前的pobtran的srBRec到資料庫。
-                  inSqlite_Get_Max_TableID_Flow:
-                        抓出最大筆的TableID，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                 inFunc_Save_Last_Txn_Host:
-                       刪除既有的LAST_TXN_HOST.txt檔案，新增檔案，設定檔案權限為744
-                       開啟檔案，寫入pobTran-&gt;srBRec.inHDTIndex到檔案裡。
-         inFunc_Save_Last_UniqueNo:
-             不是ECR發動，return VS_SUCCESS;
-     inFunc_ComposeFileName_InvoiceNumber:
-         取得主機名稱 + 調閱編號+.bmp
-     inFILE_Delete:
-          刪除檔案。
-</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2587,6 +2389,228 @@
   </si>
   <si>
     <t>inBATCH_FuncUpdateTxnRecord_By_Sqlite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">如果pobTran-&gt;srBRec支援ESC支援且pobTran-&gt;srBRec簽名狀態是_SIGN_BYPASS_:
+    inACCUM_UpdateFlow_ESC(pobTran, _ESC_ACCUM_STATUS_BYPASS_):
+        inFunc_ComposeFileName:
+            取得檔名是NCCC+Batch Num + .amt，這個檔名已在inACCUM_UpdateFlow被建立。
+        讀取檔案的到 ACCUM_TOTAL_REC srAccumRec，執行以下兩個function，   
+        inACCUM_Update_ESC_TotalAmount:
+            srAccumRec-&gt;lnESC_BypassNum ++;
+            srAccumRec-&gt;lnESC_TotalFailULNum ++;
+            如果inUpdateType == _ESC_ACCUM_STATUS_BYPASS_:
+                如果是正向且一般交易:
+                    srAccumRec-&gt;llESC_BypassAmount += pobTran-&gt;srBRec.lnTxnAmount;
+                    srAccumRec-&gt;llESC_TotalFailULAmount += pobTran-&gt;srBRec.lnTxnAmount;
+        inACCUM_StoreRecord:
+            將ACCUM_TOTAL_REC srAccumRec 重新寫回檔案裡。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">如果pobTran-&gt;srBRec支援ESC支援且pobTran-&gt;srBRec簽名狀態是_SIGN_BYPASS_: 
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_PAPER_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    inBATCH_ESC_Save_Advice_Flow(pobTran):
+        inNCCC_Func_Get_STAN_Flow:
+            inFunc_Find_Specific_HDTindex 找到NCCC/DCC/TAKA的HDT index，比對pobTran-&gt;srBRec.inHDTIndex是抓哪個主機，
+            目前主機是選NCCC,
+            inNCCC_ATS_GetSTAN:
+                取得STAN NUM，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnSTANNum = atol(szSTANNum);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        inNCCC_Func_Set_STAN_Flow:
+            一樣透過inFunc_Find_Specific_HDTindex 找到NCCC/DCC/TAKA的HDT index，
+            且pobTran-&gt;srBRec.inHDTIndex抓NCCC主機，
+            inNCCC_ATS_SetSTAN:
+                取得HDT主機index對應的HDPT檔案的Stan Num，做Stan Num +1 ,更新回HDPT.szSTANNum，
+                inSaveHDPTRec:
+                    更新HDPT Record回資料庫。
+        inBATCH_ESC_Save_Advice_By_Sqlite:
+            inADVICE_ESC_SaveAppend_By_Sqlite:
+                inBATCH_Create_BatchTable_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_):
+                    建立table ，table name = NCCC + Batch Num + _ESCADV
+                inBATCH_Create_BatchTable_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_EMV_):
+                    建立table ，table name = NCCC + Batch Num + _ESCADVEMV，外鍵是NCCC + Batch Num + _ESCADV。
+                inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_):
+                    insert into pobTran-&gt;srBRec 資料。
+                inSqlite_Get_Max_TableID_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_, szTableID):
+                    取得最大的PK，更新值到szTableID，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
+                    pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE):
+                        inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_ESC_ADVICE_EMV_):
+                            insert into pobTran-&gt;srEMVRec 資料。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inBATCH_GetTransRecord_By_Sqlite(pobTran):
+    inBATCH_Get_Batch_ByInvNum_Flow(pobTran, _TN_BATCH_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
+        讀取最初得invoice num的pobTran-&gt;srBRec。
+        如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
+                pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE):
+                    inBATCH_Get_Batch_ByInvNum_Flow(pobTran, _TN_EMV_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
+                        讀取最初得invoice num的pobTran-&gt;srEMVRec。
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.lnOrgSTANNum = pobTran-&gt;srBRec.lnSTANNum;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inESCUploadStatus = _ESC_UPLOAD_STATUS_PAPER_;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+inBATCH_Update_ESC_Uploaded_By_Sqlite(pobTran):
+    pobTran-&gt;uszUpdateBatchBit = VS_TRUE;
+    這邊設定uszUpdateBatchBit是為了inBATCH_FuncUpdateTxnRecord_By_Sqlite只做更新資料而非Insert。
+    inBATCH_FuncUpdateTxnRecord_By_Sqlite(pobTran):
+        inSqlite_Update_ByInvNum_TranState_Flow(pobTran, _TN_BATCH_TABLE_, pobTran-&gt;srBRec.lnOrgInvNum):
+            更新資料庫欄位uszUpdated 值為1
+        inBATCH_Insert_All_Flow(pobTran, _TN_BATCH_TABLE_):
+            insert into pobTran-&gt;srBRec資料。
+        inSqlite_Get_Max_TableID_Flow(pobTran, _TN_BATCH_TABLE_, szTableID):
+            szTableID取得最大的主鍵。
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inTableID = atoi(szTableID);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    如果pobTran-&gt;srBRec.inChipStatus != 0 或 pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE 或 
+            pobTran-&gt;srBRec.uszEMVFallBackBit == VS_TRUE 或 pobTran-&gt;srBRec.uszCUPEMVQRCodeBit == VS_TRUE): 
+            inBATCH_Insert_All_Flow(pobTran, _TN_EMV_TABLE_):
+                insert into pobTran-&gt;srEMVRec 資料。
+pobTran-&gt;uszFileNameNoNeedHostBit = VS_TRUE;
+pobTran-&gt;uszFileNameNoNeedNumBit = VS_TRUE;
+設定上述兩個bit，檔名不取主機名稱+Batch num。
+inSqlite_ESC_Delete_Record_Flow(pobTran, _TN_BATCH_TABLE_ESC_TEMP_):
+    刪除最小一筆inTableID的ALL_ESCTEMP資料。
+pobTran-&gt;uszFileNameNoNeedHostBit = VS_FALSE;
+pobTran-&gt;uszFileNameNoNeedNumBit = VS_FALSE;
+設定上述兩個bit，恢復原先設定。
+</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2679,7 +2703,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2688,9 +2712,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3007,14 +3028,14 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -3025,17 +3046,17 @@
     </row>
     <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
@@ -3100,22 +3121,22 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="135" x14ac:dyDescent="0.3">
-      <c r="C24" s="5" t="s">
-        <v>111</v>
+      <c r="C24" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
-      <c r="C26" s="5" t="s">
-        <v>101</v>
+      <c r="C26" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -3130,7 +3151,7 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
@@ -3145,7 +3166,7 @@
     </row>
     <row r="32" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -3160,7 +3181,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -3190,22 +3211,22 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="165" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
@@ -3215,7 +3236,7 @@
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
@@ -3230,7 +3251,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
@@ -3295,7 +3316,7 @@
     </row>
     <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -3323,12 +3344,12 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.3">
@@ -3453,7 +3474,7 @@
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="2:4" ht="240" x14ac:dyDescent="0.3">
@@ -3463,12 +3484,12 @@
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C95" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.3">
@@ -3493,47 +3514,47 @@
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="101" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C101" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="103" spans="2:3" ht="255" x14ac:dyDescent="0.3">
       <c r="C103" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="105" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C105" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="107" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C107" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" spans="2:3" ht="105" x14ac:dyDescent="0.3">
@@ -3543,7 +3564,7 @@
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="105" x14ac:dyDescent="0.3">
@@ -3566,19 +3587,19 @@
         <v>79</v>
       </c>
     </row>
-    <row r="115" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:3" ht="225" x14ac:dyDescent="0.3">
       <c r="C115" s="1" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="C116" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" ht="120" x14ac:dyDescent="0.3">
-      <c r="C117" s="3" t="s">
-        <v>81</v>
+      <c r="C116" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="C117" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="2:3" ht="45" x14ac:dyDescent="0.3">

--- a/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
+++ b/SRC/FlowChart/一般交易/inEVENT_Responder_SALE_NEW.xlsx
@@ -382,15 +382,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inNCCC_Func_Check_Special_Card_In_OPT_Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>呼叫CTOS_CLPowerOff()，關閉無線感應讀卡機的開關</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>螢幕顯示卡號與有效期供使用者確認</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1325,182 +1317,6 @@
   </si>
   <si>
     <t>inNCCC_Func_Get_Transaction_No_From_PAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
-     inCTLS_SendReadyForSale_Internal:
-       EMVCL_InitTransactionEx(szACTData.bTagNum, szACTData.pbaTransactionData, szACTData.usTransactionDataLen):
-         初始化一筆交易，設定金額、日期、交易類型
-     顯示一般交易金額，偵測事件，包含刷卡、插卡、人工輸入卡號、感應方式
-     以感應卡為例:
-          內圈的WhileLoop:
-               inCTLS_ReceiveReadyForSales_Flow:
-                    ulCTLS_ReceiveReadyForSales_Internal:
-                          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>srCtlsObj.lnSaleRespCode = EMVCL_PerformTransactionEx(&amp;szRCDataEx):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                               透過EMVCL_PerformTransactionEx獲得 發起的交易結果(szRCDataEx)
-          外圈的WhileLoop:
-               偵測感應事件，執行
-                    ulCTLS_CheckResponseCode_SALE:
-                          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszContactlessBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                          inCTLS_UnPackReadyForSale_Flow:
-                              inCTLS_UnPackReadyForSale_Internal:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                             srCtlsObj.uszSchemeID[0] = SCHEME_ID_91_QUICKPASS;
-                                  pobTran-&gt;inTransactionCode = _CUP_SALE_;
-                                  pobTran-&gt;srBRec.inCode = pobTran-&gt;inTransactionCode;
-                                  pobTran-&gt;srBRec.inOrgCode = pobTran-&gt;inTransactionCode;
-                                  pobTran-&gt;srBRec.uszCUPTransBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inKMS_CheckKey:
-                                      這邊看起來是檢查KEY是否存在
-                                       inNCCC_Func_CUP_PowerOn_LogOn:
-                                            暫時沒看
-                                  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszWAVESchemeID = srCtlsObj.uszSchemeID[0];</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inFunc_BCD_to_ASCII(&amp;szASCII[0], &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len * 2);
-                                  szRCDataEx.bTrack2Len = szRCDataEx.bTrack2Len * 2;
-                                  memset(szRCDataEx.baTrack2Data, 0x00, sizeof(szRCDataEx.baTrack2Data));
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                             memcpy(&amp;szRCDataEx.baTrack2Data[0], &amp;szASCII[0], szRCDataEx.bTrack2Len);
-                             memcpy(pobTran-&gt;szTrack1, szRCDataEx.baTrack1Data, szRCDataEx.bTrack1Len);
-                             memcpy(pobTran-&gt;szTrack2, &amp;szRCDataEx.baTrack2Data[0], szRCDataEx.bTrack2Len);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inCARD_unPackCard:
-                                       </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>取得PAN、ExpDate、szServiceCode 、CardHolder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                                  inCTLS_ProcessChipData:
-                                       組電文的EMV Data ，這部分的tagID不清楚要參考哪個文件，需要詢問。
-                                  inCTLS_ExceptionCheck:
-                                        暫時沒看</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1986,93 +1802,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">inNCCC_Func_Check_Special_Card_In_OPT_Flow:
-     有輸入金額情況:
-          inNCCC_Func_CheckSpecialCard_Flow:
-               pobTran-&gt;uszCheck_OPT_Special_CardBit == VS_TRUE:
-                    return (VS_SUCCESS);
-                    會在inNCCC_Func_Check_Special_Card_In_OPT_Flow執行完inNCCC_Func_CheckSpecialCard_Flow，
-                    設定uszCheck_OPT_Special_CardBit，也就是在opt會做設定，之後再進入check special card會因為這個bit跳過檢查。
-               inGetSpecialCardRangeEnable(szFuncEnable):
-                    如果CFGT沒開特殊卡別參數檔，跳過不檢核。
-               inNCCC_Func_CheckSpecialCard(pobTran, _CAMPAIGNNUMBER_00_NO_SIGNATURE_):
-                    inGetSpecialCardRangeEnable(szFuncEnable):
-                         如果CFGT沒開特殊卡別參數檔，一樣跳過不檢核。
-                    取得卡號長度，
-                    for-loop:
-                         inLoadSCDTRec(i):
-                              讀SCDT檔案，每次讀一筆record，取得高低卡號範圍、活動代碼，
-                              如果是要判別的活動代碼:
-                              如果卡別是CUP:
-                                   判斷高低卡號是否皆為9999999999，如果符合，設定uszInCardBin = VS_TRUE。
-                              如果不是:
-                                   判斷卡號在高低卡號範圍內，設定uszInCardBin = VS_TRUE。
-                         如果uszInCardBin == VS_TRUE(SCDT檔案有該卡別):
-                              取得SCDT Rec的活動限額，
-                              如果交易金額&lt;=活動限額:
-                                   inFunc_SunDay_Sum_Check_In_Range:
-                                        判斷現在日期是否符合活動日期內。
-          如果活動代碼是_CAMPAIGNNUMBER_00_NO_SIGNATURE_:
-               交易類型不是簽名優先程度比活動代碼高，
-               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
-            pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-          如果活動代碼是_CAMPAIGNNUMBER_01_PLAIN_PAN_:
-               </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pobTran-&gt;srBRec.uszSpecial01Bit = VS_TRUE;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-          inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable):
-               srLink的TABLE欄位會reference inTableID和szEverRichSCDTEnable
-          inSqlite_Get_Table_ByRecordID_All:
-               會select query結果給srAll，更新szEverRichSCDTEnable的值，是為了往下客製化會用到。
-          往下做客製化是_CUSTOMER_INDICATOR_075_DUTY_FREE_或是_CUSTOMER_INDICATOR_103_DUTY_FREE_，
-          先跳過不看。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inNCCC_DCC_CurrencyOption</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2221,10 +1950,6 @@
     <t>不可連續刷卡檢核有開啟情況:
     檢查卡號和gszDuplicatePAN如果重複，顯示提示訊息。
 Note :  gszDuplicatePAN值來自於 inFunc_DuplicateSave()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inFunc_GetCardFields_CTLS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2368,10 +2093,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inCREDIT_Func_Get_OPT_StoreID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>inFunc_CheckTermStatus</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2611,6 +2332,393 @@
 設定上述兩個bit，恢復原先設定。
 </t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inCREDIT_Func_Get_OPT_StoreID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inFunc_GetCardFields_CTLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inCTLS_SendReadyForSale_Flow:
+     inCTLS_SendReadyForSale_Internal:
+       EMVCL_InitTransactionEx(szACTData.bTagNum, szACTData.pbaTransactionData, szACTData.usTransactionDataLen):
+         初始化一筆交易，設定金額、日期、交易類型
+     顯示一般交易金額，偵測事件，包含刷卡、插卡、人工輸入卡號、感應方式
+     以感應卡為例:
+          內圈的WhileLoop:
+               inCTLS_ReceiveReadyForSales_Flow:
+                    ulCTLS_ReceiveReadyForSales_Internal:
+                          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>srCtlsObj.lnSaleRespCode = EMVCL_PerformTransactionEx(&amp;szRCDataEx):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                               透過EMVCL_PerformTransactionEx獲得 發起的交易結果(szRCDataEx)
+          外圈的WhileLoop:
+               偵測感應事件(ginEventCode == _SENSOR_EVENT_):
+                    ulCTLS_CheckResponseCode_SALE:
+                         srCtlsObj.lnSaleRespCode如果是d_EMVCL_RC_DATA:
+                              (這邊的srCtlsObj.lnSaleRespCode ，
+                               可以從inCTLS_ReceiveReadyForSales_Flow &gt; ulCTLS_ReceiveReadyForSales_Internal 取得)
+                              </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszContactlessBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                              inCTLS_UnPackReadyForSale_Flow:
+                                   inCTLS_UnPackReadyForSale_Internal:
+                                        當 szRCDataEx.bSID == d_EMVCL_SID_VISA_WAVE_QVSDC:
+                                             (從ulCTLS_ReceiveReadyForSales_Internal 呼叫 EMVCL_PerformTransactionEx 取得的szRCDataEx)
+                                             srCtlsObj.uszSchemeID[0] = SCHEME_ID_17_WAVE3;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                    pobTran-&gt;srBRec.uszWAVESchemeID = srCtlsObj.uszSchemeID[0];
+                                    pobTran-&gt;shTrack1Len = szRCDataEx.bTrack1Len;
+                                    pobTran-&gt;shTrack2Len = szRCDataEx.bTrack2Len;
+                                    memcpy(pobTran-&gt;szTrack1, szRCDataEx.baTrack1Data, szRCDataEx.bTrack1Len);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                        如果pobTran-&gt;srBRec.uszWAVESchemeID 是SCHEME_ID_17_WAVE3 or SCHEME_ID_16_WAVE1:
+                                             因為Track2第0個byte為";"，因此略過，
+                                            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> memcpy(pobTran-&gt;szTrack2, &amp;szRCDataEx.baTrack2Data[1], szRCDataEx.bTrack2Len);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                        檢查Track2，如果結尾是'F'或是'?'當成結束符號，如果中間有找到'D'改為'='
+                                        如果pobTran-&gt;szTrack2有值:
+                                             inCARD_unPackCard:
+                                             如果pobTran-&gt;srBRec.uszContactlessBit 等於 True:
+                                                  (這個Bit在上述的ulCTLS_CheckResponseCode_SALE流程被設定為True)
+                                                  從pobTran-&gt;szTrack2取得PAN、ExpDate、szServiceCode，
+                                                  PAN:pobTran-&gt;szTrack2字串中等號之前的數。
+                                                  ExpDate:等號之後的四碼。
+                                                  szServiceCode:等號之後的七碼(ExpDate之後的三碼)。
+                                             檢查卡號是否符合長度。
+                                             取得持卡人名字: pobTran-&gt;szTrack1字串中包含在^^之間的字串，例如: ^ 持卡人名字 ^
+                                             檢查持卡人名字是否符合長度。
+                                         inCTLS_ProcessChipData:
+                                             這邊大部分的tag可以參考電文規格的Field_55: EMV Chip Data，更新值到</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srEMVRec</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，
+                                             但有些Tag像是50、5A、DF8F4F、DF8129...不清楚要參考哪份規格。
+                                         inCTLS_ExceptionCheck:
+                                             這邊會根據上述的Tag更新的pobTran-&gt;srEMVRec去做一些檢查，
+                                             包含例外狀況 Tag檢核 感應限額等等，這部分還未細看。
+                    如果ulCTLS_CheckResponseCode_SALE返回結果是d_EMVCL_RC_DATA:
+                         inCARD_GetBin:
+                              inCARD_LoadGetCDTIndex:
+                                   從CDT.dat檔案中找到卡號高低範圍在pobTran-&gt;srBRec.szPAN之間的Record，
+                                  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inCDTIndex = i;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                   取得這筆CDT Rec 對應交易主機索引(szHostCDTIndex)，
+                                   inFunc_Find_Specific_HDTindex_ByCDTIndex(pobTran-&gt;srBRec.inHDTIndex, szHostCDTIndex, &amp;inHDTIndex):
+                                       從HDT.dat檔案中 ，找到HDT Rec的主機索引與CDT Rec 對應交易主機索引相等的那筆Rec，
+                                       更新index到inHDTIndex。
+                                   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.inHDTIndex = inHDTIndex;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                   inLoadHDTRec(pobTran-&gt;srBRec.inHDTIndex)，判斷主機功能是否有開啟。 
+                                   inFunc_Get_HDPT_General_Data:
+                                             inLoadHDPTRec(pobTran-&gt;srBRec.inHDTIndex):
+                                                       sql query 取得HDPT_REC srHDPTRec。
+                                   取得srHDPTRec的szBatchNum、szSTANNum、szInvoiceNum，更新到pobTran-&gt;srBRec。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                            pobTran-&gt;srBRec.lnBatchNum = atol(szBatchNum);
+                            pobTran-&gt;srBRec.lnSTANNum  = atol(szSTANNum);
+                            pobTran-&gt;srBRec.lnOrgInvNum = atol(szInvoiceNum);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                         inGetModule10Check(szFuncEnable):
+                                   讀CDT檔案的檢查碼查核功能
+                         如果szFuncEnable為'Y':
+                                   inCARD_ValidTrack2_PAN:
+                                             檢查卡號是否正確 
+                         inCARD_ValidTrack2_ExpDate:
+                                   檢查卡片的有效期
+                         inNCCC_Func_Decide_CTLS_TRT(pobTran):
+                                   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;inRunTRTID = _TRT_SALE_CTLS_;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inNCCC_Func_Check_Special_Card_In_OPT_Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">inNCCC_Func_Check_Special_Card_In_OPT_Flow:
+     有輸入金額情況:
+          inNCCC_Func_CheckSpecialCard_Flow:
+               pobTran-&gt;uszCheck_OPT_Special_CardBit == VS_TRUE:
+                    return (VS_SUCCESS);
+                    Note:會在inNCCC_Func_Check_Special_Card_In_OPT_Flow執行完inNCCC_Func_CheckSpecialCard_Flow，
+                             設定uszCheck_OPT_Special_CardBit，會在opt設定，
+                             之後再進入check special card會因為這個bit跳過檢查。
+               inGetSpecialCardRangeEnable(szFuncEnable):
+                    如果CFGT沒開特殊卡別參數檔，跳過不檢核。
+               inNCCC_Func_CheckSpecialCard(pobTran, _CAMPAIGNNUMBER_00_NO_SIGNATURE_):
+                    inGetSpecialCardRangeEnable(szFuncEnable):
+                         如果CFGT沒開特殊卡別參數檔，一樣跳過不檢核。
+                    取得卡號長度，
+                    for-loop:
+                         inLoadSCDTRec(i):
+                              讀SCDT檔案，每次讀一筆record，取得高低卡號範圍、活動代碼，
+                              如果是要判別的活動代碼:
+                              如果卡別是CUP:
+                                   判斷高低卡號是否皆為9999999999，如果符合，設定uszInCardBin = VS_TRUE。
+                              如果卡別不是CUP:
+                                   判斷卡號在高低卡號範圍，設定uszInCardBin = VS_TRUE。
+                         如果uszInCardBin == VS_TRUE(SCDT檔案有該卡別):
+                              取得SCDT Rec的活動限額，
+                              如果交易金額&lt;=活動限額:
+                                   inFunc_SunDay_Sum_Check_In_Range:
+                                        判斷現在日期是否符合活動日期內。
+          如果活動代碼是_CAMPAIGNNUMBER_00_NO_SIGNATURE_:
+               交易類型不是簽名優先程度比活動代碼高，
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial00Bit = VS_TRUE;
+            pobTran-&gt;srBRec.uszNoSignatureBit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+          如果活動代碼是_CAMPAIGNNUMBER_01_PLAIN_PAN_:
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pobTran-&gt;srBRec.uszSpecial01Bit = VS_TRUE;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+          inNCCC_Func_Table_Link_Duty_Free_Function(&amp;srAll, _LS_READ_, &amp;inTableID, szEverRichSCDTEnable):
+               srLink的TABLE欄位會reference inTableID和szEverRichSCDTEnable
+          inSqlite_Get_Table_ByRecordID_All:
+               會select query結果給srAll，更新szEverRichSCDTEnable的值，是為了往下客製化會用到。
+          往下做客製化是_CUSTOMER_INDICATOR_075_DUTY_FREE_或是_CUSTOMER_INDICATOR_103_DUTY_FREE_，
+          先跳過不看。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這邊不顯示卡號有效期的判斷有很多，我只列出其中一項，
+如果pobTran-&gt;srBRec.uszContactlessBit == VS_TRUE:
+    return;
+螢幕顯示卡號與有效期，使用者輸入Enter確認，return VS_SUCCESS，如果按取消/timeout，return VS_ERROR，導致inFLOW_RunOperation的返回值為VS_ERROR。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3028,14 +3136,14 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -3046,17 +3154,17 @@
     </row>
     <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.3">
@@ -3071,7 +3179,7 @@
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -3121,27 +3229,27 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C24" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="120" x14ac:dyDescent="0.3">
       <c r="C26" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="120" x14ac:dyDescent="0.3">
@@ -3151,42 +3259,42 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C36" t="s">
-        <v>32</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="75" x14ac:dyDescent="0.3">
+      <c r="C36" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -3201,32 +3309,32 @@
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="165" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
@@ -3236,7 +3344,7 @@
     </row>
     <row r="46" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
@@ -3251,7 +3359,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="135" x14ac:dyDescent="0.3">
@@ -3261,27 +3369,27 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="75" x14ac:dyDescent="0.3">
       <c r="C54" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
@@ -3291,7 +3399,7 @@
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -3301,85 +3409,85 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="195" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="60" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="2:3" ht="45" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="225" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="60" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="2:4" ht="90" x14ac:dyDescent="0.3">
       <c r="C70" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C72" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="2:4" ht="120" x14ac:dyDescent="0.3">
       <c r="C74" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.3">
@@ -3394,77 +3502,77 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="2:4" ht="165" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="2:4" ht="105" x14ac:dyDescent="0.3">
       <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="2:4" ht="390" x14ac:dyDescent="0.3">
       <c r="C82" s="1"/>
       <c r="D82" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="2:4" ht="165" x14ac:dyDescent="0.3">
       <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="2:4" ht="30" x14ac:dyDescent="0.3">
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="2:4" ht="30" x14ac:dyDescent="0.3">
       <c r="C89" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.3">
@@ -3474,7 +3582,7 @@
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="2:4" ht="240" x14ac:dyDescent="0.3">
@@ -3484,17 +3592,17 @@
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" spans="2:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C95" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="2:3" ht="45" x14ac:dyDescent="0.3">
@@ -3504,102 +3612,102 @@
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="2:3" ht="30" x14ac:dyDescent="0.3">
       <c r="C99" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="101" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C101" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103" spans="2:3" ht="255" x14ac:dyDescent="0.3">
       <c r="C103" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="2:3" ht="135" x14ac:dyDescent="0.3">
       <c r="C105" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="107" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C107" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C109" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="111" spans="2:3" ht="105" x14ac:dyDescent="0.3">
       <c r="C111" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="115" spans="2:3" ht="225" x14ac:dyDescent="0.3">
       <c r="C115" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C116" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="2:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C117" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="118" spans="2:3" ht="45" x14ac:dyDescent="0.3">
